--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -4813,10 +4813,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133582091</v>
+        <v>133582155</v>
       </c>
       <c r="B40" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4824,21 +4824,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4848,10 +4848,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>484893</v>
+        <v>484885</v>
       </c>
       <c r="R40" t="n">
-        <v>7086018</v>
+        <v>7086164</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4883,7 +4883,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4920,7 +4920,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133582072</v>
+        <v>133582091</v>
       </c>
       <c r="B41" t="n">
         <v>80438</v>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>484979</v>
+        <v>484893</v>
       </c>
       <c r="R41" t="n">
-        <v>7086133</v>
+        <v>7086018</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5027,7 +5027,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133582268</v>
+        <v>133582072</v>
       </c>
       <c r="B42" t="n">
         <v>80438</v>
@@ -5062,10 +5062,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484974</v>
+        <v>484979</v>
       </c>
       <c r="R42" t="n">
-        <v>7086064</v>
+        <v>7086133</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5097,7 +5097,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5107,7 +5107,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5134,7 +5134,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133582198</v>
+        <v>133582268</v>
       </c>
       <c r="B43" t="n">
         <v>80438</v>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>484719</v>
+        <v>484974</v>
       </c>
       <c r="R43" t="n">
-        <v>7085978</v>
+        <v>7086064</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5241,7 +5241,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133582059</v>
+        <v>133582198</v>
       </c>
       <c r="B44" t="n">
         <v>80438</v>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484703</v>
+        <v>484719</v>
       </c>
       <c r="R44" t="n">
-        <v>7085994</v>
+        <v>7085978</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5321,7 +5321,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5348,10 +5348,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133582155</v>
+        <v>133582059</v>
       </c>
       <c r="B45" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5359,21 +5359,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5383,10 +5383,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>484885</v>
+        <v>484703</v>
       </c>
       <c r="R45" t="n">
-        <v>7086164</v>
+        <v>7085994</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5418,7 +5418,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5695,10 +5695,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133582273</v>
+        <v>133582070</v>
       </c>
       <c r="B48" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5706,21 +5706,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5730,10 +5730,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>484937</v>
+        <v>484969</v>
       </c>
       <c r="R48" t="n">
-        <v>7086072</v>
+        <v>7086150</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5765,7 +5765,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5775,7 +5775,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5802,10 +5802,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133582261</v>
+        <v>133582065</v>
       </c>
       <c r="B49" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5813,21 +5813,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5837,10 +5837,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>485011</v>
+        <v>484873</v>
       </c>
       <c r="R49" t="n">
-        <v>7086069</v>
+        <v>7086047</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5872,7 +5872,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5882,7 +5882,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5909,10 +5909,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133582156</v>
+        <v>133582223</v>
       </c>
       <c r="B50" t="n">
-        <v>79333</v>
+        <v>83181</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5920,21 +5920,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5944,10 +5944,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>484918</v>
+        <v>484876</v>
       </c>
       <c r="R50" t="n">
-        <v>7086183</v>
+        <v>7086138</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5979,7 +5979,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6016,32 +6016,32 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133582121</v>
+        <v>133582106</v>
       </c>
       <c r="B51" t="n">
-        <v>91881</v>
+        <v>91932</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6051,10 +6051,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485166</v>
+        <v>485052</v>
       </c>
       <c r="R51" t="n">
-        <v>7086186</v>
+        <v>7085993</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133582098</v>
+        <v>133582248</v>
       </c>
       <c r="B52" t="n">
-        <v>79333</v>
+        <v>83307</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>484881</v>
+        <v>485157</v>
       </c>
       <c r="R52" t="n">
-        <v>7085801</v>
+        <v>7086076</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6203,12 +6203,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>20:53</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6235,10 +6230,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133582070</v>
+        <v>133582251</v>
       </c>
       <c r="B53" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6246,21 +6241,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6270,10 +6265,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>484969</v>
+        <v>485137</v>
       </c>
       <c r="R53" t="n">
-        <v>7086150</v>
+        <v>7086066</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6305,7 +6300,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6315,7 +6310,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6342,32 +6337,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133582065</v>
+        <v>133582083</v>
       </c>
       <c r="B54" t="n">
-        <v>91932</v>
+        <v>79492</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6377,10 +6372,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>484873</v>
+        <v>484926</v>
       </c>
       <c r="R54" t="n">
-        <v>7086047</v>
+        <v>7086090</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6412,7 +6407,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6422,7 +6417,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6449,10 +6444,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133582223</v>
+        <v>133582021</v>
       </c>
       <c r="B55" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6460,21 +6455,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6484,10 +6479,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>484876</v>
+        <v>485082</v>
       </c>
       <c r="R55" t="n">
-        <v>7086138</v>
+        <v>7086186</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6519,7 +6514,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6529,7 +6524,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6556,10 +6551,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133582106</v>
+        <v>133582273</v>
       </c>
       <c r="B56" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6567,21 +6562,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6591,10 +6586,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>485052</v>
+        <v>484937</v>
       </c>
       <c r="R56" t="n">
-        <v>7085993</v>
+        <v>7086072</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6626,7 +6621,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6636,7 +6631,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6663,10 +6658,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133582248</v>
+        <v>133582261</v>
       </c>
       <c r="B57" t="n">
-        <v>83307</v>
+        <v>80438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6674,21 +6669,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6698,10 +6693,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485157</v>
+        <v>485011</v>
       </c>
       <c r="R57" t="n">
-        <v>7086076</v>
+        <v>7086069</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6733,7 +6728,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6743,7 +6738,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6770,10 +6765,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133582251</v>
+        <v>133582156</v>
       </c>
       <c r="B58" t="n">
-        <v>83181</v>
+        <v>79333</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6781,21 +6776,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6805,10 +6800,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485137</v>
+        <v>484918</v>
       </c>
       <c r="R58" t="n">
-        <v>7086066</v>
+        <v>7086183</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6840,7 +6835,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6850,7 +6845,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6877,32 +6872,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133582083</v>
+        <v>133582121</v>
       </c>
       <c r="B59" t="n">
-        <v>79492</v>
+        <v>91881</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1249</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6912,10 +6907,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>484926</v>
+        <v>485166</v>
       </c>
       <c r="R59" t="n">
-        <v>7086090</v>
+        <v>7086186</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6947,7 +6942,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6957,7 +6952,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6984,10 +6979,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133582021</v>
+        <v>133582098</v>
       </c>
       <c r="B60" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6995,21 +6990,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7019,10 +7014,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>485082</v>
+        <v>484881</v>
       </c>
       <c r="R60" t="n">
-        <v>7086186</v>
+        <v>7085801</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7054,7 +7049,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7064,7 +7059,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7412,32 +7412,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133582174</v>
+        <v>133582239</v>
       </c>
       <c r="B64" t="n">
-        <v>80467</v>
+        <v>79492</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6462</v>
+        <v>1249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>484630</v>
+        <v>485081</v>
       </c>
       <c r="R64" t="n">
-        <v>7086018</v>
+        <v>7086147</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7519,10 +7519,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133582203</v>
+        <v>133582249</v>
       </c>
       <c r="B65" t="n">
-        <v>80438</v>
+        <v>83181</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7530,21 +7530,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>484774</v>
+        <v>485150</v>
       </c>
       <c r="R65" t="n">
-        <v>7085997</v>
+        <v>7086053</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7626,32 +7626,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133582183</v>
+        <v>133582174</v>
       </c>
       <c r="B66" t="n">
-        <v>83313</v>
+        <v>80467</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6486</v>
+        <v>6462</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>484634</v>
+        <v>484630</v>
       </c>
       <c r="R66" t="n">
-        <v>7085988</v>
+        <v>7086018</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7733,7 +7733,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133582246</v>
+        <v>133582203</v>
       </c>
       <c r="B67" t="n">
         <v>80438</v>
@@ -7768,10 +7768,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>485159</v>
+        <v>484774</v>
       </c>
       <c r="R67" t="n">
-        <v>7086078</v>
+        <v>7085997</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7840,32 +7840,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>133582146</v>
+        <v>133582183</v>
       </c>
       <c r="B68" t="n">
-        <v>80398</v>
+        <v>83313</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229497</v>
+        <v>6486</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7875,10 +7875,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>485019</v>
+        <v>484634</v>
       </c>
       <c r="R68" t="n">
-        <v>7086200</v>
+        <v>7085988</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7947,32 +7947,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>133582124</v>
+        <v>133582246</v>
       </c>
       <c r="B69" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7982,10 +7982,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>485137</v>
+        <v>485159</v>
       </c>
       <c r="R69" t="n">
-        <v>7086195</v>
+        <v>7086078</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8017,7 +8017,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8054,10 +8054,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>133582049</v>
+        <v>133582288</v>
       </c>
       <c r="B70" t="n">
-        <v>80398</v>
+        <v>92641</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8065,21 +8065,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>484616</v>
+        <v>484904</v>
       </c>
       <c r="R70" t="n">
-        <v>7085997</v>
+        <v>7085957</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8161,32 +8161,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133582239</v>
+        <v>133582146</v>
       </c>
       <c r="B71" t="n">
-        <v>79492</v>
+        <v>80398</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>485081</v>
+        <v>485019</v>
       </c>
       <c r="R71" t="n">
-        <v>7086147</v>
+        <v>7086200</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8268,32 +8268,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133582249</v>
+        <v>133582124</v>
       </c>
       <c r="B72" t="n">
-        <v>83181</v>
+        <v>80398</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>485150</v>
+        <v>485137</v>
       </c>
       <c r="R72" t="n">
-        <v>7086053</v>
+        <v>7086195</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8375,10 +8375,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133582288</v>
+        <v>133582049</v>
       </c>
       <c r="B73" t="n">
-        <v>92641</v>
+        <v>80398</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8386,21 +8386,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>484904</v>
+        <v>484616</v>
       </c>
       <c r="R73" t="n">
-        <v>7085957</v>
+        <v>7085997</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -11508,32 +11508,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133582233</v>
+        <v>133582105</v>
       </c>
       <c r="B102" t="n">
-        <v>80438</v>
+        <v>92641</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11543,10 +11543,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>485025</v>
+        <v>485150</v>
       </c>
       <c r="R102" t="n">
-        <v>7086137</v>
+        <v>7085949</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11615,10 +11615,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133582224</v>
+        <v>133582042</v>
       </c>
       <c r="B103" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11626,21 +11626,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>484963</v>
+        <v>484762</v>
       </c>
       <c r="R103" t="n">
-        <v>7086155</v>
+        <v>7086084</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11695,7 +11695,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11722,32 +11727,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133582145</v>
+        <v>133582179</v>
       </c>
       <c r="B104" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11757,10 +11762,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485022</v>
+        <v>484623</v>
       </c>
       <c r="R104" t="n">
-        <v>7086194</v>
+        <v>7086004</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11792,7 +11797,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11802,7 +11807,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11829,7 +11834,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133582144</v>
+        <v>133582233</v>
       </c>
       <c r="B105" t="n">
         <v>80438</v>
@@ -11864,10 +11869,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>485024</v>
+        <v>485025</v>
       </c>
       <c r="R105" t="n">
-        <v>7086180</v>
+        <v>7086137</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11899,7 +11904,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11909,7 +11914,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11936,7 +11941,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133582255</v>
+        <v>133582224</v>
       </c>
       <c r="B106" t="n">
         <v>80438</v>
@@ -11971,10 +11976,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>485082</v>
+        <v>484963</v>
       </c>
       <c r="R106" t="n">
-        <v>7086082</v>
+        <v>7086155</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12006,7 +12011,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12016,7 +12021,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12043,7 +12048,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133582034</v>
+        <v>133582145</v>
       </c>
       <c r="B107" t="n">
         <v>80438</v>
@@ -12078,10 +12083,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>484996</v>
+        <v>485022</v>
       </c>
       <c r="R107" t="n">
-        <v>7086209</v>
+        <v>7086194</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12113,7 +12118,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12123,7 +12128,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12150,7 +12155,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133582195</v>
+        <v>133582144</v>
       </c>
       <c r="B108" t="n">
         <v>80438</v>
@@ -12185,10 +12190,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>484677</v>
+        <v>485024</v>
       </c>
       <c r="R108" t="n">
-        <v>7085977</v>
+        <v>7086180</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12220,7 +12225,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12230,7 +12235,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12257,7 +12262,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133582188</v>
+        <v>133582255</v>
       </c>
       <c r="B109" t="n">
         <v>80438</v>
@@ -12292,10 +12297,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>484675</v>
+        <v>485082</v>
       </c>
       <c r="R109" t="n">
-        <v>7085987</v>
+        <v>7086082</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12327,7 +12332,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12337,7 +12342,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12364,7 +12369,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133582184</v>
+        <v>133582034</v>
       </c>
       <c r="B110" t="n">
         <v>80438</v>
@@ -12399,10 +12404,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>484657</v>
+        <v>484996</v>
       </c>
       <c r="R110" t="n">
-        <v>7085984</v>
+        <v>7086209</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12434,7 +12439,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12444,7 +12449,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12471,32 +12476,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133582105</v>
+        <v>133582195</v>
       </c>
       <c r="B111" t="n">
-        <v>92641</v>
+        <v>80438</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12506,10 +12511,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>485150</v>
+        <v>484677</v>
       </c>
       <c r="R111" t="n">
-        <v>7085949</v>
+        <v>7085977</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12541,7 +12546,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12551,7 +12556,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12578,10 +12583,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133582042</v>
+        <v>133582188</v>
       </c>
       <c r="B112" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12589,21 +12594,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12613,10 +12618,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>484762</v>
+        <v>484675</v>
       </c>
       <c r="R112" t="n">
-        <v>7086084</v>
+        <v>7085987</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12648,7 +12653,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12658,12 +12663,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12690,32 +12690,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133582179</v>
+        <v>133582184</v>
       </c>
       <c r="B113" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12725,10 +12725,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>484623</v>
+        <v>484657</v>
       </c>
       <c r="R113" t="n">
-        <v>7086004</v>
+        <v>7085984</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12760,7 +12760,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13465,32 +13465,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133582230</v>
+        <v>133582075</v>
       </c>
       <c r="B120" t="n">
-        <v>80398</v>
+        <v>91918</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485000</v>
+        <v>485160</v>
       </c>
       <c r="R120" t="n">
-        <v>7086155</v>
+        <v>7086132</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13572,32 +13572,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133582205</v>
+        <v>133582116</v>
       </c>
       <c r="B121" t="n">
-        <v>80398</v>
+        <v>79492</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>484779</v>
+        <v>485168</v>
       </c>
       <c r="R121" t="n">
-        <v>7085989</v>
+        <v>7086214</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13679,32 +13679,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133582101</v>
+        <v>133582162</v>
       </c>
       <c r="B122" t="n">
-        <v>80398</v>
+        <v>79492</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>484978</v>
+        <v>484794</v>
       </c>
       <c r="R122" t="n">
-        <v>7085798</v>
+        <v>7086094</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13786,32 +13786,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133582075</v>
+        <v>133582211</v>
       </c>
       <c r="B123" t="n">
-        <v>91918</v>
+        <v>92614</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13821,10 +13821,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>485160</v>
+        <v>484833</v>
       </c>
       <c r="R123" t="n">
-        <v>7086132</v>
+        <v>7085991</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13856,7 +13856,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13893,32 +13893,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133582116</v>
+        <v>133582085</v>
       </c>
       <c r="B124" t="n">
-        <v>79492</v>
+        <v>91932</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13928,10 +13928,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485168</v>
+        <v>484920</v>
       </c>
       <c r="R124" t="n">
-        <v>7086214</v>
+        <v>7086079</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14000,10 +14000,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133582162</v>
+        <v>133582044</v>
       </c>
       <c r="B125" t="n">
-        <v>79492</v>
+        <v>92614</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14011,21 +14011,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1249</v>
+        <v>898</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14035,10 +14035,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>484794</v>
+        <v>484638</v>
       </c>
       <c r="R125" t="n">
-        <v>7086094</v>
+        <v>7086023</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14107,32 +14107,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133582211</v>
+        <v>133582133</v>
       </c>
       <c r="B126" t="n">
-        <v>92614</v>
+        <v>80473</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>898</v>
+        <v>6463</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14142,10 +14142,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>484833</v>
+        <v>485084</v>
       </c>
       <c r="R126" t="n">
-        <v>7085991</v>
+        <v>7086179</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14214,10 +14214,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133582085</v>
+        <v>133582026</v>
       </c>
       <c r="B127" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14225,21 +14225,21 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14249,10 +14249,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>484920</v>
+        <v>485057</v>
       </c>
       <c r="R127" t="n">
-        <v>7086079</v>
+        <v>7086210</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14321,32 +14321,32 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133582044</v>
+        <v>133582185</v>
       </c>
       <c r="B128" t="n">
-        <v>92614</v>
+        <v>80438</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14356,10 +14356,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>484638</v>
+        <v>484663</v>
       </c>
       <c r="R128" t="n">
-        <v>7086023</v>
+        <v>7085977</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14401,7 +14401,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14428,27 +14428,27 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133582133</v>
+        <v>133582314</v>
       </c>
       <c r="B129" t="n">
-        <v>80473</v>
+        <v>79333</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -14463,10 +14463,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>485084</v>
+        <v>485031</v>
       </c>
       <c r="R129" t="n">
-        <v>7086179</v>
+        <v>7085985</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14498,7 +14498,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14508,7 +14508,12 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14535,10 +14540,10 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133582026</v>
+        <v>133582297</v>
       </c>
       <c r="B130" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14546,21 +14551,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14570,10 +14575,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>485057</v>
+        <v>484903</v>
       </c>
       <c r="R130" t="n">
-        <v>7086210</v>
+        <v>7085866</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14605,7 +14610,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14615,7 +14620,12 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14642,32 +14652,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133582185</v>
+        <v>133582230</v>
       </c>
       <c r="B131" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14677,10 +14687,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>484663</v>
+        <v>485000</v>
       </c>
       <c r="R131" t="n">
-        <v>7085977</v>
+        <v>7086155</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14712,7 +14722,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14722,7 +14732,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14749,32 +14759,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133582314</v>
+        <v>133582205</v>
       </c>
       <c r="B132" t="n">
-        <v>79333</v>
+        <v>80398</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14784,10 +14794,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>485031</v>
+        <v>484779</v>
       </c>
       <c r="R132" t="n">
-        <v>7085985</v>
+        <v>7085989</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14819,7 +14829,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14829,12 +14839,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>21:13</t>
-        </is>
-      </c>
-      <c r="AC132" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14861,32 +14866,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133582297</v>
+        <v>133582101</v>
       </c>
       <c r="B133" t="n">
-        <v>57958</v>
+        <v>80398</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14896,10 +14901,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>484903</v>
+        <v>484978</v>
       </c>
       <c r="R133" t="n">
-        <v>7085866</v>
+        <v>7085798</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14931,7 +14936,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14941,12 +14946,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>20:49</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14973,10 +14973,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133582220</v>
+        <v>133582206</v>
       </c>
       <c r="B134" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14984,21 +14984,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>484884</v>
+        <v>484786</v>
       </c>
       <c r="R134" t="n">
-        <v>7086115</v>
+        <v>7085991</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15080,10 +15080,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133582168</v>
+        <v>133582266</v>
       </c>
       <c r="B135" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15091,21 +15091,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15115,10 +15115,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>484620</v>
+        <v>484970</v>
       </c>
       <c r="R135" t="n">
-        <v>7086031</v>
+        <v>7086056</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15150,7 +15150,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15187,7 +15187,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133582206</v>
+        <v>133582256</v>
       </c>
       <c r="B136" t="n">
         <v>80438</v>
@@ -15222,10 +15222,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>484786</v>
+        <v>485049</v>
       </c>
       <c r="R136" t="n">
-        <v>7085991</v>
+        <v>7086092</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15294,7 +15294,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133582266</v>
+        <v>133582086</v>
       </c>
       <c r="B137" t="n">
         <v>80438</v>
@@ -15329,10 +15329,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>484970</v>
+        <v>484918</v>
       </c>
       <c r="R137" t="n">
-        <v>7086056</v>
+        <v>7086067</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15401,7 +15401,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133582256</v>
+        <v>133582274</v>
       </c>
       <c r="B138" t="n">
         <v>80438</v>
@@ -15436,10 +15436,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>485049</v>
+        <v>484927</v>
       </c>
       <c r="R138" t="n">
-        <v>7086092</v>
+        <v>7086073</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15471,7 +15471,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15481,7 +15481,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15508,7 +15508,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133582086</v>
+        <v>133582073</v>
       </c>
       <c r="B139" t="n">
         <v>80438</v>
@@ -15543,10 +15543,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>484918</v>
+        <v>484980</v>
       </c>
       <c r="R139" t="n">
-        <v>7086067</v>
+        <v>7086124</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15578,7 +15578,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15588,7 +15588,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15615,10 +15620,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133582274</v>
+        <v>133582220</v>
       </c>
       <c r="B140" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15626,21 +15631,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15650,10 +15655,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>484927</v>
+        <v>484884</v>
       </c>
       <c r="R140" t="n">
-        <v>7086073</v>
+        <v>7086115</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15685,7 +15690,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15695,7 +15700,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15722,10 +15727,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133582073</v>
+        <v>133582168</v>
       </c>
       <c r="B141" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15733,21 +15738,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15757,10 +15762,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>484980</v>
+        <v>484620</v>
       </c>
       <c r="R141" t="n">
-        <v>7086124</v>
+        <v>7086031</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15792,7 +15797,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15802,12 +15807,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>18:34</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -24483,32 +24483,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>133582186</v>
+        <v>133582112</v>
       </c>
       <c r="B222" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24518,10 +24518,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>484668</v>
+        <v>485199</v>
       </c>
       <c r="R222" t="n">
-        <v>7085980</v>
+        <v>7086220</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24553,7 +24553,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24590,10 +24590,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>133582081</v>
+        <v>133582126</v>
       </c>
       <c r="B223" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24601,21 +24601,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -24625,10 +24625,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>485108</v>
+        <v>485151</v>
       </c>
       <c r="R223" t="n">
-        <v>7086096</v>
+        <v>7086178</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24660,7 +24660,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24670,7 +24670,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24697,10 +24697,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>133582053</v>
+        <v>133582215</v>
       </c>
       <c r="B224" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24708,21 +24708,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24732,10 +24732,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>484633</v>
+        <v>484868</v>
       </c>
       <c r="R224" t="n">
-        <v>7085966</v>
+        <v>7086047</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24767,7 +24767,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24777,7 +24777,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24911,10 +24911,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>133582112</v>
+        <v>133582081</v>
       </c>
       <c r="B226" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -24922,21 +24922,21 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24946,10 +24946,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>485199</v>
+        <v>485108</v>
       </c>
       <c r="R226" t="n">
-        <v>7086220</v>
+        <v>7086096</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25018,10 +25018,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>133582126</v>
+        <v>133582053</v>
       </c>
       <c r="B227" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -25029,21 +25029,21 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -25053,10 +25053,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>485151</v>
+        <v>484633</v>
       </c>
       <c r="R227" t="n">
-        <v>7086178</v>
+        <v>7085966</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25088,7 +25088,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25125,32 +25125,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>133582215</v>
+        <v>133582186</v>
       </c>
       <c r="B228" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25160,10 +25160,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>484868</v>
+        <v>484668</v>
       </c>
       <c r="R228" t="n">
-        <v>7086047</v>
+        <v>7085980</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25205,7 +25205,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD228" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -2744,10 +2744,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133582315</v>
+        <v>133582132</v>
       </c>
       <c r="B21" t="n">
-        <v>83181</v>
+        <v>80439</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2755,21 +2755,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>2081</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485148</v>
+        <v>485087</v>
       </c>
       <c r="R21" t="n">
-        <v>7086030</v>
+        <v>7086182</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,10 +2851,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133582087</v>
+        <v>133582291</v>
       </c>
       <c r="B22" t="n">
-        <v>91918</v>
+        <v>83320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2862,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>1467</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2886,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>484913</v>
+        <v>484929</v>
       </c>
       <c r="R22" t="n">
-        <v>7086067</v>
+        <v>7085958</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,7 +2921,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,32 +2958,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133582131</v>
+        <v>133582243</v>
       </c>
       <c r="B23" t="n">
-        <v>79492</v>
+        <v>80438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2993,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485094</v>
+        <v>485112</v>
       </c>
       <c r="R23" t="n">
-        <v>7086180</v>
+        <v>7086149</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3028,7 +3028,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,7 +3065,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133582259</v>
+        <v>133582315</v>
       </c>
       <c r="B24" t="n">
         <v>83181</v>
@@ -3100,10 +3100,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>485025</v>
+        <v>485148</v>
       </c>
       <c r="R24" t="n">
-        <v>7086046</v>
+        <v>7086030</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3145,7 +3145,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3172,32 +3172,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133582279</v>
+        <v>133582087</v>
       </c>
       <c r="B25" t="n">
-        <v>79492</v>
+        <v>91918</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3207,10 +3207,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>484908</v>
+        <v>484913</v>
       </c>
       <c r="R25" t="n">
-        <v>7086035</v>
+        <v>7086067</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,7 +3242,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3252,7 +3252,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3279,10 +3279,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133582182</v>
+        <v>133582258</v>
       </c>
       <c r="B26" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3290,21 +3290,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3314,10 +3314,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>484666</v>
+        <v>485063</v>
       </c>
       <c r="R26" t="n">
-        <v>7086016</v>
+        <v>7086065</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3349,7 +3349,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3359,7 +3359,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3386,32 +3386,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133582132</v>
+        <v>133582131</v>
       </c>
       <c r="B27" t="n">
-        <v>80439</v>
+        <v>79492</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3421,10 +3421,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>485087</v>
+        <v>485094</v>
       </c>
       <c r="R27" t="n">
-        <v>7086182</v>
+        <v>7086180</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3456,7 +3456,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3466,7 +3466,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3493,10 +3493,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133582291</v>
+        <v>133582259</v>
       </c>
       <c r="B28" t="n">
-        <v>83320</v>
+        <v>83181</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3504,21 +3504,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1467</v>
+        <v>1312</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3528,10 +3528,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>484929</v>
+        <v>485025</v>
       </c>
       <c r="R28" t="n">
-        <v>7085958</v>
+        <v>7086046</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3563,7 +3563,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3573,7 +3573,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3600,32 +3600,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133582228</v>
+        <v>133582279</v>
       </c>
       <c r="B29" t="n">
-        <v>80439</v>
+        <v>79492</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>484994</v>
+        <v>484908</v>
       </c>
       <c r="R29" t="n">
-        <v>7086155</v>
+        <v>7086035</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3670,7 +3670,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3707,10 +3707,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133582258</v>
+        <v>133582228</v>
       </c>
       <c r="B30" t="n">
-        <v>91932</v>
+        <v>80439</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3718,21 +3718,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3742,10 +3742,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485063</v>
+        <v>484994</v>
       </c>
       <c r="R30" t="n">
-        <v>7086065</v>
+        <v>7086155</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3777,7 +3777,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3921,7 +3921,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133582243</v>
+        <v>133582182</v>
       </c>
       <c r="B32" t="n">
         <v>80438</v>
@@ -3956,10 +3956,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>485112</v>
+        <v>484666</v>
       </c>
       <c r="R32" t="n">
-        <v>7086149</v>
+        <v>7086016</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -10005,32 +10005,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133582280</v>
+        <v>133582109</v>
       </c>
       <c r="B88" t="n">
-        <v>92641</v>
+        <v>91918</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>484906</v>
+        <v>485213</v>
       </c>
       <c r="R88" t="n">
-        <v>7086016</v>
+        <v>7086209</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10112,10 +10112,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133582109</v>
+        <v>133582082</v>
       </c>
       <c r="B89" t="n">
-        <v>91918</v>
+        <v>89300</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10123,21 +10123,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>485213</v>
+        <v>485082</v>
       </c>
       <c r="R89" t="n">
-        <v>7086209</v>
+        <v>7086105</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10219,10 +10219,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133582082</v>
+        <v>133582018</v>
       </c>
       <c r="B90" t="n">
-        <v>89300</v>
+        <v>91918</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10230,21 +10230,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>485082</v>
+        <v>485198</v>
       </c>
       <c r="R90" t="n">
-        <v>7086105</v>
+        <v>7086232</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10326,32 +10326,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133582018</v>
+        <v>133582067</v>
       </c>
       <c r="B91" t="n">
-        <v>91918</v>
+        <v>79492</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10361,10 +10361,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>485198</v>
+        <v>484880</v>
       </c>
       <c r="R91" t="n">
-        <v>7086232</v>
+        <v>7086089</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10433,32 +10433,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133582067</v>
+        <v>133582235</v>
       </c>
       <c r="B92" t="n">
-        <v>79492</v>
+        <v>80438</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>484880</v>
+        <v>485030</v>
       </c>
       <c r="R92" t="n">
-        <v>7086089</v>
+        <v>7086138</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10540,32 +10540,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133582235</v>
+        <v>133582100</v>
       </c>
       <c r="B93" t="n">
-        <v>80438</v>
+        <v>80467</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10575,10 +10575,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>485030</v>
+        <v>484979</v>
       </c>
       <c r="R93" t="n">
-        <v>7086138</v>
+        <v>7085799</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10647,32 +10647,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133582100</v>
+        <v>133582052</v>
       </c>
       <c r="B94" t="n">
-        <v>80467</v>
+        <v>80438</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10682,10 +10682,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>484979</v>
+        <v>484630</v>
       </c>
       <c r="R94" t="n">
-        <v>7085799</v>
+        <v>7085961</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10717,7 +10717,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10754,7 +10754,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133582052</v>
+        <v>133582057</v>
       </c>
       <c r="B95" t="n">
         <v>80438</v>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>484630</v>
+        <v>484692</v>
       </c>
       <c r="R95" t="n">
-        <v>7085961</v>
+        <v>7085987</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10834,7 +10834,12 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10861,7 +10866,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133582057</v>
+        <v>133582172</v>
       </c>
       <c r="B96" t="n">
         <v>80438</v>
@@ -10896,10 +10901,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>484692</v>
+        <v>484634</v>
       </c>
       <c r="R96" t="n">
-        <v>7085987</v>
+        <v>7086020</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10931,7 +10936,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10941,12 +10946,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10973,7 +10973,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133582172</v>
+        <v>133582282</v>
       </c>
       <c r="B97" t="n">
         <v>80438</v>
@@ -11008,10 +11008,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>484634</v>
+        <v>484917</v>
       </c>
       <c r="R97" t="n">
-        <v>7086020</v>
+        <v>7086029</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11080,32 +11080,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133582282</v>
+        <v>133582280</v>
       </c>
       <c r="B98" t="n">
-        <v>80438</v>
+        <v>92641</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>484917</v>
+        <v>484906</v>
       </c>
       <c r="R98" t="n">
-        <v>7086029</v>
+        <v>7086016</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13226,10 +13226,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133582153</v>
+        <v>133582227</v>
       </c>
       <c r="B118" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13237,54 +13237,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>484961</v>
+        <v>484991</v>
       </c>
       <c r="R118" t="n">
-        <v>7086205</v>
+        <v>7086162</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13316,7 +13296,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13326,12 +13306,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Trummande och födosökande</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13358,10 +13333,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133582227</v>
+        <v>133582153</v>
       </c>
       <c r="B119" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13369,34 +13344,54 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>484991</v>
+        <v>484961</v>
       </c>
       <c r="R119" t="n">
-        <v>7086162</v>
+        <v>7086205</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13428,7 +13423,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13438,7 +13433,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Trummande och födosökande</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13465,32 +13465,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133582133</v>
+        <v>133582075</v>
       </c>
       <c r="B120" t="n">
-        <v>80473</v>
+        <v>91918</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485084</v>
+        <v>485160</v>
       </c>
       <c r="R120" t="n">
-        <v>7086179</v>
+        <v>7086132</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13572,32 +13572,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133582026</v>
+        <v>133582116</v>
       </c>
       <c r="B121" t="n">
-        <v>80438</v>
+        <v>79492</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>485057</v>
+        <v>485168</v>
       </c>
       <c r="R121" t="n">
-        <v>7086210</v>
+        <v>7086214</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13679,32 +13679,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133582075</v>
+        <v>133582162</v>
       </c>
       <c r="B122" t="n">
-        <v>91918</v>
+        <v>79492</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>485160</v>
+        <v>484794</v>
       </c>
       <c r="R122" t="n">
-        <v>7086132</v>
+        <v>7086094</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13786,10 +13786,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133582116</v>
+        <v>133582211</v>
       </c>
       <c r="B123" t="n">
-        <v>79492</v>
+        <v>92614</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13797,21 +13797,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1249</v>
+        <v>898</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13821,10 +13821,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>485168</v>
+        <v>484833</v>
       </c>
       <c r="R123" t="n">
-        <v>7086214</v>
+        <v>7085991</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13856,7 +13856,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13893,32 +13893,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133582162</v>
+        <v>133582085</v>
       </c>
       <c r="B124" t="n">
-        <v>79492</v>
+        <v>91932</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13928,10 +13928,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>484794</v>
+        <v>484920</v>
       </c>
       <c r="R124" t="n">
-        <v>7086094</v>
+        <v>7086079</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14000,7 +14000,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133582211</v>
+        <v>133582044</v>
       </c>
       <c r="B125" t="n">
         <v>92614</v>
@@ -14035,10 +14035,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>484833</v>
+        <v>484638</v>
       </c>
       <c r="R125" t="n">
-        <v>7085991</v>
+        <v>7086023</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14107,32 +14107,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133582085</v>
+        <v>133582133</v>
       </c>
       <c r="B126" t="n">
-        <v>91932</v>
+        <v>80473</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14142,10 +14142,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>484920</v>
+        <v>485084</v>
       </c>
       <c r="R126" t="n">
-        <v>7086079</v>
+        <v>7086179</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14214,32 +14214,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133582044</v>
+        <v>133582026</v>
       </c>
       <c r="B127" t="n">
-        <v>92614</v>
+        <v>80438</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14249,10 +14249,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>484638</v>
+        <v>485057</v>
       </c>
       <c r="R127" t="n">
-        <v>7086023</v>
+        <v>7086210</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14973,7 +14973,7 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133582168</v>
+        <v>133582220</v>
       </c>
       <c r="B134" t="n">
         <v>91932</v>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>484620</v>
+        <v>484884</v>
       </c>
       <c r="R134" t="n">
-        <v>7086031</v>
+        <v>7086115</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15080,10 +15080,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133582206</v>
+        <v>133582168</v>
       </c>
       <c r="B135" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15091,21 +15091,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15115,10 +15115,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>484786</v>
+        <v>484620</v>
       </c>
       <c r="R135" t="n">
-        <v>7085991</v>
+        <v>7086031</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15150,7 +15150,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15160,7 +15160,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15187,7 +15187,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133582256</v>
+        <v>133582206</v>
       </c>
       <c r="B136" t="n">
         <v>80438</v>
@@ -15222,10 +15222,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>485049</v>
+        <v>484786</v>
       </c>
       <c r="R136" t="n">
-        <v>7086092</v>
+        <v>7085991</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15294,7 +15294,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133582274</v>
+        <v>133582256</v>
       </c>
       <c r="B137" t="n">
         <v>80438</v>
@@ -15329,10 +15329,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>484927</v>
+        <v>485049</v>
       </c>
       <c r="R137" t="n">
-        <v>7086073</v>
+        <v>7086092</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15401,10 +15401,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133582299</v>
+        <v>133582274</v>
       </c>
       <c r="B138" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15412,21 +15412,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15436,10 +15436,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>484915</v>
+        <v>484927</v>
       </c>
       <c r="R138" t="n">
-        <v>7085804</v>
+        <v>7086073</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15471,7 +15471,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15481,12 +15481,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15513,10 +15508,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133582266</v>
+        <v>133582299</v>
       </c>
       <c r="B139" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15524,21 +15519,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15548,10 +15543,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>484970</v>
+        <v>484915</v>
       </c>
       <c r="R139" t="n">
-        <v>7086056</v>
+        <v>7085804</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15583,7 +15578,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15593,7 +15588,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15620,7 +15620,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133582086</v>
+        <v>133582266</v>
       </c>
       <c r="B140" t="n">
         <v>80438</v>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>484918</v>
+        <v>484970</v>
       </c>
       <c r="R140" t="n">
-        <v>7086067</v>
+        <v>7086056</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15727,7 +15727,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133582073</v>
+        <v>133582086</v>
       </c>
       <c r="B141" t="n">
         <v>80438</v>
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>484980</v>
+        <v>484918</v>
       </c>
       <c r="R141" t="n">
-        <v>7086124</v>
+        <v>7086067</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15807,12 +15807,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>18:34</t>
-        </is>
-      </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15839,10 +15834,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133582221</v>
+        <v>133582073</v>
       </c>
       <c r="B142" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15850,21 +15845,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15874,10 +15869,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>484871</v>
+        <v>484980</v>
       </c>
       <c r="R142" t="n">
-        <v>7086160</v>
+        <v>7086124</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15909,7 +15904,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15919,7 +15914,12 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15946,10 +15946,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133582220</v>
+        <v>133582221</v>
       </c>
       <c r="B143" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15957,21 +15957,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15981,10 +15981,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>484884</v>
+        <v>484871</v>
       </c>
       <c r="R143" t="n">
-        <v>7086115</v>
+        <v>7086160</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16016,7 +16016,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16026,7 +16026,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16053,7 +16053,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>133582200</v>
+        <v>133582292</v>
       </c>
       <c r="B144" t="n">
         <v>80438</v>
@@ -16088,10 +16088,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>484741</v>
+        <v>484915</v>
       </c>
       <c r="R144" t="n">
-        <v>7085987</v>
+        <v>7085946</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16123,7 +16123,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16160,7 +16160,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133582103</v>
+        <v>133582201</v>
       </c>
       <c r="B145" t="n">
         <v>80438</v>
@@ -16195,10 +16195,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>485125</v>
+        <v>484739</v>
       </c>
       <c r="R145" t="n">
-        <v>7085888</v>
+        <v>7085996</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16230,7 +16230,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16267,10 +16267,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133582265</v>
+        <v>133582055</v>
       </c>
       <c r="B146" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16278,21 +16278,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16302,10 +16302,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>484982</v>
+        <v>484664</v>
       </c>
       <c r="R146" t="n">
-        <v>7086052</v>
+        <v>7085961</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16347,7 +16347,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16374,7 +16379,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133582292</v>
+        <v>133582276</v>
       </c>
       <c r="B147" t="n">
         <v>80438</v>
@@ -16409,10 +16414,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>484915</v>
+        <v>484921</v>
       </c>
       <c r="R147" t="n">
-        <v>7085946</v>
+        <v>7086057</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16444,7 +16449,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16454,7 +16459,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16481,10 +16486,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133582201</v>
+        <v>133582245</v>
       </c>
       <c r="B148" t="n">
-        <v>80438</v>
+        <v>78345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16492,21 +16497,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16516,10 +16521,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>484739</v>
+        <v>485184</v>
       </c>
       <c r="R148" t="n">
-        <v>7085996</v>
+        <v>7086083</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16551,7 +16556,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16561,7 +16566,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16588,10 +16593,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133582055</v>
+        <v>133582140</v>
       </c>
       <c r="B149" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16599,21 +16604,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16623,10 +16628,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>484664</v>
+        <v>485048</v>
       </c>
       <c r="R149" t="n">
-        <v>7085961</v>
+        <v>7086195</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16658,7 +16663,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16668,12 +16673,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16700,10 +16700,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133582276</v>
+        <v>133582069</v>
       </c>
       <c r="B150" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16711,21 +16711,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16735,10 +16735,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>484921</v>
+        <v>484935</v>
       </c>
       <c r="R150" t="n">
-        <v>7086057</v>
+        <v>7086163</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16807,7 +16807,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133582140</v>
+        <v>133582139</v>
       </c>
       <c r="B151" t="n">
         <v>91932</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>485048</v>
+        <v>485039</v>
       </c>
       <c r="R151" t="n">
-        <v>7086195</v>
+        <v>7086166</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16914,10 +16914,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133582069</v>
+        <v>133582231</v>
       </c>
       <c r="B152" t="n">
-        <v>91918</v>
+        <v>83307</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16925,21 +16925,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16949,10 +16949,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>484935</v>
+        <v>485004</v>
       </c>
       <c r="R152" t="n">
-        <v>7086163</v>
+        <v>7086161</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16984,7 +16984,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16994,7 +16994,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17021,10 +17021,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133582139</v>
+        <v>133582043</v>
       </c>
       <c r="B153" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17032,21 +17032,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17056,10 +17056,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>485039</v>
+        <v>484642</v>
       </c>
       <c r="R153" t="n">
-        <v>7086166</v>
+        <v>7086032</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17128,10 +17128,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133582231</v>
+        <v>133582272</v>
       </c>
       <c r="B154" t="n">
-        <v>83307</v>
+        <v>83181</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17139,21 +17139,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17163,10 +17163,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>485004</v>
+        <v>484952</v>
       </c>
       <c r="R154" t="n">
-        <v>7086161</v>
+        <v>7086063</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17198,7 +17198,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17235,10 +17235,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133582043</v>
+        <v>133582200</v>
       </c>
       <c r="B155" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17246,21 +17246,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17270,10 +17270,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>484642</v>
+        <v>484741</v>
       </c>
       <c r="R155" t="n">
-        <v>7086032</v>
+        <v>7085987</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17305,7 +17305,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17342,10 +17342,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133582272</v>
+        <v>133582103</v>
       </c>
       <c r="B156" t="n">
-        <v>83181</v>
+        <v>80438</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17353,21 +17353,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17377,10 +17377,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>484952</v>
+        <v>485125</v>
       </c>
       <c r="R156" t="n">
-        <v>7086063</v>
+        <v>7085888</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17449,10 +17449,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133582218</v>
+        <v>133582265</v>
       </c>
       <c r="B157" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17460,42 +17460,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>484905</v>
+        <v>484982</v>
       </c>
       <c r="R157" t="n">
-        <v>7086101</v>
+        <v>7086052</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17527,7 +17519,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17537,12 +17529,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i tajgagrantickerötad granhögstubbe</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17569,10 +17556,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133582245</v>
+        <v>133582218</v>
       </c>
       <c r="B158" t="n">
-        <v>78345</v>
+        <v>57958</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17580,34 +17567,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>485184</v>
+        <v>484905</v>
       </c>
       <c r="R158" t="n">
-        <v>7086083</v>
+        <v>7086101</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17639,7 +17634,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17649,7 +17644,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -24483,32 +24483,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>133582254</v>
+        <v>133582081</v>
       </c>
       <c r="B222" t="n">
-        <v>79492</v>
+        <v>79333</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24518,10 +24518,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>485098</v>
+        <v>485108</v>
       </c>
       <c r="R222" t="n">
-        <v>7086073</v>
+        <v>7086096</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24553,7 +24553,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24590,10 +24590,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>133582081</v>
+        <v>133582126</v>
       </c>
       <c r="B223" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -24601,21 +24601,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -24625,10 +24625,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>485108</v>
+        <v>485151</v>
       </c>
       <c r="R223" t="n">
-        <v>7086096</v>
+        <v>7086178</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24660,7 +24660,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24670,7 +24670,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24697,10 +24697,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>133582126</v>
+        <v>133582053</v>
       </c>
       <c r="B224" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -24708,21 +24708,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24732,10 +24732,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>485151</v>
+        <v>484633</v>
       </c>
       <c r="R224" t="n">
-        <v>7086178</v>
+        <v>7085966</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24767,7 +24767,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24777,7 +24777,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24804,10 +24804,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>133582053</v>
+        <v>133582215</v>
       </c>
       <c r="B225" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24815,21 +24815,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24839,10 +24839,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>484633</v>
+        <v>484868</v>
       </c>
       <c r="R225" t="n">
-        <v>7085966</v>
+        <v>7086047</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24911,32 +24911,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>133582215</v>
+        <v>133582254</v>
       </c>
       <c r="B226" t="n">
-        <v>80438</v>
+        <v>79492</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24946,10 +24946,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>484868</v>
+        <v>485098</v>
       </c>
       <c r="R226" t="n">
-        <v>7086047</v>
+        <v>7086073</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD226" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -1768,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133582177</v>
+        <v>133582078</v>
       </c>
       <c r="B12" t="n">
-        <v>80398</v>
+        <v>92641</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484640</v>
+        <v>485145</v>
       </c>
       <c r="R12" t="n">
-        <v>7085998</v>
+        <v>7086096</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133582027</v>
+        <v>133582094</v>
       </c>
       <c r="B13" t="n">
-        <v>80398</v>
+        <v>92641</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>485054</v>
+        <v>484889</v>
       </c>
       <c r="R13" t="n">
-        <v>7086211</v>
+        <v>7085970</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133582078</v>
+        <v>133582177</v>
       </c>
       <c r="B14" t="n">
-        <v>92641</v>
+        <v>80398</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485145</v>
+        <v>484640</v>
       </c>
       <c r="R14" t="n">
-        <v>7086096</v>
+        <v>7085998</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133582094</v>
+        <v>133582027</v>
       </c>
       <c r="B15" t="n">
-        <v>92641</v>
+        <v>80398</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484889</v>
+        <v>485054</v>
       </c>
       <c r="R15" t="n">
-        <v>7085970</v>
+        <v>7086211</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4380,32 +4380,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133582137</v>
+        <v>133582114</v>
       </c>
       <c r="B36" t="n">
-        <v>79492</v>
+        <v>80439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485049</v>
+        <v>485164</v>
       </c>
       <c r="R36" t="n">
-        <v>7086191</v>
+        <v>7086216</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4460,7 +4460,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4487,10 +4492,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133582102</v>
+        <v>133582155</v>
       </c>
       <c r="B37" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4498,21 +4503,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4522,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485032</v>
+        <v>484885</v>
       </c>
       <c r="R37" t="n">
-        <v>7085899</v>
+        <v>7086164</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4562,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4567,7 +4572,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4594,32 +4599,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133582278</v>
+        <v>133582268</v>
       </c>
       <c r="B38" t="n">
-        <v>79492</v>
+        <v>80438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4629,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>484899</v>
+        <v>484974</v>
       </c>
       <c r="R38" t="n">
-        <v>7086032</v>
+        <v>7086064</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,7 +4669,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4674,7 +4679,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,7 +4706,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133582091</v>
+        <v>133582198</v>
       </c>
       <c r="B39" t="n">
         <v>80438</v>
@@ -4736,10 +4741,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>484893</v>
+        <v>484719</v>
       </c>
       <c r="R39" t="n">
-        <v>7086018</v>
+        <v>7085978</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,7 +4776,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4781,7 +4786,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4808,32 +4813,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133582072</v>
+        <v>133582137</v>
       </c>
       <c r="B40" t="n">
-        <v>80438</v>
+        <v>79492</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4843,10 +4848,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>484979</v>
+        <v>485049</v>
       </c>
       <c r="R40" t="n">
-        <v>7086133</v>
+        <v>7086191</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,7 +4883,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4888,7 +4893,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,10 +4920,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133582059</v>
+        <v>133582102</v>
       </c>
       <c r="B41" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,21 +4931,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4950,10 +4955,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>484703</v>
+        <v>485032</v>
       </c>
       <c r="R41" t="n">
-        <v>7085994</v>
+        <v>7085899</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,7 +4990,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4995,7 +5000,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,32 +5027,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133582202</v>
+        <v>133582278</v>
       </c>
       <c r="B42" t="n">
-        <v>75361</v>
+        <v>79492</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229654</v>
+        <v>1249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5057,10 +5062,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484604</v>
+        <v>484899</v>
       </c>
       <c r="R42" t="n">
-        <v>7086021</v>
+        <v>7086032</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,7 +5097,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5102,12 +5107,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På en rönn, kunde enbart se två bålar med skrovellav. Varav ena hade en skrovellavsknapp växande på sig!</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5134,10 +5134,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133582114</v>
+        <v>133582091</v>
       </c>
       <c r="B43" t="n">
-        <v>80439</v>
+        <v>80438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5145,21 +5145,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>485164</v>
+        <v>484893</v>
       </c>
       <c r="R43" t="n">
-        <v>7086216</v>
+        <v>7086018</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5214,12 +5214,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5246,10 +5241,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133582155</v>
+        <v>133582072</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5257,21 +5252,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5281,10 +5276,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484885</v>
+        <v>484979</v>
       </c>
       <c r="R44" t="n">
-        <v>7086164</v>
+        <v>7086133</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5316,7 +5311,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5326,7 +5321,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5353,7 +5348,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133582268</v>
+        <v>133582059</v>
       </c>
       <c r="B45" t="n">
         <v>80438</v>
@@ -5388,10 +5383,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>484974</v>
+        <v>484703</v>
       </c>
       <c r="R45" t="n">
-        <v>7086064</v>
+        <v>7085994</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5423,7 +5418,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5433,7 +5428,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5460,32 +5455,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133582198</v>
+        <v>133582202</v>
       </c>
       <c r="B46" t="n">
-        <v>80438</v>
+        <v>75361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>229654</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5495,10 +5490,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>484719</v>
+        <v>484604</v>
       </c>
       <c r="R46" t="n">
-        <v>7085978</v>
+        <v>7086021</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,7 +5525,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5540,7 +5535,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en rönn, kunde enbart se två bålar med skrovellav. Varav ena hade en skrovellavsknapp växande på sig!</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -11294,32 +11294,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133582105</v>
+        <v>133582184</v>
       </c>
       <c r="B100" t="n">
-        <v>92641</v>
+        <v>80438</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11329,10 +11329,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>485150</v>
+        <v>484657</v>
       </c>
       <c r="R100" t="n">
-        <v>7085949</v>
+        <v>7085984</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11401,10 +11401,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133582163</v>
+        <v>133582233</v>
       </c>
       <c r="B101" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11412,21 +11412,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11436,10 +11436,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>484703</v>
+        <v>485025</v>
       </c>
       <c r="R101" t="n">
-        <v>7086043</v>
+        <v>7086137</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11508,10 +11508,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133582234</v>
+        <v>133582224</v>
       </c>
       <c r="B102" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11519,21 +11519,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11543,10 +11543,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>485009</v>
+        <v>484963</v>
       </c>
       <c r="R102" t="n">
-        <v>7086144</v>
+        <v>7086155</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11578,7 +11578,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11615,7 +11615,7 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133582184</v>
+        <v>133582145</v>
       </c>
       <c r="B103" t="n">
         <v>80438</v>
@@ -11650,10 +11650,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>484657</v>
+        <v>485022</v>
       </c>
       <c r="R103" t="n">
-        <v>7085984</v>
+        <v>7086194</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11685,7 +11685,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11695,7 +11695,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11722,7 +11722,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133582233</v>
+        <v>133582144</v>
       </c>
       <c r="B104" t="n">
         <v>80438</v>
@@ -11757,10 +11757,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485025</v>
+        <v>485024</v>
       </c>
       <c r="R104" t="n">
-        <v>7086137</v>
+        <v>7086180</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11792,7 +11792,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11802,7 +11802,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11829,7 +11829,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133582224</v>
+        <v>133582255</v>
       </c>
       <c r="B105" t="n">
         <v>80438</v>
@@ -11864,10 +11864,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>484963</v>
+        <v>485082</v>
       </c>
       <c r="R105" t="n">
-        <v>7086155</v>
+        <v>7086082</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11899,7 +11899,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11909,7 +11909,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11936,7 +11936,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133582145</v>
+        <v>133582034</v>
       </c>
       <c r="B106" t="n">
         <v>80438</v>
@@ -11971,10 +11971,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>485022</v>
+        <v>484996</v>
       </c>
       <c r="R106" t="n">
-        <v>7086194</v>
+        <v>7086209</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12006,7 +12006,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12016,7 +12016,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12043,7 +12043,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133582144</v>
+        <v>133582195</v>
       </c>
       <c r="B107" t="n">
         <v>80438</v>
@@ -12078,10 +12078,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>485024</v>
+        <v>484677</v>
       </c>
       <c r="R107" t="n">
-        <v>7086180</v>
+        <v>7085977</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12123,7 +12123,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12150,7 +12150,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133582255</v>
+        <v>133582188</v>
       </c>
       <c r="B108" t="n">
         <v>80438</v>
@@ -12185,10 +12185,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>485082</v>
+        <v>484675</v>
       </c>
       <c r="R108" t="n">
-        <v>7086082</v>
+        <v>7085987</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12220,7 +12220,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12230,7 +12230,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12257,10 +12257,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133582034</v>
+        <v>133582042</v>
       </c>
       <c r="B109" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12268,21 +12268,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12292,10 +12292,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>484996</v>
+        <v>484762</v>
       </c>
       <c r="R109" t="n">
-        <v>7086209</v>
+        <v>7086084</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12327,7 +12327,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12337,7 +12337,12 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12364,32 +12369,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133582195</v>
+        <v>133582179</v>
       </c>
       <c r="B110" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12399,10 +12404,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>484677</v>
+        <v>484623</v>
       </c>
       <c r="R110" t="n">
-        <v>7085977</v>
+        <v>7086004</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12434,7 +12439,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12444,7 +12449,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12471,32 +12476,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133582188</v>
+        <v>133582105</v>
       </c>
       <c r="B111" t="n">
-        <v>80438</v>
+        <v>92641</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12506,10 +12511,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>484675</v>
+        <v>485150</v>
       </c>
       <c r="R111" t="n">
-        <v>7085987</v>
+        <v>7085949</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12541,7 +12546,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12551,7 +12556,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12578,10 +12583,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133582042</v>
+        <v>133582163</v>
       </c>
       <c r="B112" t="n">
-        <v>57958</v>
+        <v>91932</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12589,21 +12594,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12613,10 +12618,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>484762</v>
+        <v>484703</v>
       </c>
       <c r="R112" t="n">
-        <v>7086084</v>
+        <v>7086043</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12648,7 +12653,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12658,12 +12663,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12690,32 +12690,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133582179</v>
+        <v>133582234</v>
       </c>
       <c r="B113" t="n">
-        <v>80398</v>
+        <v>91932</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12725,10 +12725,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>484623</v>
+        <v>485009</v>
       </c>
       <c r="R113" t="n">
-        <v>7086004</v>
+        <v>7086144</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12760,7 +12760,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13226,10 +13226,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133582227</v>
+        <v>133582153</v>
       </c>
       <c r="B118" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13237,34 +13237,54 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>484991</v>
+        <v>484961</v>
       </c>
       <c r="R118" t="n">
-        <v>7086162</v>
+        <v>7086205</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13296,7 +13316,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13306,7 +13326,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Trummande och födosökande</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13333,10 +13358,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133582153</v>
+        <v>133582227</v>
       </c>
       <c r="B119" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13344,54 +13369,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>484961</v>
+        <v>484991</v>
       </c>
       <c r="R119" t="n">
-        <v>7086205</v>
+        <v>7086162</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13423,7 +13428,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13433,12 +13438,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Trummande och födosökande</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13465,32 +13465,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133582075</v>
+        <v>133582133</v>
       </c>
       <c r="B120" t="n">
-        <v>91918</v>
+        <v>80473</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485160</v>
+        <v>485084</v>
       </c>
       <c r="R120" t="n">
-        <v>7086132</v>
+        <v>7086179</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13572,32 +13572,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133582116</v>
+        <v>133582026</v>
       </c>
       <c r="B121" t="n">
-        <v>79492</v>
+        <v>80438</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>485168</v>
+        <v>485057</v>
       </c>
       <c r="R121" t="n">
-        <v>7086214</v>
+        <v>7086210</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13679,32 +13679,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133582162</v>
+        <v>133582075</v>
       </c>
       <c r="B122" t="n">
-        <v>79492</v>
+        <v>91918</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>484794</v>
+        <v>485160</v>
       </c>
       <c r="R122" t="n">
-        <v>7086094</v>
+        <v>7086132</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13786,10 +13786,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133582211</v>
+        <v>133582116</v>
       </c>
       <c r="B123" t="n">
-        <v>92614</v>
+        <v>79492</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13797,21 +13797,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>898</v>
+        <v>1249</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13821,10 +13821,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>484833</v>
+        <v>485168</v>
       </c>
       <c r="R123" t="n">
-        <v>7085991</v>
+        <v>7086214</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13856,7 +13856,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13893,32 +13893,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133582085</v>
+        <v>133582162</v>
       </c>
       <c r="B124" t="n">
-        <v>91932</v>
+        <v>79492</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13928,10 +13928,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>484920</v>
+        <v>484794</v>
       </c>
       <c r="R124" t="n">
-        <v>7086079</v>
+        <v>7086094</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14000,7 +14000,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133582044</v>
+        <v>133582211</v>
       </c>
       <c r="B125" t="n">
         <v>92614</v>
@@ -14035,10 +14035,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>484638</v>
+        <v>484833</v>
       </c>
       <c r="R125" t="n">
-        <v>7086023</v>
+        <v>7085991</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14107,32 +14107,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133582133</v>
+        <v>133582085</v>
       </c>
       <c r="B126" t="n">
-        <v>80473</v>
+        <v>91932</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6463</v>
+        <v>1204</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14142,10 +14142,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>485084</v>
+        <v>484920</v>
       </c>
       <c r="R126" t="n">
-        <v>7086179</v>
+        <v>7086079</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14214,32 +14214,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133582026</v>
+        <v>133582044</v>
       </c>
       <c r="B127" t="n">
-        <v>80438</v>
+        <v>92614</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14249,10 +14249,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>485057</v>
+        <v>484638</v>
       </c>
       <c r="R127" t="n">
-        <v>7086210</v>
+        <v>7086023</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -15187,7 +15187,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133582206</v>
+        <v>133582266</v>
       </c>
       <c r="B136" t="n">
         <v>80438</v>
@@ -15222,10 +15222,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>484786</v>
+        <v>484970</v>
       </c>
       <c r="R136" t="n">
-        <v>7085991</v>
+        <v>7086056</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15294,7 +15294,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133582256</v>
+        <v>133582086</v>
       </c>
       <c r="B137" t="n">
         <v>80438</v>
@@ -15329,10 +15329,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>485049</v>
+        <v>484918</v>
       </c>
       <c r="R137" t="n">
-        <v>7086092</v>
+        <v>7086067</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15401,7 +15401,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133582274</v>
+        <v>133582073</v>
       </c>
       <c r="B138" t="n">
         <v>80438</v>
@@ -15436,10 +15436,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>484927</v>
+        <v>484980</v>
       </c>
       <c r="R138" t="n">
-        <v>7086073</v>
+        <v>7086124</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15471,7 +15471,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15481,7 +15481,12 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15508,7 +15513,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133582299</v>
+        <v>133582221</v>
       </c>
       <c r="B139" t="n">
         <v>79333</v>
@@ -15543,10 +15548,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>484915</v>
+        <v>484871</v>
       </c>
       <c r="R139" t="n">
-        <v>7085804</v>
+        <v>7086160</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15578,7 +15583,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15588,12 +15593,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15620,7 +15620,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133582266</v>
+        <v>133582206</v>
       </c>
       <c r="B140" t="n">
         <v>80438</v>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>484970</v>
+        <v>484786</v>
       </c>
       <c r="R140" t="n">
-        <v>7086056</v>
+        <v>7085991</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15727,7 +15727,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133582086</v>
+        <v>133582256</v>
       </c>
       <c r="B141" t="n">
         <v>80438</v>
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>484918</v>
+        <v>485049</v>
       </c>
       <c r="R141" t="n">
-        <v>7086067</v>
+        <v>7086092</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15834,7 +15834,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133582073</v>
+        <v>133582274</v>
       </c>
       <c r="B142" t="n">
         <v>80438</v>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>484980</v>
+        <v>484927</v>
       </c>
       <c r="R142" t="n">
-        <v>7086124</v>
+        <v>7086073</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15914,12 +15914,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>18:34</t>
-        </is>
-      </c>
-      <c r="AC142" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15946,7 +15941,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133582221</v>
+        <v>133582299</v>
       </c>
       <c r="B143" t="n">
         <v>79333</v>
@@ -15981,10 +15976,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>484871</v>
+        <v>484915</v>
       </c>
       <c r="R143" t="n">
-        <v>7086160</v>
+        <v>7085804</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16016,7 +16011,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16026,7 +16021,12 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -19072,32 +19072,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133582041</v>
+        <v>133582178</v>
       </c>
       <c r="B172" t="n">
-        <v>92641</v>
+        <v>80439</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19107,10 +19107,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>484769</v>
+        <v>484611</v>
       </c>
       <c r="R172" t="n">
-        <v>7086104</v>
+        <v>7086015</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19179,32 +19179,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133582178</v>
+        <v>133582250</v>
       </c>
       <c r="B173" t="n">
-        <v>80439</v>
+        <v>79492</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19214,10 +19214,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>484611</v>
+        <v>485142</v>
       </c>
       <c r="R173" t="n">
-        <v>7086015</v>
+        <v>7086068</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19249,7 +19249,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19259,7 +19259,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19286,32 +19286,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133582152</v>
+        <v>133582309</v>
       </c>
       <c r="B174" t="n">
-        <v>80438</v>
+        <v>79492</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19321,10 +19321,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>484963</v>
+        <v>484989</v>
       </c>
       <c r="R174" t="n">
-        <v>7086207</v>
+        <v>7086017</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19356,7 +19356,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19393,7 +19393,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133582250</v>
+        <v>133582260</v>
       </c>
       <c r="B175" t="n">
         <v>79492</v>
@@ -19428,10 +19428,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>485142</v>
+        <v>485011</v>
       </c>
       <c r="R175" t="n">
-        <v>7086068</v>
+        <v>7086077</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19500,32 +19500,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133582309</v>
+        <v>133582108</v>
       </c>
       <c r="B176" t="n">
-        <v>79492</v>
+        <v>91932</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19535,10 +19535,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>484989</v>
+        <v>485217</v>
       </c>
       <c r="R176" t="n">
-        <v>7086017</v>
+        <v>7086221</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19570,7 +19570,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19607,32 +19607,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133582260</v>
+        <v>133582084</v>
       </c>
       <c r="B177" t="n">
-        <v>79492</v>
+        <v>91932</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19642,10 +19642,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>485011</v>
+        <v>484920</v>
       </c>
       <c r="R177" t="n">
-        <v>7086077</v>
+        <v>7086083</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19714,32 +19714,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>133582108</v>
+        <v>133582242</v>
       </c>
       <c r="B178" t="n">
-        <v>91932</v>
+        <v>79492</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19749,10 +19749,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>485217</v>
+        <v>485108</v>
       </c>
       <c r="R178" t="n">
-        <v>7086221</v>
+        <v>7086152</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19821,10 +19821,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>133582084</v>
+        <v>133582152</v>
       </c>
       <c r="B179" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19832,21 +19832,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19856,10 +19856,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>484920</v>
+        <v>484963</v>
       </c>
       <c r="R179" t="n">
-        <v>7086083</v>
+        <v>7086207</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19891,7 +19891,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19928,32 +19928,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>133582242</v>
+        <v>133582095</v>
       </c>
       <c r="B180" t="n">
-        <v>79492</v>
+        <v>79333</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19963,10 +19963,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>485108</v>
+        <v>484865</v>
       </c>
       <c r="R180" t="n">
-        <v>7086152</v>
+        <v>7085963</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19998,7 +19998,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20008,7 +20008,12 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20035,7 +20040,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>133582176</v>
+        <v>133582271</v>
       </c>
       <c r="B181" t="n">
         <v>80438</v>
@@ -20070,10 +20075,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>484642</v>
+        <v>484957</v>
       </c>
       <c r="R181" t="n">
-        <v>7086007</v>
+        <v>7086063</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20105,7 +20110,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20115,7 +20120,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20142,10 +20147,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133582095</v>
+        <v>133582175</v>
       </c>
       <c r="B182" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20153,21 +20158,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20177,10 +20182,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>484865</v>
+        <v>484608</v>
       </c>
       <c r="R182" t="n">
-        <v>7085963</v>
+        <v>7085979</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20212,7 +20217,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20222,12 +20227,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>20:42</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20254,10 +20254,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133582271</v>
+        <v>133582305</v>
       </c>
       <c r="B183" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20265,21 +20265,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20289,10 +20289,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>484957</v>
+        <v>485018</v>
       </c>
       <c r="R183" t="n">
-        <v>7086063</v>
+        <v>7085907</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20324,7 +20324,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20334,7 +20334,12 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20361,7 +20366,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133582175</v>
+        <v>133582232</v>
       </c>
       <c r="B184" t="n">
         <v>80438</v>
@@ -20396,10 +20401,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>484608</v>
+        <v>485001</v>
       </c>
       <c r="R184" t="n">
-        <v>7085979</v>
+        <v>7086162</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20431,7 +20436,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20441,7 +20446,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20468,32 +20473,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133582305</v>
+        <v>133582041</v>
       </c>
       <c r="B185" t="n">
-        <v>79333</v>
+        <v>92641</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20503,10 +20508,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>485018</v>
+        <v>484769</v>
       </c>
       <c r="R185" t="n">
-        <v>7085907</v>
+        <v>7086104</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20538,7 +20543,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20548,12 +20553,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>21:03</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20580,7 +20580,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133582232</v>
+        <v>133582176</v>
       </c>
       <c r="B186" t="n">
         <v>80438</v>
@@ -20615,10 +20615,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>485001</v>
+        <v>484642</v>
       </c>
       <c r="R186" t="n">
-        <v>7086162</v>
+        <v>7086007</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20687,32 +20687,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133582263</v>
+        <v>133582300</v>
       </c>
       <c r="B187" t="n">
-        <v>79492</v>
+        <v>80473</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1249</v>
+        <v>6463</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20722,10 +20722,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>484998</v>
+        <v>484976</v>
       </c>
       <c r="R187" t="n">
-        <v>7086055</v>
+        <v>7085795</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20767,7 +20767,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20794,10 +20794,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133582066</v>
+        <v>133582225</v>
       </c>
       <c r="B188" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20805,21 +20805,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20829,10 +20829,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>484881</v>
+        <v>484969</v>
       </c>
       <c r="R188" t="n">
-        <v>7086060</v>
+        <v>7086169</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20864,7 +20864,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20901,32 +20901,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133582300</v>
+        <v>133582237</v>
       </c>
       <c r="B189" t="n">
-        <v>80473</v>
+        <v>80438</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20936,10 +20936,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>484976</v>
+        <v>485067</v>
       </c>
       <c r="R189" t="n">
-        <v>7085795</v>
+        <v>7086146</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20971,7 +20971,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20981,7 +20981,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21008,7 +21008,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133582225</v>
+        <v>133582208</v>
       </c>
       <c r="B190" t="n">
         <v>80438</v>
@@ -21043,10 +21043,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>484969</v>
+        <v>484791</v>
       </c>
       <c r="R190" t="n">
-        <v>7086169</v>
+        <v>7085988</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21115,7 +21115,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133582237</v>
+        <v>133582048</v>
       </c>
       <c r="B191" t="n">
         <v>80438</v>
@@ -21144,16 +21144,23 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>485067</v>
+        <v>484618</v>
       </c>
       <c r="R191" t="n">
-        <v>7086146</v>
+        <v>7085997</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21185,7 +21192,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21195,7 +21202,12 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21204,6 +21216,7 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
+      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -21222,10 +21235,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133582208</v>
+        <v>133582298</v>
       </c>
       <c r="B192" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21233,21 +21246,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21257,10 +21270,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>484791</v>
+        <v>484895</v>
       </c>
       <c r="R192" t="n">
-        <v>7085988</v>
+        <v>7085846</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21292,7 +21305,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21302,7 +21315,12 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>Rikligt &gt; 1000 bålar</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21329,52 +21347,45 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133582048</v>
+        <v>133582263</v>
       </c>
       <c r="B193" t="n">
-        <v>80438</v>
+        <v>79492</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>484618</v>
+        <v>484998</v>
       </c>
       <c r="R193" t="n">
-        <v>7085997</v>
+        <v>7086055</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21406,7 +21417,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21416,12 +21427,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21430,7 +21436,6 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -21449,10 +21454,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133582298</v>
+        <v>133582066</v>
       </c>
       <c r="B194" t="n">
-        <v>79333</v>
+        <v>91918</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21460,21 +21465,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21484,10 +21489,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>484895</v>
+        <v>484881</v>
       </c>
       <c r="R194" t="n">
-        <v>7085846</v>
+        <v>7086060</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21519,7 +21524,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21529,12 +21534,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>20:50</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Rikligt &gt; 1000 bålar</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -21561,10 +21561,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133582192</v>
+        <v>133582310</v>
       </c>
       <c r="B195" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21572,21 +21572,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21596,10 +21596,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>484686</v>
+        <v>484981</v>
       </c>
       <c r="R195" t="n">
-        <v>7086001</v>
+        <v>7086019</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21641,7 +21641,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21668,10 +21668,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133582240</v>
+        <v>133582076</v>
       </c>
       <c r="B196" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21679,21 +21679,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21703,10 +21703,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>485087</v>
+        <v>485222</v>
       </c>
       <c r="R196" t="n">
-        <v>7086110</v>
+        <v>7086147</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21738,7 +21738,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21748,7 +21748,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21775,10 +21775,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133582111</v>
+        <v>133582165</v>
       </c>
       <c r="B197" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21786,21 +21786,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21810,10 +21810,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>485195</v>
+        <v>484635</v>
       </c>
       <c r="R197" t="n">
-        <v>7086212</v>
+        <v>7086042</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21845,7 +21845,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21855,7 +21855,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21882,7 +21882,7 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133582141</v>
+        <v>133582192</v>
       </c>
       <c r="B198" t="n">
         <v>80438</v>
@@ -21917,10 +21917,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>485018</v>
+        <v>484686</v>
       </c>
       <c r="R198" t="n">
-        <v>7086170</v>
+        <v>7086001</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21952,7 +21952,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21962,7 +21962,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21989,7 +21989,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133582025</v>
+        <v>133582240</v>
       </c>
       <c r="B199" t="n">
         <v>80438</v>
@@ -22024,10 +22024,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>485061</v>
+        <v>485087</v>
       </c>
       <c r="R199" t="n">
-        <v>7086190</v>
+        <v>7086110</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22059,7 +22059,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22069,7 +22069,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22096,7 +22096,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133582050</v>
+        <v>133582111</v>
       </c>
       <c r="B200" t="n">
         <v>80438</v>
@@ -22125,23 +22125,16 @@
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
-      <c r="J200" t="inlineStr"/>
-      <c r="K200" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N200" t="inlineStr"/>
       <c r="P200" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>484621</v>
+        <v>485195</v>
       </c>
       <c r="R200" t="n">
-        <v>7085976</v>
+        <v>7086212</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22173,7 +22166,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22183,12 +22176,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC200" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22197,7 +22185,6 @@
       <c r="AE200" t="b">
         <v>0</v>
       </c>
-      <c r="AF200" t="inlineStr"/>
       <c r="AG200" t="b">
         <v>0</v>
       </c>
@@ -22216,7 +22203,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133582157</v>
+        <v>133582141</v>
       </c>
       <c r="B201" t="n">
         <v>80438</v>
@@ -22251,10 +22238,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>484872</v>
+        <v>485018</v>
       </c>
       <c r="R201" t="n">
-        <v>7086175</v>
+        <v>7086170</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22286,7 +22273,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22296,7 +22283,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22323,10 +22310,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>133582039</v>
+        <v>133582025</v>
       </c>
       <c r="B202" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22334,21 +22321,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22358,10 +22345,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>484820</v>
+        <v>485061</v>
       </c>
       <c r="R202" t="n">
-        <v>7086145</v>
+        <v>7086190</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22393,7 +22380,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22403,12 +22390,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22435,10 +22417,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>133582038</v>
+        <v>133582050</v>
       </c>
       <c r="B203" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22446,34 +22428,41 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
+      <c r="J203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N203" t="inlineStr"/>
       <c r="P203" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>484815</v>
+        <v>484621</v>
       </c>
       <c r="R203" t="n">
-        <v>7086160</v>
+        <v>7085976</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22505,7 +22494,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22515,12 +22504,12 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC203" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22529,6 +22518,7 @@
       <c r="AE203" t="b">
         <v>0</v>
       </c>
+      <c r="AF203" t="inlineStr"/>
       <c r="AG203" t="b">
         <v>0</v>
       </c>
@@ -22547,10 +22537,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>133582310</v>
+        <v>133582157</v>
       </c>
       <c r="B204" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22558,21 +22548,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -22582,10 +22572,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>484981</v>
+        <v>484872</v>
       </c>
       <c r="R204" t="n">
-        <v>7086019</v>
+        <v>7086175</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22617,7 +22607,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22627,7 +22617,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22654,10 +22644,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>133582076</v>
+        <v>133582039</v>
       </c>
       <c r="B205" t="n">
-        <v>91932</v>
+        <v>57958</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22665,21 +22655,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22689,10 +22679,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>485222</v>
+        <v>484820</v>
       </c>
       <c r="R205" t="n">
-        <v>7086147</v>
+        <v>7086145</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22724,7 +22714,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22734,7 +22724,12 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22761,10 +22756,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>133582165</v>
+        <v>133582038</v>
       </c>
       <c r="B206" t="n">
-        <v>91932</v>
+        <v>57958</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22772,21 +22767,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22796,10 +22791,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>484635</v>
+        <v>484815</v>
       </c>
       <c r="R206" t="n">
-        <v>7086042</v>
+        <v>7086160</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22831,7 +22826,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22841,7 +22836,12 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -22868,10 +22868,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>133582097</v>
+        <v>133582173</v>
       </c>
       <c r="B207" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22879,21 +22879,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -22903,10 +22903,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>484907</v>
+        <v>484630</v>
       </c>
       <c r="R207" t="n">
-        <v>7085829</v>
+        <v>7086019</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22938,7 +22938,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22948,12 +22948,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>20:51</t>
-        </is>
-      </c>
-      <c r="AC207" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22980,32 +22975,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>133582092</v>
+        <v>133582149</v>
       </c>
       <c r="B208" t="n">
-        <v>79333</v>
+        <v>92641</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23015,10 +23010,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>484910</v>
+        <v>484989</v>
       </c>
       <c r="R208" t="n">
-        <v>7085990</v>
+        <v>7086182</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23050,7 +23045,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23060,12 +23055,7 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>20:37</t>
-        </is>
-      </c>
-      <c r="AC208" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23092,10 +23082,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>133582051</v>
+        <v>133582252</v>
       </c>
       <c r="B209" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23103,21 +23093,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23127,10 +23117,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>484623</v>
+        <v>485119</v>
       </c>
       <c r="R209" t="n">
-        <v>7085960</v>
+        <v>7086079</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23162,7 +23152,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23172,7 +23162,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23199,32 +23189,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>133582229</v>
+        <v>133582212</v>
       </c>
       <c r="B210" t="n">
-        <v>80438</v>
+        <v>91881</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23234,10 +23224,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>484994</v>
+        <v>484829</v>
       </c>
       <c r="R210" t="n">
-        <v>7086157</v>
+        <v>7085996</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23269,7 +23259,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23279,7 +23269,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23306,10 +23296,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>133582301</v>
+        <v>133582056</v>
       </c>
       <c r="B211" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23317,21 +23307,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23341,10 +23331,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>485003</v>
+        <v>484670</v>
       </c>
       <c r="R211" t="n">
-        <v>7085818</v>
+        <v>7085973</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23376,7 +23366,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -23386,7 +23376,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23413,32 +23403,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>133582173</v>
+        <v>133582190</v>
       </c>
       <c r="B212" t="n">
-        <v>80439</v>
+        <v>79492</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23448,10 +23438,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>484630</v>
+        <v>484688</v>
       </c>
       <c r="R212" t="n">
-        <v>7086019</v>
+        <v>7085978</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23483,7 +23473,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -23493,7 +23483,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23520,32 +23510,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>133582149</v>
+        <v>133582296</v>
       </c>
       <c r="B213" t="n">
-        <v>92641</v>
+        <v>80438</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23555,10 +23545,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>484989</v>
+        <v>484845</v>
       </c>
       <c r="R213" t="n">
-        <v>7086182</v>
+        <v>7085934</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23590,7 +23580,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -23600,7 +23590,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23627,10 +23617,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>133582252</v>
+        <v>133582122</v>
       </c>
       <c r="B214" t="n">
-        <v>80439</v>
+        <v>80438</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23638,21 +23628,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23662,10 +23652,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>485119</v>
+        <v>485143</v>
       </c>
       <c r="R214" t="n">
-        <v>7086079</v>
+        <v>7086201</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23697,7 +23687,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23707,7 +23697,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23734,10 +23724,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>133582212</v>
+        <v>133582204</v>
       </c>
       <c r="B215" t="n">
-        <v>91881</v>
+        <v>80473</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23745,21 +23735,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>5447</v>
+        <v>6463</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23769,10 +23759,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>484829</v>
+        <v>484777</v>
       </c>
       <c r="R215" t="n">
-        <v>7085996</v>
+        <v>7085989</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23804,7 +23794,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23814,7 +23804,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23841,10 +23831,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>133582056</v>
+        <v>133582047</v>
       </c>
       <c r="B216" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23852,21 +23842,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -23876,10 +23866,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>484670</v>
+        <v>484606</v>
       </c>
       <c r="R216" t="n">
-        <v>7085973</v>
+        <v>7085997</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23911,7 +23901,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23921,7 +23911,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23948,32 +23938,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>133582190</v>
+        <v>133582097</v>
       </c>
       <c r="B217" t="n">
-        <v>79492</v>
+        <v>57958</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>1249</v>
+        <v>100109</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23983,10 +23973,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>484688</v>
+        <v>484907</v>
       </c>
       <c r="R217" t="n">
-        <v>7085978</v>
+        <v>7085829</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24018,7 +24008,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24028,7 +24018,12 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="AC217" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24055,10 +24050,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>133582296</v>
+        <v>133582092</v>
       </c>
       <c r="B218" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24066,21 +24061,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24090,10 +24085,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>484845</v>
+        <v>484910</v>
       </c>
       <c r="R218" t="n">
-        <v>7085934</v>
+        <v>7085990</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24125,7 +24120,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24135,7 +24130,12 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AC218" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24162,7 +24162,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>133582122</v>
+        <v>133582051</v>
       </c>
       <c r="B219" t="n">
         <v>80438</v>
@@ -24197,10 +24197,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>485143</v>
+        <v>484623</v>
       </c>
       <c r="R219" t="n">
-        <v>7086201</v>
+        <v>7085960</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24232,7 +24232,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24242,7 +24242,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24269,32 +24269,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>133582204</v>
+        <v>133582229</v>
       </c>
       <c r="B220" t="n">
-        <v>80473</v>
+        <v>80438</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24304,10 +24304,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>484777</v>
+        <v>484994</v>
       </c>
       <c r="R220" t="n">
-        <v>7085989</v>
+        <v>7086157</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24376,7 +24376,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>133582047</v>
+        <v>133582301</v>
       </c>
       <c r="B221" t="n">
         <v>80438</v>
@@ -24411,10 +24411,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>484606</v>
+        <v>485003</v>
       </c>
       <c r="R221" t="n">
-        <v>7085997</v>
+        <v>7085818</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24446,7 +24446,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24456,7 +24456,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD221" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -1768,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133582078</v>
+        <v>133582177</v>
       </c>
       <c r="B12" t="n">
-        <v>92641</v>
+        <v>80398</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1779,21 +1779,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>485145</v>
+        <v>484640</v>
       </c>
       <c r="R12" t="n">
-        <v>7086096</v>
+        <v>7085998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133582094</v>
+        <v>133582027</v>
       </c>
       <c r="B13" t="n">
-        <v>92641</v>
+        <v>80398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1886,21 +1886,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484889</v>
+        <v>485054</v>
       </c>
       <c r="R13" t="n">
-        <v>7085970</v>
+        <v>7086211</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133582177</v>
+        <v>133582078</v>
       </c>
       <c r="B14" t="n">
-        <v>80398</v>
+        <v>92641</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484640</v>
+        <v>485145</v>
       </c>
       <c r="R14" t="n">
-        <v>7085998</v>
+        <v>7086096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133582027</v>
+        <v>133582094</v>
       </c>
       <c r="B15" t="n">
-        <v>80398</v>
+        <v>92641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,21 +2100,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>485054</v>
+        <v>484889</v>
       </c>
       <c r="R15" t="n">
-        <v>7086211</v>
+        <v>7085970</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -4380,32 +4380,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133582114</v>
+        <v>133582137</v>
       </c>
       <c r="B36" t="n">
-        <v>80439</v>
+        <v>79492</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485164</v>
+        <v>485049</v>
       </c>
       <c r="R36" t="n">
-        <v>7086216</v>
+        <v>7086191</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4460,12 +4460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4492,10 +4487,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133582155</v>
+        <v>133582102</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4503,21 +4498,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4527,10 +4522,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>484885</v>
+        <v>485032</v>
       </c>
       <c r="R37" t="n">
-        <v>7086164</v>
+        <v>7085899</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4562,7 +4557,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4572,7 +4567,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4599,32 +4594,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133582268</v>
+        <v>133582278</v>
       </c>
       <c r="B38" t="n">
-        <v>80438</v>
+        <v>79492</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4634,10 +4629,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>484974</v>
+        <v>484899</v>
       </c>
       <c r="R38" t="n">
-        <v>7086064</v>
+        <v>7086032</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4669,7 +4664,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4679,7 +4674,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4706,7 +4701,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133582198</v>
+        <v>133582091</v>
       </c>
       <c r="B39" t="n">
         <v>80438</v>
@@ -4741,10 +4736,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>484719</v>
+        <v>484893</v>
       </c>
       <c r="R39" t="n">
-        <v>7085978</v>
+        <v>7086018</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4776,7 +4771,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4786,7 +4781,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4813,32 +4808,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133582137</v>
+        <v>133582072</v>
       </c>
       <c r="B40" t="n">
-        <v>79492</v>
+        <v>80438</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4848,10 +4843,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>485049</v>
+        <v>484979</v>
       </c>
       <c r="R40" t="n">
-        <v>7086191</v>
+        <v>7086133</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4883,7 +4878,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4893,7 +4888,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4920,10 +4915,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133582102</v>
+        <v>133582059</v>
       </c>
       <c r="B41" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4931,21 +4926,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4955,10 +4950,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>485032</v>
+        <v>484703</v>
       </c>
       <c r="R41" t="n">
-        <v>7085899</v>
+        <v>7085994</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4990,7 +4985,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5000,7 +4995,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5027,32 +5022,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133582278</v>
+        <v>133582202</v>
       </c>
       <c r="B42" t="n">
-        <v>79492</v>
+        <v>75361</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1249</v>
+        <v>229654</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5062,10 +5057,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484899</v>
+        <v>484604</v>
       </c>
       <c r="R42" t="n">
-        <v>7086032</v>
+        <v>7086021</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5097,7 +5092,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5107,7 +5102,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en rönn, kunde enbart se två bålar med skrovellav. Varav ena hade en skrovellavsknapp växande på sig!</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5134,10 +5134,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133582091</v>
+        <v>133582114</v>
       </c>
       <c r="B43" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5145,21 +5145,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>484893</v>
+        <v>485164</v>
       </c>
       <c r="R43" t="n">
-        <v>7086018</v>
+        <v>7086216</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5214,7 +5214,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5241,10 +5246,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133582072</v>
+        <v>133582155</v>
       </c>
       <c r="B44" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5252,21 +5257,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5276,10 +5281,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484979</v>
+        <v>484885</v>
       </c>
       <c r="R44" t="n">
-        <v>7086133</v>
+        <v>7086164</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5311,7 +5316,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5321,7 +5326,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5348,7 +5353,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133582059</v>
+        <v>133582268</v>
       </c>
       <c r="B45" t="n">
         <v>80438</v>
@@ -5383,10 +5388,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>484703</v>
+        <v>484974</v>
       </c>
       <c r="R45" t="n">
-        <v>7085994</v>
+        <v>7086064</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5418,7 +5423,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5428,7 +5433,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5455,32 +5460,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133582202</v>
+        <v>133582198</v>
       </c>
       <c r="B46" t="n">
-        <v>75361</v>
+        <v>80438</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229654</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5490,10 +5495,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>484604</v>
+        <v>484719</v>
       </c>
       <c r="R46" t="n">
-        <v>7086021</v>
+        <v>7085978</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5525,7 +5530,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5535,12 +5540,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På en rönn, kunde enbart se två bålar med skrovellav. Varav ena hade en skrovellavsknapp växande på sig!</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -10005,32 +10005,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133582109</v>
+        <v>133582280</v>
       </c>
       <c r="B88" t="n">
-        <v>91918</v>
+        <v>92641</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>485213</v>
+        <v>484906</v>
       </c>
       <c r="R88" t="n">
-        <v>7086209</v>
+        <v>7086016</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10112,10 +10112,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133582082</v>
+        <v>133582109</v>
       </c>
       <c r="B89" t="n">
-        <v>89300</v>
+        <v>91918</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10123,21 +10123,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>485082</v>
+        <v>485213</v>
       </c>
       <c r="R89" t="n">
-        <v>7086105</v>
+        <v>7086209</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10219,10 +10219,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133582018</v>
+        <v>133582082</v>
       </c>
       <c r="B90" t="n">
-        <v>91918</v>
+        <v>89300</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10230,21 +10230,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>485198</v>
+        <v>485082</v>
       </c>
       <c r="R90" t="n">
-        <v>7086232</v>
+        <v>7086105</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10326,32 +10326,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133582067</v>
+        <v>133582018</v>
       </c>
       <c r="B91" t="n">
-        <v>79492</v>
+        <v>91918</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10361,10 +10361,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>484880</v>
+        <v>485198</v>
       </c>
       <c r="R91" t="n">
-        <v>7086089</v>
+        <v>7086232</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10433,32 +10433,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133582235</v>
+        <v>133582067</v>
       </c>
       <c r="B92" t="n">
-        <v>80438</v>
+        <v>79492</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>485030</v>
+        <v>484880</v>
       </c>
       <c r="R92" t="n">
-        <v>7086138</v>
+        <v>7086089</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10540,32 +10540,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133582100</v>
+        <v>133582235</v>
       </c>
       <c r="B93" t="n">
-        <v>80467</v>
+        <v>80438</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10575,10 +10575,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>484979</v>
+        <v>485030</v>
       </c>
       <c r="R93" t="n">
-        <v>7085799</v>
+        <v>7086138</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10647,32 +10647,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133582052</v>
+        <v>133582100</v>
       </c>
       <c r="B94" t="n">
-        <v>80438</v>
+        <v>80467</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10682,10 +10682,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>484630</v>
+        <v>484979</v>
       </c>
       <c r="R94" t="n">
-        <v>7085961</v>
+        <v>7085799</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10717,7 +10717,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10727,7 +10727,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10754,7 +10754,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133582057</v>
+        <v>133582052</v>
       </c>
       <c r="B95" t="n">
         <v>80438</v>
@@ -10789,10 +10789,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>484692</v>
+        <v>484630</v>
       </c>
       <c r="R95" t="n">
-        <v>7085987</v>
+        <v>7085961</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10824,7 +10824,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10834,12 +10834,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10866,7 +10861,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133582172</v>
+        <v>133582057</v>
       </c>
       <c r="B96" t="n">
         <v>80438</v>
@@ -10901,10 +10896,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>484634</v>
+        <v>484692</v>
       </c>
       <c r="R96" t="n">
-        <v>7086020</v>
+        <v>7085987</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10936,7 +10931,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10946,7 +10941,12 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10973,7 +10973,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133582282</v>
+        <v>133582172</v>
       </c>
       <c r="B97" t="n">
         <v>80438</v>
@@ -11008,10 +11008,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>484917</v>
+        <v>484634</v>
       </c>
       <c r="R97" t="n">
-        <v>7086029</v>
+        <v>7086020</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11080,32 +11080,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133582280</v>
+        <v>133582282</v>
       </c>
       <c r="B98" t="n">
-        <v>92641</v>
+        <v>80438</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>484906</v>
+        <v>484917</v>
       </c>
       <c r="R98" t="n">
-        <v>7086016</v>
+        <v>7086029</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13226,10 +13226,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133582153</v>
+        <v>133582227</v>
       </c>
       <c r="B118" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13237,54 +13237,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>484961</v>
+        <v>484991</v>
       </c>
       <c r="R118" t="n">
-        <v>7086205</v>
+        <v>7086162</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13316,7 +13296,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13326,12 +13306,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Trummande och födosökande</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13358,10 +13333,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133582227</v>
+        <v>133582153</v>
       </c>
       <c r="B119" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13369,34 +13344,54 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>484991</v>
+        <v>484961</v>
       </c>
       <c r="R119" t="n">
-        <v>7086162</v>
+        <v>7086205</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13428,7 +13423,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13438,7 +13433,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Trummande och födosökande</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13465,32 +13465,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133582133</v>
+        <v>133582075</v>
       </c>
       <c r="B120" t="n">
-        <v>80473</v>
+        <v>91918</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485084</v>
+        <v>485160</v>
       </c>
       <c r="R120" t="n">
-        <v>7086179</v>
+        <v>7086132</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13572,32 +13572,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133582026</v>
+        <v>133582116</v>
       </c>
       <c r="B121" t="n">
-        <v>80438</v>
+        <v>79492</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>485057</v>
+        <v>485168</v>
       </c>
       <c r="R121" t="n">
-        <v>7086210</v>
+        <v>7086214</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13679,32 +13679,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133582075</v>
+        <v>133582162</v>
       </c>
       <c r="B122" t="n">
-        <v>91918</v>
+        <v>79492</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>485160</v>
+        <v>484794</v>
       </c>
       <c r="R122" t="n">
-        <v>7086132</v>
+        <v>7086094</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13786,10 +13786,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133582116</v>
+        <v>133582211</v>
       </c>
       <c r="B123" t="n">
-        <v>79492</v>
+        <v>92614</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13797,21 +13797,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1249</v>
+        <v>898</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13821,10 +13821,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>485168</v>
+        <v>484833</v>
       </c>
       <c r="R123" t="n">
-        <v>7086214</v>
+        <v>7085991</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13856,7 +13856,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13866,7 +13866,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13893,32 +13893,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133582162</v>
+        <v>133582085</v>
       </c>
       <c r="B124" t="n">
-        <v>79492</v>
+        <v>91932</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13928,10 +13928,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>484794</v>
+        <v>484920</v>
       </c>
       <c r="R124" t="n">
-        <v>7086094</v>
+        <v>7086079</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13963,7 +13963,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14000,7 +14000,7 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133582211</v>
+        <v>133582044</v>
       </c>
       <c r="B125" t="n">
         <v>92614</v>
@@ -14035,10 +14035,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>484833</v>
+        <v>484638</v>
       </c>
       <c r="R125" t="n">
-        <v>7085991</v>
+        <v>7086023</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14107,32 +14107,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133582085</v>
+        <v>133582133</v>
       </c>
       <c r="B126" t="n">
-        <v>91932</v>
+        <v>80473</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1204</v>
+        <v>6463</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14142,10 +14142,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>484920</v>
+        <v>485084</v>
       </c>
       <c r="R126" t="n">
-        <v>7086079</v>
+        <v>7086179</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14177,7 +14177,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14187,7 +14187,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14214,32 +14214,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133582044</v>
+        <v>133582026</v>
       </c>
       <c r="B127" t="n">
-        <v>92614</v>
+        <v>80438</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14249,10 +14249,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>484638</v>
+        <v>485057</v>
       </c>
       <c r="R127" t="n">
-        <v>7086023</v>
+        <v>7086210</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14284,7 +14284,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -16053,7 +16053,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>133582292</v>
+        <v>133582200</v>
       </c>
       <c r="B144" t="n">
         <v>80438</v>
@@ -16088,10 +16088,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>484915</v>
+        <v>484741</v>
       </c>
       <c r="R144" t="n">
-        <v>7085946</v>
+        <v>7085987</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16123,7 +16123,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16160,7 +16160,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133582201</v>
+        <v>133582103</v>
       </c>
       <c r="B145" t="n">
         <v>80438</v>
@@ -16195,10 +16195,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>484739</v>
+        <v>485125</v>
       </c>
       <c r="R145" t="n">
-        <v>7085996</v>
+        <v>7085888</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16230,7 +16230,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16267,10 +16267,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133582055</v>
+        <v>133582265</v>
       </c>
       <c r="B146" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16278,21 +16278,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16302,10 +16302,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>484664</v>
+        <v>484982</v>
       </c>
       <c r="R146" t="n">
-        <v>7085961</v>
+        <v>7086052</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16347,12 +16347,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16379,7 +16374,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133582276</v>
+        <v>133582292</v>
       </c>
       <c r="B147" t="n">
         <v>80438</v>
@@ -16414,10 +16409,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>484921</v>
+        <v>484915</v>
       </c>
       <c r="R147" t="n">
-        <v>7086057</v>
+        <v>7085946</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16449,7 +16444,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16459,7 +16454,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16486,10 +16481,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133582245</v>
+        <v>133582201</v>
       </c>
       <c r="B148" t="n">
-        <v>78345</v>
+        <v>80438</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16497,21 +16492,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16521,10 +16516,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>485184</v>
+        <v>484739</v>
       </c>
       <c r="R148" t="n">
-        <v>7086083</v>
+        <v>7085996</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16556,7 +16551,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16566,7 +16561,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16593,10 +16588,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133582140</v>
+        <v>133582055</v>
       </c>
       <c r="B149" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16604,21 +16599,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16628,10 +16623,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>485048</v>
+        <v>484664</v>
       </c>
       <c r="R149" t="n">
-        <v>7086195</v>
+        <v>7085961</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16663,7 +16658,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16673,7 +16668,12 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16700,10 +16700,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133582069</v>
+        <v>133582276</v>
       </c>
       <c r="B150" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16711,21 +16711,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16735,10 +16735,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>484935</v>
+        <v>484921</v>
       </c>
       <c r="R150" t="n">
-        <v>7086163</v>
+        <v>7086057</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16807,7 +16807,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133582139</v>
+        <v>133582140</v>
       </c>
       <c r="B151" t="n">
         <v>91932</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>485039</v>
+        <v>485048</v>
       </c>
       <c r="R151" t="n">
-        <v>7086166</v>
+        <v>7086195</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16914,10 +16914,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133582231</v>
+        <v>133582069</v>
       </c>
       <c r="B152" t="n">
-        <v>83307</v>
+        <v>91918</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16925,21 +16925,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16949,10 +16949,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>485004</v>
+        <v>484935</v>
       </c>
       <c r="R152" t="n">
-        <v>7086161</v>
+        <v>7086163</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16984,7 +16984,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16994,7 +16994,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17021,10 +17021,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133582043</v>
+        <v>133582139</v>
       </c>
       <c r="B153" t="n">
-        <v>91918</v>
+        <v>91932</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17032,21 +17032,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17056,10 +17056,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>484642</v>
+        <v>485039</v>
       </c>
       <c r="R153" t="n">
-        <v>7086032</v>
+        <v>7086166</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17128,10 +17128,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133582272</v>
+        <v>133582231</v>
       </c>
       <c r="B154" t="n">
-        <v>83181</v>
+        <v>83307</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17139,21 +17139,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>1312</v>
+        <v>308</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17163,10 +17163,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>484952</v>
+        <v>485004</v>
       </c>
       <c r="R154" t="n">
-        <v>7086063</v>
+        <v>7086161</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17198,7 +17198,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17235,10 +17235,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133582200</v>
+        <v>133582043</v>
       </c>
       <c r="B155" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17246,21 +17246,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17270,10 +17270,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>484741</v>
+        <v>484642</v>
       </c>
       <c r="R155" t="n">
-        <v>7085987</v>
+        <v>7086032</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17305,7 +17305,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17342,10 +17342,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133582103</v>
+        <v>133582272</v>
       </c>
       <c r="B156" t="n">
-        <v>80438</v>
+        <v>83181</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17353,21 +17353,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17377,10 +17377,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>485125</v>
+        <v>484952</v>
       </c>
       <c r="R156" t="n">
-        <v>7085888</v>
+        <v>7086063</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17449,10 +17449,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133582265</v>
+        <v>133582218</v>
       </c>
       <c r="B157" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17460,34 +17460,42 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>484982</v>
+        <v>484905</v>
       </c>
       <c r="R157" t="n">
-        <v>7086052</v>
+        <v>7086101</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17519,7 +17527,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17529,7 +17537,12 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17556,10 +17569,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133582218</v>
+        <v>133582245</v>
       </c>
       <c r="B158" t="n">
-        <v>57958</v>
+        <v>78345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17567,42 +17580,34 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>100109</v>
+        <v>228579</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>484905</v>
+        <v>485184</v>
       </c>
       <c r="R158" t="n">
-        <v>7086101</v>
+        <v>7086083</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17634,7 +17639,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17644,12 +17649,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i tajgagrantickerötad granhögstubbe</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18216,7 +18216,7 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>133582257</v>
+        <v>133582196</v>
       </c>
       <c r="B164" t="n">
         <v>80438</v>
@@ -18251,10 +18251,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>485063</v>
+        <v>484701</v>
       </c>
       <c r="R164" t="n">
-        <v>7086069</v>
+        <v>7085982</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18323,10 +18323,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133582119</v>
+        <v>133582160</v>
       </c>
       <c r="B165" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18334,21 +18334,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18358,10 +18358,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>485161</v>
+        <v>484827</v>
       </c>
       <c r="R165" t="n">
-        <v>7086201</v>
+        <v>7086151</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18393,7 +18393,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18430,32 +18430,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133582311</v>
+        <v>133582135</v>
       </c>
       <c r="B166" t="n">
-        <v>91932</v>
+        <v>80398</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1204</v>
+        <v>229497</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18465,10 +18465,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>484937</v>
+        <v>485056</v>
       </c>
       <c r="R166" t="n">
-        <v>7086009</v>
+        <v>7086182</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18751,7 +18751,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133582196</v>
+        <v>133582257</v>
       </c>
       <c r="B169" t="n">
         <v>80438</v>
@@ -18786,10 +18786,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>484701</v>
+        <v>485063</v>
       </c>
       <c r="R169" t="n">
-        <v>7085982</v>
+        <v>7086069</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18858,10 +18858,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133582160</v>
+        <v>133582119</v>
       </c>
       <c r="B170" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18869,21 +18869,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18893,10 +18893,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>484827</v>
+        <v>485161</v>
       </c>
       <c r="R170" t="n">
-        <v>7086151</v>
+        <v>7086201</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18965,32 +18965,32 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133582135</v>
+        <v>133582311</v>
       </c>
       <c r="B171" t="n">
-        <v>80398</v>
+        <v>91932</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19000,10 +19000,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>485056</v>
+        <v>484937</v>
       </c>
       <c r="R171" t="n">
-        <v>7086182</v>
+        <v>7086009</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19045,7 +19045,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19072,32 +19072,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133582178</v>
+        <v>133582041</v>
       </c>
       <c r="B172" t="n">
-        <v>80439</v>
+        <v>92641</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2081</v>
+        <v>3298</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19107,10 +19107,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>484611</v>
+        <v>484769</v>
       </c>
       <c r="R172" t="n">
-        <v>7086015</v>
+        <v>7086104</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19179,32 +19179,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133582250</v>
+        <v>133582178</v>
       </c>
       <c r="B173" t="n">
-        <v>79492</v>
+        <v>80439</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19214,10 +19214,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>485142</v>
+        <v>484611</v>
       </c>
       <c r="R173" t="n">
-        <v>7086068</v>
+        <v>7086015</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19249,7 +19249,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19259,7 +19259,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19286,32 +19286,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133582309</v>
+        <v>133582152</v>
       </c>
       <c r="B174" t="n">
-        <v>79492</v>
+        <v>80438</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19321,10 +19321,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>484989</v>
+        <v>484963</v>
       </c>
       <c r="R174" t="n">
-        <v>7086017</v>
+        <v>7086207</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19356,7 +19356,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19393,7 +19393,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133582260</v>
+        <v>133582250</v>
       </c>
       <c r="B175" t="n">
         <v>79492</v>
@@ -19428,10 +19428,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>485011</v>
+        <v>485142</v>
       </c>
       <c r="R175" t="n">
-        <v>7086077</v>
+        <v>7086068</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19500,32 +19500,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133582108</v>
+        <v>133582309</v>
       </c>
       <c r="B176" t="n">
-        <v>91932</v>
+        <v>79492</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19535,10 +19535,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>485217</v>
+        <v>484989</v>
       </c>
       <c r="R176" t="n">
-        <v>7086221</v>
+        <v>7086017</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19570,7 +19570,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19607,32 +19607,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133582084</v>
+        <v>133582260</v>
       </c>
       <c r="B177" t="n">
-        <v>91932</v>
+        <v>79492</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19642,10 +19642,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>484920</v>
+        <v>485011</v>
       </c>
       <c r="R177" t="n">
-        <v>7086083</v>
+        <v>7086077</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19714,32 +19714,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>133582242</v>
+        <v>133582108</v>
       </c>
       <c r="B178" t="n">
-        <v>79492</v>
+        <v>91932</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19749,10 +19749,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>485108</v>
+        <v>485217</v>
       </c>
       <c r="R178" t="n">
-        <v>7086152</v>
+        <v>7086221</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19821,10 +19821,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>133582152</v>
+        <v>133582084</v>
       </c>
       <c r="B179" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19832,21 +19832,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19856,10 +19856,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>484963</v>
+        <v>484920</v>
       </c>
       <c r="R179" t="n">
-        <v>7086207</v>
+        <v>7086083</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19891,7 +19891,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19928,32 +19928,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>133582095</v>
+        <v>133582242</v>
       </c>
       <c r="B180" t="n">
-        <v>79333</v>
+        <v>79492</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19963,10 +19963,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>484865</v>
+        <v>485108</v>
       </c>
       <c r="R180" t="n">
-        <v>7085963</v>
+        <v>7086152</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19998,7 +19998,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20008,12 +20008,7 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>20:42</t>
-        </is>
-      </c>
-      <c r="AC180" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20040,7 +20035,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>133582271</v>
+        <v>133582176</v>
       </c>
       <c r="B181" t="n">
         <v>80438</v>
@@ -20075,10 +20070,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>484957</v>
+        <v>484642</v>
       </c>
       <c r="R181" t="n">
-        <v>7086063</v>
+        <v>7086007</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20110,7 +20105,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20120,7 +20115,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20147,10 +20142,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133582175</v>
+        <v>133582095</v>
       </c>
       <c r="B182" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20158,21 +20153,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20182,10 +20177,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>484608</v>
+        <v>484865</v>
       </c>
       <c r="R182" t="n">
-        <v>7085979</v>
+        <v>7085963</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20217,7 +20212,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20227,7 +20222,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20254,10 +20254,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133582305</v>
+        <v>133582271</v>
       </c>
       <c r="B183" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20265,21 +20265,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20289,10 +20289,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>485018</v>
+        <v>484957</v>
       </c>
       <c r="R183" t="n">
-        <v>7085907</v>
+        <v>7086063</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20324,7 +20324,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20334,12 +20334,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>21:03</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20366,7 +20361,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133582232</v>
+        <v>133582175</v>
       </c>
       <c r="B184" t="n">
         <v>80438</v>
@@ -20401,10 +20396,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>485001</v>
+        <v>484608</v>
       </c>
       <c r="R184" t="n">
-        <v>7086162</v>
+        <v>7085979</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20436,7 +20431,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20446,7 +20441,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20473,32 +20468,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133582041</v>
+        <v>133582305</v>
       </c>
       <c r="B185" t="n">
-        <v>92641</v>
+        <v>79333</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20508,10 +20503,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>484769</v>
+        <v>485018</v>
       </c>
       <c r="R185" t="n">
-        <v>7086104</v>
+        <v>7085907</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20543,7 +20538,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20553,7 +20548,12 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20580,7 +20580,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133582176</v>
+        <v>133582232</v>
       </c>
       <c r="B186" t="n">
         <v>80438</v>
@@ -20615,10 +20615,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>484642</v>
+        <v>485001</v>
       </c>
       <c r="R186" t="n">
-        <v>7086007</v>
+        <v>7086162</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -22868,10 +22868,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>133582173</v>
+        <v>133582097</v>
       </c>
       <c r="B207" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22879,21 +22879,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -22903,10 +22903,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>484630</v>
+        <v>484907</v>
       </c>
       <c r="R207" t="n">
-        <v>7086019</v>
+        <v>7085829</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22938,7 +22938,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22948,7 +22948,12 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="AC207" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22975,32 +22980,32 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>133582149</v>
+        <v>133582092</v>
       </c>
       <c r="B208" t="n">
-        <v>92641</v>
+        <v>79333</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>3298</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23010,10 +23015,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>484989</v>
+        <v>484910</v>
       </c>
       <c r="R208" t="n">
-        <v>7086182</v>
+        <v>7085990</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23045,7 +23050,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23055,7 +23060,12 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23082,10 +23092,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>133582252</v>
+        <v>133582051</v>
       </c>
       <c r="B209" t="n">
-        <v>80439</v>
+        <v>80438</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23093,21 +23103,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23117,10 +23127,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>485119</v>
+        <v>484623</v>
       </c>
       <c r="R209" t="n">
-        <v>7086079</v>
+        <v>7085960</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23152,7 +23162,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23162,7 +23172,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23189,32 +23199,32 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>133582212</v>
+        <v>133582229</v>
       </c>
       <c r="B210" t="n">
-        <v>91881</v>
+        <v>80438</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23224,10 +23234,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>484829</v>
+        <v>484994</v>
       </c>
       <c r="R210" t="n">
-        <v>7085996</v>
+        <v>7086157</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23259,7 +23269,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23269,7 +23279,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23296,10 +23306,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>133582056</v>
+        <v>133582301</v>
       </c>
       <c r="B211" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23307,21 +23317,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23331,10 +23341,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>484670</v>
+        <v>485003</v>
       </c>
       <c r="R211" t="n">
-        <v>7085973</v>
+        <v>7085818</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23366,7 +23376,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -23376,7 +23386,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23403,32 +23413,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>133582190</v>
+        <v>133582173</v>
       </c>
       <c r="B212" t="n">
-        <v>79492</v>
+        <v>80439</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23438,10 +23448,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>484688</v>
+        <v>484630</v>
       </c>
       <c r="R212" t="n">
-        <v>7085978</v>
+        <v>7086019</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23473,7 +23483,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -23483,7 +23493,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23510,32 +23520,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>133582296</v>
+        <v>133582149</v>
       </c>
       <c r="B213" t="n">
-        <v>80438</v>
+        <v>92641</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23545,10 +23555,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>484845</v>
+        <v>484989</v>
       </c>
       <c r="R213" t="n">
-        <v>7085934</v>
+        <v>7086182</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23580,7 +23590,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -23590,7 +23600,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23617,10 +23627,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>133582122</v>
+        <v>133582252</v>
       </c>
       <c r="B214" t="n">
-        <v>80438</v>
+        <v>80439</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23628,21 +23638,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23652,10 +23662,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>485143</v>
+        <v>485119</v>
       </c>
       <c r="R214" t="n">
-        <v>7086201</v>
+        <v>7086079</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23687,7 +23697,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23697,7 +23707,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23724,10 +23734,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>133582204</v>
+        <v>133582212</v>
       </c>
       <c r="B215" t="n">
-        <v>80473</v>
+        <v>91881</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23735,21 +23745,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6463</v>
+        <v>5447</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23759,10 +23769,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>484777</v>
+        <v>484829</v>
       </c>
       <c r="R215" t="n">
-        <v>7085989</v>
+        <v>7085996</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23794,7 +23804,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23804,7 +23814,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23831,10 +23841,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>133582047</v>
+        <v>133582056</v>
       </c>
       <c r="B216" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23842,21 +23852,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -23866,10 +23876,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>484606</v>
+        <v>484670</v>
       </c>
       <c r="R216" t="n">
-        <v>7085997</v>
+        <v>7085973</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23901,7 +23911,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23911,7 +23921,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23938,32 +23948,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>133582097</v>
+        <v>133582190</v>
       </c>
       <c r="B217" t="n">
-        <v>57958</v>
+        <v>79492</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23973,10 +23983,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>484907</v>
+        <v>484688</v>
       </c>
       <c r="R217" t="n">
-        <v>7085829</v>
+        <v>7085978</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24008,7 +24018,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24018,12 +24028,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>20:51</t>
-        </is>
-      </c>
-      <c r="AC217" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24050,10 +24055,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>133582092</v>
+        <v>133582296</v>
       </c>
       <c r="B218" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -24061,21 +24066,21 @@
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24085,10 +24090,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>484910</v>
+        <v>484845</v>
       </c>
       <c r="R218" t="n">
-        <v>7085990</v>
+        <v>7085934</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24120,7 +24125,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24130,12 +24135,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>20:37</t>
-        </is>
-      </c>
-      <c r="AC218" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24162,7 +24162,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>133582051</v>
+        <v>133582122</v>
       </c>
       <c r="B219" t="n">
         <v>80438</v>
@@ -24197,10 +24197,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>484623</v>
+        <v>485143</v>
       </c>
       <c r="R219" t="n">
-        <v>7085960</v>
+        <v>7086201</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24232,7 +24232,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24242,7 +24242,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24269,32 +24269,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>133582229</v>
+        <v>133582204</v>
       </c>
       <c r="B220" t="n">
-        <v>80438</v>
+        <v>80473</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24304,10 +24304,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>484994</v>
+        <v>484777</v>
       </c>
       <c r="R220" t="n">
-        <v>7086157</v>
+        <v>7085989</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24339,7 +24339,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -24349,7 +24349,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24376,7 +24376,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>133582301</v>
+        <v>133582047</v>
       </c>
       <c r="B221" t="n">
         <v>80438</v>
@@ -24411,10 +24411,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>485003</v>
+        <v>484606</v>
       </c>
       <c r="R221" t="n">
-        <v>7085818</v>
+        <v>7085997</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24446,7 +24446,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24456,7 +24456,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD221" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -4380,32 +4380,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>133582137</v>
+        <v>133582114</v>
       </c>
       <c r="B36" t="n">
-        <v>79492</v>
+        <v>80439</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1249</v>
+        <v>2081</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4415,10 +4415,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>485049</v>
+        <v>485164</v>
       </c>
       <c r="R36" t="n">
-        <v>7086191</v>
+        <v>7086216</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4450,7 +4450,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4460,7 +4460,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4487,10 +4492,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133582102</v>
+        <v>133582155</v>
       </c>
       <c r="B37" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4498,21 +4503,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4522,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485032</v>
+        <v>484885</v>
       </c>
       <c r="R37" t="n">
-        <v>7085899</v>
+        <v>7086164</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4557,7 +4562,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4567,7 +4572,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4594,32 +4599,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133582278</v>
+        <v>133582268</v>
       </c>
       <c r="B38" t="n">
-        <v>79492</v>
+        <v>80438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4629,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>484899</v>
+        <v>484974</v>
       </c>
       <c r="R38" t="n">
-        <v>7086032</v>
+        <v>7086064</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4664,7 +4669,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4674,7 +4679,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4701,7 +4706,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133582091</v>
+        <v>133582198</v>
       </c>
       <c r="B39" t="n">
         <v>80438</v>
@@ -4736,10 +4741,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>484893</v>
+        <v>484719</v>
       </c>
       <c r="R39" t="n">
-        <v>7086018</v>
+        <v>7085978</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4771,7 +4776,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4781,7 +4786,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4808,32 +4813,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133582072</v>
+        <v>133582137</v>
       </c>
       <c r="B40" t="n">
-        <v>80438</v>
+        <v>79492</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4843,10 +4848,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>484979</v>
+        <v>485049</v>
       </c>
       <c r="R40" t="n">
-        <v>7086133</v>
+        <v>7086191</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4878,7 +4883,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4888,7 +4893,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4915,10 +4920,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133582059</v>
+        <v>133582102</v>
       </c>
       <c r="B41" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4926,21 +4931,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4950,10 +4955,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>484703</v>
+        <v>485032</v>
       </c>
       <c r="R41" t="n">
-        <v>7085994</v>
+        <v>7085899</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4985,7 +4990,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4995,7 +5000,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5022,32 +5027,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133582202</v>
+        <v>133582278</v>
       </c>
       <c r="B42" t="n">
-        <v>75361</v>
+        <v>79492</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>229654</v>
+        <v>1249</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5057,10 +5062,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484604</v>
+        <v>484899</v>
       </c>
       <c r="R42" t="n">
-        <v>7086021</v>
+        <v>7086032</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5092,7 +5097,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5102,12 +5107,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På en rönn, kunde enbart se två bålar med skrovellav. Varav ena hade en skrovellavsknapp växande på sig!</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5134,10 +5134,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133582114</v>
+        <v>133582091</v>
       </c>
       <c r="B43" t="n">
-        <v>80439</v>
+        <v>80438</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5145,21 +5145,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5169,10 +5169,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>485164</v>
+        <v>484893</v>
       </c>
       <c r="R43" t="n">
-        <v>7086216</v>
+        <v>7086018</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5214,12 +5214,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5246,10 +5241,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133582155</v>
+        <v>133582072</v>
       </c>
       <c r="B44" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5257,21 +5252,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5281,10 +5276,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484885</v>
+        <v>484979</v>
       </c>
       <c r="R44" t="n">
-        <v>7086164</v>
+        <v>7086133</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5316,7 +5311,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5326,7 +5321,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5353,7 +5348,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133582268</v>
+        <v>133582059</v>
       </c>
       <c r="B45" t="n">
         <v>80438</v>
@@ -5388,10 +5383,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>484974</v>
+        <v>484703</v>
       </c>
       <c r="R45" t="n">
-        <v>7086064</v>
+        <v>7085994</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5423,7 +5418,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5433,7 +5428,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5460,32 +5455,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133582198</v>
+        <v>133582202</v>
       </c>
       <c r="B46" t="n">
-        <v>80438</v>
+        <v>75361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>229654</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5495,10 +5490,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>484719</v>
+        <v>484604</v>
       </c>
       <c r="R46" t="n">
-        <v>7085978</v>
+        <v>7086021</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,7 +5525,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5540,7 +5535,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en rönn, kunde enbart se två bålar med skrovellav. Varav ena hade en skrovellavsknapp växande på sig!</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5567,32 +5567,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133582121</v>
+        <v>133582070</v>
       </c>
       <c r="B47" t="n">
-        <v>91881</v>
+        <v>91932</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>485166</v>
+        <v>484969</v>
       </c>
       <c r="R47" t="n">
-        <v>7086186</v>
+        <v>7086150</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5674,7 +5674,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133582070</v>
+        <v>133582065</v>
       </c>
       <c r="B48" t="n">
         <v>91932</v>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>484969</v>
+        <v>484873</v>
       </c>
       <c r="R48" t="n">
-        <v>7086150</v>
+        <v>7086047</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5781,10 +5781,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133582065</v>
+        <v>133582223</v>
       </c>
       <c r="B49" t="n">
-        <v>91932</v>
+        <v>83181</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>484873</v>
+        <v>484876</v>
       </c>
       <c r="R49" t="n">
-        <v>7086047</v>
+        <v>7086138</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,10 +5888,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133582223</v>
+        <v>133582106</v>
       </c>
       <c r="B50" t="n">
-        <v>83181</v>
+        <v>91932</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5899,21 +5899,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>484876</v>
+        <v>485052</v>
       </c>
       <c r="R50" t="n">
-        <v>7086138</v>
+        <v>7085993</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5995,10 +5995,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133582106</v>
+        <v>133582248</v>
       </c>
       <c r="B51" t="n">
-        <v>91932</v>
+        <v>83307</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1204</v>
+        <v>308</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485052</v>
+        <v>485157</v>
       </c>
       <c r="R51" t="n">
-        <v>7085993</v>
+        <v>7086076</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6102,10 +6102,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133582248</v>
+        <v>133582251</v>
       </c>
       <c r="B52" t="n">
-        <v>83307</v>
+        <v>83181</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6113,21 +6113,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485157</v>
+        <v>485137</v>
       </c>
       <c r="R52" t="n">
-        <v>7086076</v>
+        <v>7086066</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6209,32 +6209,32 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133582251</v>
+        <v>133582083</v>
       </c>
       <c r="B53" t="n">
-        <v>83181</v>
+        <v>79492</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>1249</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>485137</v>
+        <v>484926</v>
       </c>
       <c r="R53" t="n">
-        <v>7086066</v>
+        <v>7086090</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6316,32 +6316,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133582083</v>
+        <v>133582021</v>
       </c>
       <c r="B54" t="n">
-        <v>79492</v>
+        <v>91932</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>484926</v>
+        <v>485082</v>
       </c>
       <c r="R54" t="n">
-        <v>7086090</v>
+        <v>7086186</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6423,10 +6423,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133582021</v>
+        <v>133582273</v>
       </c>
       <c r="B55" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6434,21 +6434,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6458,10 +6458,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485082</v>
+        <v>484937</v>
       </c>
       <c r="R55" t="n">
-        <v>7086186</v>
+        <v>7086072</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6493,7 +6493,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6503,7 +6503,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6530,10 +6530,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133582273</v>
+        <v>133582156</v>
       </c>
       <c r="B56" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6541,21 +6541,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6565,10 +6565,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>484937</v>
+        <v>484918</v>
       </c>
       <c r="R56" t="n">
-        <v>7086072</v>
+        <v>7086183</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6610,7 +6610,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6637,10 +6637,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133582156</v>
+        <v>133582261</v>
       </c>
       <c r="B57" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6648,21 +6648,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6672,10 +6672,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>484918</v>
+        <v>485011</v>
       </c>
       <c r="R57" t="n">
-        <v>7086183</v>
+        <v>7086069</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6717,7 +6717,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6744,10 +6744,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133582261</v>
+        <v>133582098</v>
       </c>
       <c r="B58" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6755,21 +6755,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485011</v>
+        <v>484881</v>
       </c>
       <c r="R58" t="n">
-        <v>7086069</v>
+        <v>7085801</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6814,7 +6814,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6824,7 +6824,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6851,32 +6856,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133582098</v>
+        <v>133582121</v>
       </c>
       <c r="B59" t="n">
-        <v>79333</v>
+        <v>91881</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6886,10 +6891,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>484881</v>
+        <v>485166</v>
       </c>
       <c r="R59" t="n">
-        <v>7085801</v>
+        <v>7086186</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6921,7 +6926,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6931,12 +6936,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:53</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6963,45 +6963,61 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133582046</v>
+        <v>133582036</v>
       </c>
       <c r="B60" t="n">
-        <v>80398</v>
+        <v>57958</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>484605</v>
+        <v>484867</v>
       </c>
       <c r="R60" t="n">
-        <v>7086015</v>
+        <v>7086182</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7033,7 +7049,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7043,7 +7059,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Bohål, flertalet i tajgagrantickerötad granhögstubbe.  Hane ser ut att färdigställa bohål vid besöket.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7070,7 +7091,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133582115</v>
+        <v>133582046</v>
       </c>
       <c r="B61" t="n">
         <v>80398</v>
@@ -7105,10 +7126,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>485166</v>
+        <v>484605</v>
       </c>
       <c r="R61" t="n">
-        <v>7086199</v>
+        <v>7086015</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7140,7 +7161,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7150,7 +7171,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7177,7 +7198,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133582110</v>
+        <v>133582115</v>
       </c>
       <c r="B62" t="n">
         <v>80398</v>
@@ -7212,10 +7233,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>485191</v>
+        <v>485166</v>
       </c>
       <c r="R62" t="n">
-        <v>7086213</v>
+        <v>7086199</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7247,7 +7268,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7257,7 +7278,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7284,61 +7305,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133582036</v>
+        <v>133582110</v>
       </c>
       <c r="B63" t="n">
-        <v>57958</v>
+        <v>80398</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>229497</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>484867</v>
+        <v>485191</v>
       </c>
       <c r="R63" t="n">
-        <v>7086182</v>
+        <v>7086213</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7370,7 +7375,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7380,12 +7385,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Bohål, flertalet i tajgagrantickerötad granhögstubbe.  Hane ser ut att färdigställa bohål vid besöket.</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7412,10 +7412,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133582288</v>
+        <v>133582146</v>
       </c>
       <c r="B64" t="n">
-        <v>92641</v>
+        <v>80398</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7423,21 +7423,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>484904</v>
+        <v>485019</v>
       </c>
       <c r="R64" t="n">
-        <v>7085957</v>
+        <v>7086200</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7519,7 +7519,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133582146</v>
+        <v>133582124</v>
       </c>
       <c r="B65" t="n">
         <v>80398</v>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>485019</v>
+        <v>485137</v>
       </c>
       <c r="R65" t="n">
-        <v>7086200</v>
+        <v>7086195</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7626,7 +7626,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133582124</v>
+        <v>133582049</v>
       </c>
       <c r="B66" t="n">
         <v>80398</v>
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>485137</v>
+        <v>484616</v>
       </c>
       <c r="R66" t="n">
-        <v>7086195</v>
+        <v>7085997</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7733,10 +7733,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>133582049</v>
+        <v>133582288</v>
       </c>
       <c r="B67" t="n">
-        <v>80398</v>
+        <v>92641</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7744,21 +7744,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7768,10 +7768,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>484616</v>
+        <v>484904</v>
       </c>
       <c r="R67" t="n">
-        <v>7085997</v>
+        <v>7085957</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7813,7 +7813,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8268,32 +8268,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133582183</v>
+        <v>133582246</v>
       </c>
       <c r="B72" t="n">
-        <v>83313</v>
+        <v>80438</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6486</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skuggnål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chaenotheca sphaerocephala</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Nádv.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>484634</v>
+        <v>485159</v>
       </c>
       <c r="R72" t="n">
-        <v>7085988</v>
+        <v>7086078</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8375,32 +8375,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133582246</v>
+        <v>133582183</v>
       </c>
       <c r="B73" t="n">
-        <v>80438</v>
+        <v>83313</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6486</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>485159</v>
+        <v>484634</v>
       </c>
       <c r="R73" t="n">
-        <v>7086078</v>
+        <v>7085988</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -11294,10 +11294,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133582184</v>
+        <v>133582042</v>
       </c>
       <c r="B100" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11305,21 +11305,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11329,10 +11329,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>484657</v>
+        <v>484762</v>
       </c>
       <c r="R100" t="n">
-        <v>7085984</v>
+        <v>7086084</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11374,7 +11374,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11401,32 +11406,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133582233</v>
+        <v>133582179</v>
       </c>
       <c r="B101" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11436,10 +11441,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485025</v>
+        <v>484623</v>
       </c>
       <c r="R101" t="n">
-        <v>7086137</v>
+        <v>7086004</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11471,7 +11476,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11481,7 +11486,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11508,10 +11513,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133582224</v>
+        <v>133582163</v>
       </c>
       <c r="B102" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11519,21 +11524,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11543,10 +11548,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>484963</v>
+        <v>484703</v>
       </c>
       <c r="R102" t="n">
-        <v>7086155</v>
+        <v>7086043</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11578,7 +11583,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11588,7 +11593,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11615,10 +11620,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133582145</v>
+        <v>133582234</v>
       </c>
       <c r="B103" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11626,21 +11631,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11650,10 +11655,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>485022</v>
+        <v>485009</v>
       </c>
       <c r="R103" t="n">
-        <v>7086194</v>
+        <v>7086144</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11685,7 +11690,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11695,7 +11700,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11722,7 +11727,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133582144</v>
+        <v>133582184</v>
       </c>
       <c r="B104" t="n">
         <v>80438</v>
@@ -11757,10 +11762,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485024</v>
+        <v>484657</v>
       </c>
       <c r="R104" t="n">
-        <v>7086180</v>
+        <v>7085984</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11792,7 +11797,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11802,7 +11807,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11829,7 +11834,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133582255</v>
+        <v>133582233</v>
       </c>
       <c r="B105" t="n">
         <v>80438</v>
@@ -11864,10 +11869,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>485082</v>
+        <v>485025</v>
       </c>
       <c r="R105" t="n">
-        <v>7086082</v>
+        <v>7086137</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11899,7 +11904,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11909,7 +11914,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11936,7 +11941,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133582034</v>
+        <v>133582224</v>
       </c>
       <c r="B106" t="n">
         <v>80438</v>
@@ -11971,10 +11976,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>484996</v>
+        <v>484963</v>
       </c>
       <c r="R106" t="n">
-        <v>7086209</v>
+        <v>7086155</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12006,7 +12011,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12016,7 +12021,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12043,7 +12048,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133582195</v>
+        <v>133582145</v>
       </c>
       <c r="B107" t="n">
         <v>80438</v>
@@ -12078,10 +12083,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>484677</v>
+        <v>485022</v>
       </c>
       <c r="R107" t="n">
-        <v>7085977</v>
+        <v>7086194</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12113,7 +12118,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12123,7 +12128,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12150,7 +12155,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133582188</v>
+        <v>133582144</v>
       </c>
       <c r="B108" t="n">
         <v>80438</v>
@@ -12185,10 +12190,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>484675</v>
+        <v>485024</v>
       </c>
       <c r="R108" t="n">
-        <v>7085987</v>
+        <v>7086180</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12220,7 +12225,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12230,7 +12235,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12257,10 +12262,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133582042</v>
+        <v>133582255</v>
       </c>
       <c r="B109" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12268,21 +12273,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12292,10 +12297,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>484762</v>
+        <v>485082</v>
       </c>
       <c r="R109" t="n">
-        <v>7086084</v>
+        <v>7086082</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12327,7 +12332,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12337,12 +12342,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AC109" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12369,32 +12369,32 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133582179</v>
+        <v>133582034</v>
       </c>
       <c r="B110" t="n">
-        <v>80398</v>
+        <v>80438</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12404,10 +12404,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>484623</v>
+        <v>484996</v>
       </c>
       <c r="R110" t="n">
-        <v>7086004</v>
+        <v>7086209</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12476,32 +12476,32 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133582105</v>
+        <v>133582195</v>
       </c>
       <c r="B111" t="n">
-        <v>92641</v>
+        <v>80438</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -12511,10 +12511,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>485150</v>
+        <v>484677</v>
       </c>
       <c r="R111" t="n">
-        <v>7085949</v>
+        <v>7085977</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12583,10 +12583,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133582163</v>
+        <v>133582188</v>
       </c>
       <c r="B112" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12594,21 +12594,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12618,10 +12618,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>484703</v>
+        <v>484675</v>
       </c>
       <c r="R112" t="n">
-        <v>7086043</v>
+        <v>7085987</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12690,32 +12690,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133582234</v>
+        <v>133582105</v>
       </c>
       <c r="B113" t="n">
-        <v>91932</v>
+        <v>92641</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12725,10 +12725,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>485009</v>
+        <v>485150</v>
       </c>
       <c r="R113" t="n">
-        <v>7086144</v>
+        <v>7085949</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12760,7 +12760,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13226,10 +13226,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133582227</v>
+        <v>133582153</v>
       </c>
       <c r="B118" t="n">
-        <v>80438</v>
+        <v>57958</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13237,34 +13237,54 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>484991</v>
+        <v>484961</v>
       </c>
       <c r="R118" t="n">
-        <v>7086162</v>
+        <v>7086205</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13296,7 +13316,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13306,7 +13326,12 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Trummande och födosökande</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13333,10 +13358,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133582153</v>
+        <v>133582227</v>
       </c>
       <c r="B119" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13344,54 +13369,34 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>484961</v>
+        <v>484991</v>
       </c>
       <c r="R119" t="n">
-        <v>7086205</v>
+        <v>7086162</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13423,7 +13428,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13433,12 +13438,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Trummande och födosökande</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -15187,7 +15187,7 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133582266</v>
+        <v>133582206</v>
       </c>
       <c r="B136" t="n">
         <v>80438</v>
@@ -15222,10 +15222,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>484970</v>
+        <v>484786</v>
       </c>
       <c r="R136" t="n">
-        <v>7086056</v>
+        <v>7085991</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15257,7 +15257,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15267,7 +15267,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15294,7 +15294,7 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133582086</v>
+        <v>133582256</v>
       </c>
       <c r="B137" t="n">
         <v>80438</v>
@@ -15329,10 +15329,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>484918</v>
+        <v>485049</v>
       </c>
       <c r="R137" t="n">
-        <v>7086067</v>
+        <v>7086092</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15364,7 +15364,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15401,7 +15401,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133582073</v>
+        <v>133582274</v>
       </c>
       <c r="B138" t="n">
         <v>80438</v>
@@ -15436,10 +15436,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>484980</v>
+        <v>484927</v>
       </c>
       <c r="R138" t="n">
-        <v>7086124</v>
+        <v>7086073</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15471,7 +15471,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15481,12 +15481,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>18:34</t>
-        </is>
-      </c>
-      <c r="AC138" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15513,7 +15508,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133582221</v>
+        <v>133582299</v>
       </c>
       <c r="B139" t="n">
         <v>79333</v>
@@ -15548,10 +15543,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>484871</v>
+        <v>484915</v>
       </c>
       <c r="R139" t="n">
-        <v>7086160</v>
+        <v>7085804</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15583,7 +15578,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15593,7 +15588,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15620,7 +15620,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133582206</v>
+        <v>133582266</v>
       </c>
       <c r="B140" t="n">
         <v>80438</v>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>484786</v>
+        <v>484970</v>
       </c>
       <c r="R140" t="n">
-        <v>7085991</v>
+        <v>7086056</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15700,7 +15700,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15727,7 +15727,7 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133582256</v>
+        <v>133582086</v>
       </c>
       <c r="B141" t="n">
         <v>80438</v>
@@ -15762,10 +15762,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>485049</v>
+        <v>484918</v>
       </c>
       <c r="R141" t="n">
-        <v>7086092</v>
+        <v>7086067</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15797,7 +15797,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15834,7 +15834,7 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133582274</v>
+        <v>133582073</v>
       </c>
       <c r="B142" t="n">
         <v>80438</v>
@@ -15869,10 +15869,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>484927</v>
+        <v>484980</v>
       </c>
       <c r="R142" t="n">
-        <v>7086073</v>
+        <v>7086124</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15904,7 +15904,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15914,7 +15914,12 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15941,7 +15946,7 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133582299</v>
+        <v>133582221</v>
       </c>
       <c r="B143" t="n">
         <v>79333</v>
@@ -15976,10 +15981,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>484915</v>
+        <v>484871</v>
       </c>
       <c r="R143" t="n">
-        <v>7085804</v>
+        <v>7086160</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16011,7 +16016,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16021,12 +16026,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16053,7 +16053,7 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>133582200</v>
+        <v>133582292</v>
       </c>
       <c r="B144" t="n">
         <v>80438</v>
@@ -16088,10 +16088,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>484741</v>
+        <v>484915</v>
       </c>
       <c r="R144" t="n">
-        <v>7085987</v>
+        <v>7085946</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16123,7 +16123,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16133,7 +16133,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16160,7 +16160,7 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133582103</v>
+        <v>133582201</v>
       </c>
       <c r="B145" t="n">
         <v>80438</v>
@@ -16195,10 +16195,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>485125</v>
+        <v>484739</v>
       </c>
       <c r="R145" t="n">
-        <v>7085888</v>
+        <v>7085996</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16230,7 +16230,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16240,7 +16240,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16267,10 +16267,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133582265</v>
+        <v>133582055</v>
       </c>
       <c r="B146" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16278,21 +16278,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16302,10 +16302,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>484982</v>
+        <v>484664</v>
       </c>
       <c r="R146" t="n">
-        <v>7086052</v>
+        <v>7085961</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16337,7 +16337,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16347,7 +16347,12 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16374,7 +16379,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133582292</v>
+        <v>133582276</v>
       </c>
       <c r="B147" t="n">
         <v>80438</v>
@@ -16409,10 +16414,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>484915</v>
+        <v>484921</v>
       </c>
       <c r="R147" t="n">
-        <v>7085946</v>
+        <v>7086057</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16444,7 +16449,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16454,7 +16459,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16481,10 +16486,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133582201</v>
+        <v>133582245</v>
       </c>
       <c r="B148" t="n">
-        <v>80438</v>
+        <v>78345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16492,21 +16497,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16516,10 +16521,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>484739</v>
+        <v>485184</v>
       </c>
       <c r="R148" t="n">
-        <v>7085996</v>
+        <v>7086083</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16551,7 +16556,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16561,7 +16566,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16588,10 +16593,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133582055</v>
+        <v>133582140</v>
       </c>
       <c r="B149" t="n">
-        <v>79333</v>
+        <v>91932</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16599,21 +16604,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16623,10 +16628,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>484664</v>
+        <v>485048</v>
       </c>
       <c r="R149" t="n">
-        <v>7085961</v>
+        <v>7086195</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16658,7 +16663,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16668,12 +16673,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16700,10 +16700,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133582276</v>
+        <v>133582069</v>
       </c>
       <c r="B150" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16711,21 +16711,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16735,10 +16735,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>484921</v>
+        <v>484935</v>
       </c>
       <c r="R150" t="n">
-        <v>7086057</v>
+        <v>7086163</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16780,7 +16780,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16807,7 +16807,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133582140</v>
+        <v>133582139</v>
       </c>
       <c r="B151" t="n">
         <v>91932</v>
@@ -16842,10 +16842,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>485048</v>
+        <v>485039</v>
       </c>
       <c r="R151" t="n">
-        <v>7086195</v>
+        <v>7086166</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16877,7 +16877,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16887,7 +16887,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16914,10 +16914,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133582069</v>
+        <v>133582231</v>
       </c>
       <c r="B152" t="n">
-        <v>91918</v>
+        <v>83307</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16925,21 +16925,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16949,10 +16949,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>484935</v>
+        <v>485004</v>
       </c>
       <c r="R152" t="n">
-        <v>7086163</v>
+        <v>7086161</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16984,7 +16984,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -16994,7 +16994,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17021,10 +17021,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133582139</v>
+        <v>133582043</v>
       </c>
       <c r="B153" t="n">
-        <v>91932</v>
+        <v>91918</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17032,21 +17032,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17056,10 +17056,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>485039</v>
+        <v>484642</v>
       </c>
       <c r="R153" t="n">
-        <v>7086166</v>
+        <v>7086032</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17091,7 +17091,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17101,7 +17101,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17128,10 +17128,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133582231</v>
+        <v>133582272</v>
       </c>
       <c r="B154" t="n">
-        <v>83307</v>
+        <v>83181</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17139,21 +17139,21 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>308</v>
+        <v>1312</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -17163,10 +17163,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>485004</v>
+        <v>484952</v>
       </c>
       <c r="R154" t="n">
-        <v>7086161</v>
+        <v>7086063</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17198,7 +17198,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17208,7 +17208,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17235,10 +17235,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133582043</v>
+        <v>133582200</v>
       </c>
       <c r="B155" t="n">
-        <v>91918</v>
+        <v>80438</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17246,21 +17246,21 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -17270,10 +17270,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>484642</v>
+        <v>484741</v>
       </c>
       <c r="R155" t="n">
-        <v>7086032</v>
+        <v>7085987</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17305,7 +17305,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17315,7 +17315,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17342,10 +17342,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133582272</v>
+        <v>133582103</v>
       </c>
       <c r="B156" t="n">
-        <v>83181</v>
+        <v>80438</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17353,21 +17353,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17377,10 +17377,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>484952</v>
+        <v>485125</v>
       </c>
       <c r="R156" t="n">
-        <v>7086063</v>
+        <v>7085888</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17412,7 +17412,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17422,7 +17422,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17449,10 +17449,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133582218</v>
+        <v>133582265</v>
       </c>
       <c r="B157" t="n">
-        <v>57958</v>
+        <v>80438</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17460,42 +17460,34 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>484905</v>
+        <v>484982</v>
       </c>
       <c r="R157" t="n">
-        <v>7086101</v>
+        <v>7086052</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17527,7 +17519,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17537,12 +17529,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i tajgagrantickerötad granhögstubbe</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17569,10 +17556,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133582245</v>
+        <v>133582218</v>
       </c>
       <c r="B158" t="n">
-        <v>78345</v>
+        <v>57958</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17580,34 +17567,42 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>485184</v>
+        <v>484905</v>
       </c>
       <c r="R158" t="n">
-        <v>7086083</v>
+        <v>7086101</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17639,7 +17634,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17649,7 +17644,12 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18216,10 +18216,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>133582196</v>
+        <v>133582311</v>
       </c>
       <c r="B164" t="n">
-        <v>80438</v>
+        <v>91932</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18227,21 +18227,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18251,10 +18251,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>484701</v>
+        <v>484937</v>
       </c>
       <c r="R164" t="n">
-        <v>7085982</v>
+        <v>7086009</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18323,10 +18323,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133582160</v>
+        <v>133582130</v>
       </c>
       <c r="B165" t="n">
-        <v>80438</v>
+        <v>91914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18334,21 +18334,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18358,10 +18358,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>484827</v>
+        <v>485082</v>
       </c>
       <c r="R165" t="n">
-        <v>7086151</v>
+        <v>7086189</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18393,7 +18393,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18430,32 +18430,32 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133582135</v>
+        <v>133582019</v>
       </c>
       <c r="B166" t="n">
-        <v>80398</v>
+        <v>91932</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18465,10 +18465,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>485056</v>
+        <v>485182</v>
       </c>
       <c r="R166" t="n">
-        <v>7086182</v>
+        <v>7086232</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18537,10 +18537,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133582130</v>
+        <v>133582196</v>
       </c>
       <c r="B167" t="n">
-        <v>91914</v>
+        <v>80438</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18548,21 +18548,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18572,10 +18572,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>485082</v>
+        <v>484701</v>
       </c>
       <c r="R167" t="n">
-        <v>7086189</v>
+        <v>7085982</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18644,10 +18644,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133582019</v>
+        <v>133582160</v>
       </c>
       <c r="B168" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -18655,21 +18655,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -18679,10 +18679,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>485182</v>
+        <v>484827</v>
       </c>
       <c r="R168" t="n">
-        <v>7086232</v>
+        <v>7086151</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18751,32 +18751,32 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133582257</v>
+        <v>133582135</v>
       </c>
       <c r="B169" t="n">
-        <v>80438</v>
+        <v>80398</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -18786,10 +18786,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>485063</v>
+        <v>485056</v>
       </c>
       <c r="R169" t="n">
-        <v>7086069</v>
+        <v>7086182</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18858,10 +18858,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133582119</v>
+        <v>133582257</v>
       </c>
       <c r="B170" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18869,21 +18869,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18893,10 +18893,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>485161</v>
+        <v>485063</v>
       </c>
       <c r="R170" t="n">
-        <v>7086201</v>
+        <v>7086069</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -18965,10 +18965,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>133582311</v>
+        <v>133582119</v>
       </c>
       <c r="B171" t="n">
-        <v>91932</v>
+        <v>79333</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -18976,21 +18976,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -19000,10 +19000,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>484937</v>
+        <v>485161</v>
       </c>
       <c r="R171" t="n">
-        <v>7086009</v>
+        <v>7086201</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19035,7 +19035,7 @@
       </c>
       <c r="Z171" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
@@ -19045,7 +19045,7 @@
       </c>
       <c r="AB171" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19072,32 +19072,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133582041</v>
+        <v>133582178</v>
       </c>
       <c r="B172" t="n">
-        <v>92641</v>
+        <v>80439</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>3298</v>
+        <v>2081</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19107,10 +19107,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>484769</v>
+        <v>484611</v>
       </c>
       <c r="R172" t="n">
-        <v>7086104</v>
+        <v>7086015</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19179,32 +19179,32 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>133582178</v>
+        <v>133582250</v>
       </c>
       <c r="B173" t="n">
-        <v>80439</v>
+        <v>79492</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2081</v>
+        <v>1249</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19214,10 +19214,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>484611</v>
+        <v>485142</v>
       </c>
       <c r="R173" t="n">
-        <v>7086015</v>
+        <v>7086068</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19249,7 +19249,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19259,7 +19259,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19286,32 +19286,32 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>133582152</v>
+        <v>133582309</v>
       </c>
       <c r="B174" t="n">
-        <v>80438</v>
+        <v>79492</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -19321,10 +19321,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>484963</v>
+        <v>484989</v>
       </c>
       <c r="R174" t="n">
-        <v>7086207</v>
+        <v>7086017</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -19356,7 +19356,7 @@
       </c>
       <c r="Z174" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
@@ -19366,7 +19366,7 @@
       </c>
       <c r="AB174" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AD174" t="b">
@@ -19393,7 +19393,7 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>133582250</v>
+        <v>133582260</v>
       </c>
       <c r="B175" t="n">
         <v>79492</v>
@@ -19428,10 +19428,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>485142</v>
+        <v>485011</v>
       </c>
       <c r="R175" t="n">
-        <v>7086068</v>
+        <v>7086077</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -19463,7 +19463,7 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
@@ -19473,7 +19473,7 @@
       </c>
       <c r="AB175" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD175" t="b">
@@ -19500,32 +19500,32 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>133582309</v>
+        <v>133582108</v>
       </c>
       <c r="B176" t="n">
-        <v>79492</v>
+        <v>91932</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -19535,10 +19535,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>484989</v>
+        <v>485217</v>
       </c>
       <c r="R176" t="n">
-        <v>7086017</v>
+        <v>7086221</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -19570,7 +19570,7 @@
       </c>
       <c r="Z176" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -19580,7 +19580,7 @@
       </c>
       <c r="AB176" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD176" t="b">
@@ -19607,32 +19607,32 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>133582260</v>
+        <v>133582084</v>
       </c>
       <c r="B177" t="n">
-        <v>79492</v>
+        <v>91932</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -19642,10 +19642,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>485011</v>
+        <v>484920</v>
       </c>
       <c r="R177" t="n">
-        <v>7086077</v>
+        <v>7086083</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -19677,7 +19677,7 @@
       </c>
       <c r="Z177" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AA177" t="inlineStr">
@@ -19687,7 +19687,7 @@
       </c>
       <c r="AB177" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD177" t="b">
@@ -19714,32 +19714,32 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>133582108</v>
+        <v>133582242</v>
       </c>
       <c r="B178" t="n">
-        <v>91932</v>
+        <v>79492</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -19749,10 +19749,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>485217</v>
+        <v>485108</v>
       </c>
       <c r="R178" t="n">
-        <v>7086221</v>
+        <v>7086152</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -19784,7 +19784,7 @@
       </c>
       <c r="Z178" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -19794,7 +19794,7 @@
       </c>
       <c r="AB178" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD178" t="b">
@@ -19821,10 +19821,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>133582084</v>
+        <v>133582152</v>
       </c>
       <c r="B179" t="n">
-        <v>91932</v>
+        <v>80438</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -19832,21 +19832,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -19856,10 +19856,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>484920</v>
+        <v>484963</v>
       </c>
       <c r="R179" t="n">
-        <v>7086083</v>
+        <v>7086207</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -19891,7 +19891,7 @@
       </c>
       <c r="Z179" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
@@ -19901,7 +19901,7 @@
       </c>
       <c r="AB179" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -19928,32 +19928,32 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>133582242</v>
+        <v>133582095</v>
       </c>
       <c r="B180" t="n">
-        <v>79492</v>
+        <v>79333</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -19963,10 +19963,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>485108</v>
+        <v>484865</v>
       </c>
       <c r="R180" t="n">
-        <v>7086152</v>
+        <v>7085963</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -19998,7 +19998,7 @@
       </c>
       <c r="Z180" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -20008,7 +20008,12 @@
       </c>
       <c r="AB180" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD180" t="b">
@@ -20035,7 +20040,7 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>133582176</v>
+        <v>133582271</v>
       </c>
       <c r="B181" t="n">
         <v>80438</v>
@@ -20070,10 +20075,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>484642</v>
+        <v>484957</v>
       </c>
       <c r="R181" t="n">
-        <v>7086007</v>
+        <v>7086063</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20105,7 +20110,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20115,7 +20120,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:23</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20142,10 +20147,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133582095</v>
+        <v>133582175</v>
       </c>
       <c r="B182" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20153,21 +20158,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20177,10 +20182,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>484865</v>
+        <v>484608</v>
       </c>
       <c r="R182" t="n">
-        <v>7085963</v>
+        <v>7085979</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20212,7 +20217,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20222,12 +20227,7 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>20:42</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20254,10 +20254,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133582271</v>
+        <v>133582305</v>
       </c>
       <c r="B183" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20265,21 +20265,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20289,10 +20289,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>484957</v>
+        <v>485018</v>
       </c>
       <c r="R183" t="n">
-        <v>7086063</v>
+        <v>7085907</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20324,7 +20324,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:03</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20334,7 +20334,12 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>20:23</t>
+          <t>21:03</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -20361,7 +20366,7 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>133582175</v>
+        <v>133582232</v>
       </c>
       <c r="B184" t="n">
         <v>80438</v>
@@ -20396,10 +20401,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>484608</v>
+        <v>485001</v>
       </c>
       <c r="R184" t="n">
-        <v>7085979</v>
+        <v>7086162</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -20431,7 +20436,7 @@
       </c>
       <c r="Z184" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -20441,7 +20446,7 @@
       </c>
       <c r="AB184" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD184" t="b">
@@ -20468,32 +20473,32 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>133582305</v>
+        <v>133582041</v>
       </c>
       <c r="B185" t="n">
-        <v>79333</v>
+        <v>92641</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6425</v>
+        <v>3298</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -20503,10 +20508,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>485018</v>
+        <v>484769</v>
       </c>
       <c r="R185" t="n">
-        <v>7085907</v>
+        <v>7086104</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -20538,7 +20543,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>21:03</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -20548,12 +20553,7 @@
       </c>
       <c r="AB185" t="inlineStr">
         <is>
-          <t>21:03</t>
-        </is>
-      </c>
-      <c r="AC185" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD185" t="b">
@@ -20580,7 +20580,7 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>133582232</v>
+        <v>133582176</v>
       </c>
       <c r="B186" t="n">
         <v>80438</v>
@@ -20615,10 +20615,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>485001</v>
+        <v>484642</v>
       </c>
       <c r="R186" t="n">
-        <v>7086162</v>
+        <v>7086007</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="Z186" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -20660,7 +20660,7 @@
       </c>
       <c r="AB186" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD186" t="b">
@@ -20687,32 +20687,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133582300</v>
+        <v>133582263</v>
       </c>
       <c r="B187" t="n">
-        <v>80473</v>
+        <v>79492</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6463</v>
+        <v>1249</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20722,10 +20722,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>484976</v>
+        <v>484998</v>
       </c>
       <c r="R187" t="n">
-        <v>7085795</v>
+        <v>7086055</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20767,7 +20767,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20794,10 +20794,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133582225</v>
+        <v>133582066</v>
       </c>
       <c r="B188" t="n">
-        <v>80438</v>
+        <v>91918</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -20805,21 +20805,21 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20829,10 +20829,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>484969</v>
+        <v>484881</v>
       </c>
       <c r="R188" t="n">
-        <v>7086169</v>
+        <v>7086060</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20864,7 +20864,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20901,32 +20901,32 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133582237</v>
+        <v>133582300</v>
       </c>
       <c r="B189" t="n">
-        <v>80438</v>
+        <v>80473</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20936,10 +20936,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>485067</v>
+        <v>484976</v>
       </c>
       <c r="R189" t="n">
-        <v>7086146</v>
+        <v>7085795</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20971,7 +20971,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20981,7 +20981,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21008,7 +21008,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133582208</v>
+        <v>133582225</v>
       </c>
       <c r="B190" t="n">
         <v>80438</v>
@@ -21043,10 +21043,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>484791</v>
+        <v>484969</v>
       </c>
       <c r="R190" t="n">
-        <v>7085988</v>
+        <v>7086169</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21078,7 +21078,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21088,7 +21088,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21115,7 +21115,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133582048</v>
+        <v>133582237</v>
       </c>
       <c r="B191" t="n">
         <v>80438</v>
@@ -21144,23 +21144,16 @@
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
-      <c r="J191" t="inlineStr"/>
-      <c r="K191" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N191" t="inlineStr"/>
       <c r="P191" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>484618</v>
+        <v>485067</v>
       </c>
       <c r="R191" t="n">
-        <v>7085997</v>
+        <v>7086146</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21192,7 +21185,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21202,12 +21195,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC191" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21216,7 +21204,6 @@
       <c r="AE191" t="b">
         <v>0</v>
       </c>
-      <c r="AF191" t="inlineStr"/>
       <c r="AG191" t="b">
         <v>0</v>
       </c>
@@ -21235,10 +21222,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133582298</v>
+        <v>133582208</v>
       </c>
       <c r="B192" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -21246,21 +21233,21 @@
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21270,10 +21257,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>484895</v>
+        <v>484791</v>
       </c>
       <c r="R192" t="n">
-        <v>7085846</v>
+        <v>7085988</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21305,7 +21292,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21315,12 +21302,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>20:50</t>
-        </is>
-      </c>
-      <c r="AC192" t="inlineStr">
-        <is>
-          <t>Rikligt &gt; 1000 bålar</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21347,45 +21329,52 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133582263</v>
+        <v>133582048</v>
       </c>
       <c r="B193" t="n">
-        <v>79492</v>
+        <v>80438</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>484998</v>
+        <v>484618</v>
       </c>
       <c r="R193" t="n">
-        <v>7086055</v>
+        <v>7085997</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21417,7 +21406,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21427,7 +21416,12 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21436,6 +21430,7 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -21454,10 +21449,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133582066</v>
+        <v>133582298</v>
       </c>
       <c r="B194" t="n">
-        <v>91918</v>
+        <v>79333</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21465,21 +21460,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21489,10 +21484,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>484881</v>
+        <v>484895</v>
       </c>
       <c r="R194" t="n">
-        <v>7086060</v>
+        <v>7085846</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21524,7 +21519,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21534,7 +21529,12 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Rikligt &gt; 1000 bålar</t>
         </is>
       </c>
       <c r="AD194" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133582217</v>
+        <v>133582045</v>
       </c>
       <c r="B2" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484892</v>
+        <v>484603</v>
       </c>
       <c r="R2" t="n">
-        <v>7086073</v>
+        <v>7086026</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Äldre bohål i granhögstubbe</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133582307</v>
+        <v>133582035</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>57958</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +806,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +830,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485011</v>
+        <v>484926</v>
       </c>
       <c r="R3" t="n">
-        <v>7085969</v>
+        <v>7086214</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +875,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt &gt;1000 bålar</t>
+          <t>Ringhack (års)färska och äldre</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +907,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133582295</v>
+        <v>133582217</v>
       </c>
       <c r="B4" t="n">
         <v>80439</v>
@@ -929,10 +942,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484865</v>
+        <v>484892</v>
       </c>
       <c r="R4" t="n">
-        <v>7085940</v>
+        <v>7086073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +977,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +987,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133582161</v>
+        <v>133582307</v>
       </c>
       <c r="B5" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1025,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1049,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484823</v>
+        <v>485011</v>
       </c>
       <c r="R5" t="n">
-        <v>7086116</v>
+        <v>7085969</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1084,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1094,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;1000 bålar</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,7 +1126,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133582180</v>
+        <v>133582295</v>
       </c>
       <c r="B6" t="n">
         <v>80439</v>
@@ -1143,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484629</v>
+        <v>484865</v>
       </c>
       <c r="R6" t="n">
-        <v>7086008</v>
+        <v>7085940</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1233,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133582045</v>
+        <v>133582161</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,42 +1244,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484603</v>
+        <v>484823</v>
       </c>
       <c r="R7" t="n">
-        <v>7086026</v>
+        <v>7086116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1293,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1303,12 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Äldre bohål i granhögstubbe</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133582035</v>
+        <v>133582180</v>
       </c>
       <c r="B8" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1346,21 +1351,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1370,10 +1375,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484926</v>
+        <v>484629</v>
       </c>
       <c r="R8" t="n">
-        <v>7086214</v>
+        <v>7086008</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1405,7 +1410,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1415,12 +1420,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:38</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack (års)färska och äldre</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1768,32 +1768,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133582058</v>
+        <v>133582177</v>
       </c>
       <c r="B12" t="n">
-        <v>91920</v>
+        <v>80399</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>484700</v>
+        <v>484640</v>
       </c>
       <c r="R12" t="n">
-        <v>7085983</v>
+        <v>7085998</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1838,7 +1838,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1875,32 +1875,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133582207</v>
+        <v>133582027</v>
       </c>
       <c r="B13" t="n">
-        <v>80439</v>
+        <v>80399</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1910,10 +1910,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>484790</v>
+        <v>485054</v>
       </c>
       <c r="R13" t="n">
-        <v>7085985</v>
+        <v>7086211</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1945,7 +1945,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1982,32 +1982,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133582264</v>
+        <v>133582078</v>
       </c>
       <c r="B14" t="n">
-        <v>80439</v>
+        <v>92643</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484985</v>
+        <v>485145</v>
       </c>
       <c r="R14" t="n">
-        <v>7086052</v>
+        <v>7086096</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,32 +2089,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133582194</v>
+        <v>133582094</v>
       </c>
       <c r="B15" t="n">
-        <v>80439</v>
+        <v>92643</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484693</v>
+        <v>484889</v>
       </c>
       <c r="R15" t="n">
-        <v>7085982</v>
+        <v>7085970</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133582089</v>
+        <v>133582058</v>
       </c>
       <c r="B16" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,42 +2207,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484911</v>
+        <v>484700</v>
       </c>
       <c r="R16" t="n">
-        <v>7086064</v>
+        <v>7085983</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2274,7 +2266,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2284,12 +2276,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Troligt bohål, ca 1,7 m upp i tajgagrantickerötad död gran</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,32 +2303,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133582078</v>
+        <v>133582207</v>
       </c>
       <c r="B17" t="n">
-        <v>92643</v>
+        <v>80439</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2351,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>485145</v>
+        <v>484790</v>
       </c>
       <c r="R17" t="n">
-        <v>7086096</v>
+        <v>7085985</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2396,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2423,32 +2410,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133582094</v>
+        <v>133582264</v>
       </c>
       <c r="B18" t="n">
-        <v>92643</v>
+        <v>80439</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2458,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484889</v>
+        <v>484985</v>
       </c>
       <c r="R18" t="n">
-        <v>7085970</v>
+        <v>7086052</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,7 +2480,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2503,7 +2490,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,32 +2517,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133582177</v>
+        <v>133582194</v>
       </c>
       <c r="B19" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484640</v>
+        <v>484693</v>
       </c>
       <c r="R19" t="n">
-        <v>7085998</v>
+        <v>7085982</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2600,7 +2587,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2610,7 +2597,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2637,45 +2624,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133582027</v>
+        <v>133582089</v>
       </c>
       <c r="B20" t="n">
-        <v>80399</v>
+        <v>57958</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>485054</v>
+        <v>484911</v>
       </c>
       <c r="R20" t="n">
-        <v>7086211</v>
+        <v>7086064</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,7 +2702,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2717,7 +2712,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Troligt bohål, ca 1,7 m upp i tajgagrantickerötad död gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -10005,32 +10005,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133582170</v>
+        <v>133582109</v>
       </c>
       <c r="B88" t="n">
-        <v>80399</v>
+        <v>91920</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>484639</v>
+        <v>485213</v>
       </c>
       <c r="R88" t="n">
-        <v>7086021</v>
+        <v>7086209</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10112,10 +10112,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133582172</v>
+        <v>133582082</v>
       </c>
       <c r="B89" t="n">
-        <v>80439</v>
+        <v>89302</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10123,21 +10123,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>484634</v>
+        <v>485082</v>
       </c>
       <c r="R89" t="n">
-        <v>7086020</v>
+        <v>7086105</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10219,32 +10219,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133582100</v>
+        <v>133582018</v>
       </c>
       <c r="B90" t="n">
-        <v>80468</v>
+        <v>91920</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6462</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>484979</v>
+        <v>485198</v>
       </c>
       <c r="R90" t="n">
-        <v>7085799</v>
+        <v>7086232</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10326,32 +10326,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133582280</v>
+        <v>133582067</v>
       </c>
       <c r="B91" t="n">
-        <v>92643</v>
+        <v>79493</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10361,10 +10361,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>484906</v>
+        <v>484880</v>
       </c>
       <c r="R91" t="n">
-        <v>7086016</v>
+        <v>7086089</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10433,32 +10433,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133582109</v>
+        <v>133582280</v>
       </c>
       <c r="B92" t="n">
-        <v>91920</v>
+        <v>92643</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1202</v>
+        <v>3298</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>485213</v>
+        <v>484906</v>
       </c>
       <c r="R92" t="n">
-        <v>7086209</v>
+        <v>7086016</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10540,10 +10540,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133582082</v>
+        <v>133582052</v>
       </c>
       <c r="B93" t="n">
-        <v>89302</v>
+        <v>80439</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10551,21 +10551,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10575,10 +10575,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>485082</v>
+        <v>484630</v>
       </c>
       <c r="R93" t="n">
-        <v>7086105</v>
+        <v>7085961</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10647,10 +10647,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133582018</v>
+        <v>133582057</v>
       </c>
       <c r="B94" t="n">
-        <v>91920</v>
+        <v>80439</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10658,21 +10658,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10682,10 +10682,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>485198</v>
+        <v>484692</v>
       </c>
       <c r="R94" t="n">
-        <v>7086232</v>
+        <v>7085987</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10717,7 +10717,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10727,7 +10727,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10754,32 +10759,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133582067</v>
+        <v>133582172</v>
       </c>
       <c r="B95" t="n">
-        <v>79493</v>
+        <v>80439</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10789,10 +10794,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>484880</v>
+        <v>484634</v>
       </c>
       <c r="R95" t="n">
-        <v>7086089</v>
+        <v>7086020</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10824,7 +10829,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10834,7 +10839,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10861,7 +10866,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133582052</v>
+        <v>133582235</v>
       </c>
       <c r="B96" t="n">
         <v>80439</v>
@@ -10896,10 +10901,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>484630</v>
+        <v>485030</v>
       </c>
       <c r="R96" t="n">
-        <v>7085961</v>
+        <v>7086138</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10931,7 +10936,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10941,7 +10946,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10968,32 +10973,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133582057</v>
+        <v>133582100</v>
       </c>
       <c r="B97" t="n">
-        <v>80439</v>
+        <v>80468</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11003,10 +11008,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>484692</v>
+        <v>484979</v>
       </c>
       <c r="R97" t="n">
-        <v>7085987</v>
+        <v>7085799</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11038,7 +11043,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11048,12 +11053,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11080,7 +11080,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133582235</v>
+        <v>133582282</v>
       </c>
       <c r="B98" t="n">
         <v>80439</v>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>485030</v>
+        <v>484917</v>
       </c>
       <c r="R98" t="n">
-        <v>7086138</v>
+        <v>7086029</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11187,32 +11187,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133582282</v>
+        <v>133582170</v>
       </c>
       <c r="B99" t="n">
-        <v>80439</v>
+        <v>80399</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11222,10 +11222,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>484917</v>
+        <v>484639</v>
       </c>
       <c r="R99" t="n">
-        <v>7086029</v>
+        <v>7086021</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -13465,32 +13465,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133582314</v>
+        <v>133582230</v>
       </c>
       <c r="B120" t="n">
-        <v>79334</v>
+        <v>80399</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485031</v>
+        <v>485000</v>
       </c>
       <c r="R120" t="n">
-        <v>7085985</v>
+        <v>7086155</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13545,12 +13545,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>21:13</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13577,32 +13572,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133582075</v>
+        <v>133582205</v>
       </c>
       <c r="B121" t="n">
-        <v>91920</v>
+        <v>80399</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13612,10 +13607,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>485160</v>
+        <v>484779</v>
       </c>
       <c r="R121" t="n">
-        <v>7086132</v>
+        <v>7085989</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13647,7 +13642,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13657,7 +13652,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13684,32 +13679,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133582116</v>
+        <v>133582101</v>
       </c>
       <c r="B122" t="n">
-        <v>79493</v>
+        <v>80399</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13719,10 +13714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>485168</v>
+        <v>484978</v>
       </c>
       <c r="R122" t="n">
-        <v>7086214</v>
+        <v>7085798</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13754,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13764,7 +13759,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13791,32 +13786,32 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133582162</v>
+        <v>133582314</v>
       </c>
       <c r="B123" t="n">
-        <v>79493</v>
+        <v>79334</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13826,10 +13821,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>484794</v>
+        <v>485031</v>
       </c>
       <c r="R123" t="n">
-        <v>7086094</v>
+        <v>7085985</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13861,7 +13856,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13871,7 +13866,12 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13898,32 +13898,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133582211</v>
+        <v>133582075</v>
       </c>
       <c r="B124" t="n">
-        <v>92616</v>
+        <v>91920</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13933,10 +13933,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>484833</v>
+        <v>485160</v>
       </c>
       <c r="R124" t="n">
-        <v>7085991</v>
+        <v>7086132</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14005,32 +14005,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133582085</v>
+        <v>133582116</v>
       </c>
       <c r="B125" t="n">
-        <v>91934</v>
+        <v>79493</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14040,10 +14040,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>484920</v>
+        <v>485168</v>
       </c>
       <c r="R125" t="n">
-        <v>7086079</v>
+        <v>7086214</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14075,7 +14075,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14085,7 +14085,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14112,10 +14112,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133582044</v>
+        <v>133582162</v>
       </c>
       <c r="B126" t="n">
-        <v>92616</v>
+        <v>79493</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14123,21 +14123,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>898</v>
+        <v>1249</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14147,10 +14147,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>484638</v>
+        <v>484794</v>
       </c>
       <c r="R126" t="n">
-        <v>7086023</v>
+        <v>7086094</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14182,7 +14182,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14192,7 +14192,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14219,32 +14219,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133582133</v>
+        <v>133582211</v>
       </c>
       <c r="B127" t="n">
-        <v>80474</v>
+        <v>92616</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>6463</v>
+        <v>898</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14254,10 +14254,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>485084</v>
+        <v>484833</v>
       </c>
       <c r="R127" t="n">
-        <v>7086179</v>
+        <v>7085991</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14289,7 +14289,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14299,7 +14299,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14326,10 +14326,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133582026</v>
+        <v>133582085</v>
       </c>
       <c r="B128" t="n">
-        <v>80439</v>
+        <v>91934</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14337,21 +14337,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14361,10 +14361,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485057</v>
+        <v>484920</v>
       </c>
       <c r="R128" t="n">
-        <v>7086210</v>
+        <v>7086079</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14396,7 +14396,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14406,7 +14406,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14433,32 +14433,32 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133582185</v>
+        <v>133582044</v>
       </c>
       <c r="B129" t="n">
-        <v>80439</v>
+        <v>92616</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14468,10 +14468,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>484663</v>
+        <v>484638</v>
       </c>
       <c r="R129" t="n">
-        <v>7085977</v>
+        <v>7086023</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14503,7 +14503,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14513,7 +14513,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14540,32 +14540,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133582297</v>
+        <v>133582133</v>
       </c>
       <c r="B130" t="n">
-        <v>57958</v>
+        <v>80474</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14575,10 +14575,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>484903</v>
+        <v>485084</v>
       </c>
       <c r="R130" t="n">
-        <v>7085866</v>
+        <v>7086179</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14610,7 +14610,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>20:49</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14620,12 +14620,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>20:49</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14652,32 +14647,32 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133582230</v>
+        <v>133582026</v>
       </c>
       <c r="B131" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14687,10 +14682,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>485000</v>
+        <v>485057</v>
       </c>
       <c r="R131" t="n">
-        <v>7086155</v>
+        <v>7086210</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14722,7 +14717,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14732,7 +14727,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14759,32 +14754,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133582205</v>
+        <v>133582185</v>
       </c>
       <c r="B132" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14794,10 +14789,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>484779</v>
+        <v>484663</v>
       </c>
       <c r="R132" t="n">
-        <v>7085989</v>
+        <v>7085977</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14829,7 +14824,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14839,7 +14834,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14866,32 +14861,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133582101</v>
+        <v>133582297</v>
       </c>
       <c r="B133" t="n">
-        <v>80399</v>
+        <v>57958</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14901,10 +14896,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>484978</v>
+        <v>484903</v>
       </c>
       <c r="R133" t="n">
-        <v>7085798</v>
+        <v>7085866</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14936,7 +14931,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:49</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14946,7 +14941,12 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>20:49</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -16053,10 +16053,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>133582231</v>
+        <v>133582218</v>
       </c>
       <c r="B144" t="n">
-        <v>83308</v>
+        <v>57958</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16064,34 +16064,42 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>485004</v>
+        <v>484905</v>
       </c>
       <c r="R144" t="n">
-        <v>7086161</v>
+        <v>7086101</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16123,7 +16131,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16133,7 +16141,12 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16160,10 +16173,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133582055</v>
+        <v>133582140</v>
       </c>
       <c r="B145" t="n">
-        <v>79334</v>
+        <v>91934</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16171,21 +16184,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16195,10 +16208,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>484664</v>
+        <v>485048</v>
       </c>
       <c r="R145" t="n">
-        <v>7085961</v>
+        <v>7086195</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16230,7 +16243,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16240,12 +16253,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16272,10 +16280,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133582276</v>
+        <v>133582069</v>
       </c>
       <c r="B146" t="n">
-        <v>80439</v>
+        <v>91920</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16283,21 +16291,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16307,10 +16315,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>484921</v>
+        <v>484935</v>
       </c>
       <c r="R146" t="n">
-        <v>7086057</v>
+        <v>7086163</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16342,7 +16350,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16352,7 +16360,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16379,10 +16387,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133582218</v>
+        <v>133582139</v>
       </c>
       <c r="B147" t="n">
-        <v>57958</v>
+        <v>91934</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16390,42 +16398,34 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
-      <c r="K147" t="inlineStr"/>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>484905</v>
+        <v>485039</v>
       </c>
       <c r="R147" t="n">
-        <v>7086101</v>
+        <v>7086166</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16467,12 +16467,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i tajgagrantickerötad granhögstubbe</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16499,10 +16494,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133582245</v>
+        <v>133582043</v>
       </c>
       <c r="B148" t="n">
-        <v>78346</v>
+        <v>91920</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16510,21 +16505,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>228579</v>
+        <v>1202</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16534,10 +16529,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>485184</v>
+        <v>484642</v>
       </c>
       <c r="R148" t="n">
-        <v>7086083</v>
+        <v>7086032</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16569,7 +16564,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16579,7 +16574,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16606,10 +16601,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133582140</v>
+        <v>133582272</v>
       </c>
       <c r="B149" t="n">
-        <v>91934</v>
+        <v>83182</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16617,21 +16612,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16641,10 +16636,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>485048</v>
+        <v>484952</v>
       </c>
       <c r="R149" t="n">
-        <v>7086195</v>
+        <v>7086063</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16676,7 +16671,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16686,7 +16681,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16713,10 +16708,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133582069</v>
+        <v>133582231</v>
       </c>
       <c r="B150" t="n">
-        <v>91920</v>
+        <v>83308</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16724,21 +16719,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>1202</v>
+        <v>308</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16748,10 +16743,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>484935</v>
+        <v>485004</v>
       </c>
       <c r="R150" t="n">
-        <v>7086163</v>
+        <v>7086161</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16783,7 +16778,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16793,7 +16788,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16820,10 +16815,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133582139</v>
+        <v>133582292</v>
       </c>
       <c r="B151" t="n">
-        <v>91934</v>
+        <v>80439</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16831,21 +16826,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16855,10 +16850,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>485039</v>
+        <v>484915</v>
       </c>
       <c r="R151" t="n">
-        <v>7086166</v>
+        <v>7085946</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16890,7 +16885,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16900,7 +16895,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16927,10 +16922,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133582043</v>
+        <v>133582200</v>
       </c>
       <c r="B152" t="n">
-        <v>91920</v>
+        <v>80439</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16938,21 +16933,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16962,10 +16957,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>484642</v>
+        <v>484741</v>
       </c>
       <c r="R152" t="n">
-        <v>7086032</v>
+        <v>7085987</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16997,7 +16992,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17007,7 +17002,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17034,10 +17029,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133582272</v>
+        <v>133582103</v>
       </c>
       <c r="B153" t="n">
-        <v>83182</v>
+        <v>80439</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17045,21 +17040,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17069,10 +17064,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>484952</v>
+        <v>485125</v>
       </c>
       <c r="R153" t="n">
-        <v>7086063</v>
+        <v>7085888</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17104,7 +17099,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17114,7 +17109,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17141,7 +17136,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133582292</v>
+        <v>133582201</v>
       </c>
       <c r="B154" t="n">
         <v>80439</v>
@@ -17176,10 +17171,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>484915</v>
+        <v>484739</v>
       </c>
       <c r="R154" t="n">
-        <v>7085946</v>
+        <v>7085996</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17211,7 +17206,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17221,7 +17216,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17248,7 +17243,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133582200</v>
+        <v>133582265</v>
       </c>
       <c r="B155" t="n">
         <v>80439</v>
@@ -17283,10 +17278,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>484741</v>
+        <v>484982</v>
       </c>
       <c r="R155" t="n">
-        <v>7085987</v>
+        <v>7086052</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17318,7 +17313,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17328,7 +17323,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17355,10 +17350,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133582103</v>
+        <v>133582055</v>
       </c>
       <c r="B156" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17366,21 +17361,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17390,10 +17385,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>485125</v>
+        <v>484664</v>
       </c>
       <c r="R156" t="n">
-        <v>7085888</v>
+        <v>7085961</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17425,7 +17420,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17435,7 +17430,12 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17462,7 +17462,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133582201</v>
+        <v>133582276</v>
       </c>
       <c r="B157" t="n">
         <v>80439</v>
@@ -17497,10 +17497,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>484739</v>
+        <v>484921</v>
       </c>
       <c r="R157" t="n">
-        <v>7085996</v>
+        <v>7086057</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17569,10 +17569,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133582265</v>
+        <v>133582245</v>
       </c>
       <c r="B158" t="n">
-        <v>80439</v>
+        <v>78346</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17580,21 +17580,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>6458</v>
+        <v>228579</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17604,10 +17604,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>484982</v>
+        <v>485184</v>
       </c>
       <c r="R158" t="n">
-        <v>7086052</v>
+        <v>7086083</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17639,7 +17639,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17649,7 +17649,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -21561,10 +21561,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133582038</v>
+        <v>133582310</v>
       </c>
       <c r="B195" t="n">
-        <v>57958</v>
+        <v>91920</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21572,21 +21572,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21596,10 +21596,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>484815</v>
+        <v>484981</v>
       </c>
       <c r="R195" t="n">
-        <v>7086160</v>
+        <v>7086019</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21641,12 +21641,7 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC195" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21673,10 +21668,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133582039</v>
+        <v>133582076</v>
       </c>
       <c r="B196" t="n">
-        <v>57958</v>
+        <v>91934</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21684,21 +21679,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21708,10 +21703,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>484820</v>
+        <v>485222</v>
       </c>
       <c r="R196" t="n">
-        <v>7086145</v>
+        <v>7086147</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21743,7 +21738,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21753,12 +21748,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21785,10 +21775,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133582240</v>
+        <v>133582165</v>
       </c>
       <c r="B197" t="n">
-        <v>80439</v>
+        <v>91934</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21796,21 +21786,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21820,10 +21810,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>485087</v>
+        <v>484635</v>
       </c>
       <c r="R197" t="n">
-        <v>7086110</v>
+        <v>7086042</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21855,7 +21845,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21865,7 +21855,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21892,10 +21882,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133582310</v>
+        <v>133582192</v>
       </c>
       <c r="B198" t="n">
-        <v>91920</v>
+        <v>80439</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21903,21 +21893,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21927,10 +21917,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>484981</v>
+        <v>484686</v>
       </c>
       <c r="R198" t="n">
-        <v>7086019</v>
+        <v>7086001</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21962,7 +21952,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21972,7 +21962,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21999,10 +21989,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133582076</v>
+        <v>133582240</v>
       </c>
       <c r="B199" t="n">
-        <v>91934</v>
+        <v>80439</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22010,21 +22000,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22034,10 +22024,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>485222</v>
+        <v>485087</v>
       </c>
       <c r="R199" t="n">
-        <v>7086147</v>
+        <v>7086110</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22069,7 +22059,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22079,7 +22069,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22106,10 +22096,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133582165</v>
+        <v>133582111</v>
       </c>
       <c r="B200" t="n">
-        <v>91934</v>
+        <v>80439</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22117,21 +22107,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22141,10 +22131,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>484635</v>
+        <v>485195</v>
       </c>
       <c r="R200" t="n">
-        <v>7086042</v>
+        <v>7086212</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22176,7 +22166,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22186,7 +22176,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22213,7 +22203,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133582192</v>
+        <v>133582141</v>
       </c>
       <c r="B201" t="n">
         <v>80439</v>
@@ -22248,10 +22238,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>484686</v>
+        <v>485018</v>
       </c>
       <c r="R201" t="n">
-        <v>7086001</v>
+        <v>7086170</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22283,7 +22273,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22293,7 +22283,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22320,7 +22310,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>133582111</v>
+        <v>133582050</v>
       </c>
       <c r="B202" t="n">
         <v>80439</v>
@@ -22349,16 +22339,23 @@
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>485195</v>
+        <v>484621</v>
       </c>
       <c r="R202" t="n">
-        <v>7086212</v>
+        <v>7085976</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22390,7 +22387,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22400,7 +22397,12 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC202" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22409,6 +22411,7 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
+      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -22427,7 +22430,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>133582141</v>
+        <v>133582025</v>
       </c>
       <c r="B203" t="n">
         <v>80439</v>
@@ -22462,10 +22465,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>485018</v>
+        <v>485061</v>
       </c>
       <c r="R203" t="n">
-        <v>7086170</v>
+        <v>7086190</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22497,7 +22500,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22507,7 +22510,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22534,7 +22537,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>133582050</v>
+        <v>133582157</v>
       </c>
       <c r="B204" t="n">
         <v>80439</v>
@@ -22563,23 +22566,16 @@
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
-      <c r="J204" t="inlineStr"/>
-      <c r="K204" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>484621</v>
+        <v>484872</v>
       </c>
       <c r="R204" t="n">
-        <v>7085976</v>
+        <v>7086175</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22611,7 +22607,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22621,12 +22617,7 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC204" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22635,7 +22626,6 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
-      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -22654,10 +22644,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>133582025</v>
+        <v>133582038</v>
       </c>
       <c r="B205" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22665,21 +22655,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22689,10 +22679,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>485061</v>
+        <v>484815</v>
       </c>
       <c r="R205" t="n">
-        <v>7086190</v>
+        <v>7086160</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22724,7 +22714,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22734,7 +22724,12 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC205" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22761,10 +22756,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>133582157</v>
+        <v>133582039</v>
       </c>
       <c r="B206" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22772,21 +22767,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22796,10 +22791,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>484872</v>
+        <v>484820</v>
       </c>
       <c r="R206" t="n">
-        <v>7086175</v>
+        <v>7086145</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22831,7 +22826,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22841,7 +22836,12 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC206" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24483,32 +24483,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>133582186</v>
+        <v>133582081</v>
       </c>
       <c r="B222" t="n">
-        <v>80399</v>
+        <v>79334</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24518,10 +24518,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>484668</v>
+        <v>485108</v>
       </c>
       <c r="R222" t="n">
-        <v>7085980</v>
+        <v>7086096</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24553,7 +24553,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24590,7 +24590,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>133582081</v>
+        <v>133582053</v>
       </c>
       <c r="B223" t="n">
         <v>79334</v>
@@ -24625,10 +24625,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>485108</v>
+        <v>484633</v>
       </c>
       <c r="R223" t="n">
-        <v>7086096</v>
+        <v>7085966</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24660,7 +24660,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24670,7 +24670,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24697,32 +24697,32 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>133582053</v>
+        <v>133582254</v>
       </c>
       <c r="B224" t="n">
-        <v>79334</v>
+        <v>79493</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24732,10 +24732,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>484633</v>
+        <v>485098</v>
       </c>
       <c r="R224" t="n">
-        <v>7085966</v>
+        <v>7086073</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24767,7 +24767,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24777,7 +24777,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24804,32 +24804,32 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>133582254</v>
+        <v>133582112</v>
       </c>
       <c r="B225" t="n">
-        <v>79493</v>
+        <v>80439</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24839,10 +24839,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>485098</v>
+        <v>485199</v>
       </c>
       <c r="R225" t="n">
-        <v>7086073</v>
+        <v>7086220</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24911,7 +24911,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>133582112</v>
+        <v>133582126</v>
       </c>
       <c r="B226" t="n">
         <v>80439</v>
@@ -24946,10 +24946,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>485199</v>
+        <v>485151</v>
       </c>
       <c r="R226" t="n">
-        <v>7086220</v>
+        <v>7086178</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25018,7 +25018,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>133582126</v>
+        <v>133582215</v>
       </c>
       <c r="B227" t="n">
         <v>80439</v>
@@ -25053,10 +25053,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>485151</v>
+        <v>484868</v>
       </c>
       <c r="R227" t="n">
-        <v>7086178</v>
+        <v>7086047</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25088,7 +25088,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25125,32 +25125,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>133582215</v>
+        <v>133582186</v>
       </c>
       <c r="B228" t="n">
-        <v>80439</v>
+        <v>80399</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25160,10 +25160,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>484868</v>
+        <v>484668</v>
       </c>
       <c r="R228" t="n">
-        <v>7086047</v>
+        <v>7085980</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25205,7 +25205,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD228" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133582045</v>
+        <v>133582217</v>
       </c>
       <c r="B2" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484603</v>
+        <v>484892</v>
       </c>
       <c r="R2" t="n">
-        <v>7086026</v>
+        <v>7086073</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Äldre bohål i granhögstubbe</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133582035</v>
+        <v>133582307</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -830,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484926</v>
+        <v>485011</v>
       </c>
       <c r="R3" t="n">
-        <v>7086214</v>
+        <v>7085969</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,12 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack (års)färska och äldre</t>
+          <t>Rikligt &gt;1000 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133582217</v>
+        <v>133582295</v>
       </c>
       <c r="B4" t="n">
         <v>80439</v>
@@ -942,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484892</v>
+        <v>484865</v>
       </c>
       <c r="R4" t="n">
-        <v>7086073</v>
+        <v>7085940</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133582307</v>
+        <v>133582161</v>
       </c>
       <c r="B5" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1025,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>485011</v>
+        <v>484823</v>
       </c>
       <c r="R5" t="n">
-        <v>7085969</v>
+        <v>7086116</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,12 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>21:05</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;1000 bålar</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,7 +1108,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133582295</v>
+        <v>133582180</v>
       </c>
       <c r="B6" t="n">
         <v>80439</v>
@@ -1161,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484865</v>
+        <v>484629</v>
       </c>
       <c r="R6" t="n">
-        <v>7085940</v>
+        <v>7086008</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1233,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133582161</v>
+        <v>133582045</v>
       </c>
       <c r="B7" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,34 +1226,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484823</v>
+        <v>484603</v>
       </c>
       <c r="R7" t="n">
-        <v>7086116</v>
+        <v>7086026</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1303,7 +1293,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1303,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Äldre bohål i granhögstubbe</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,10 +1335,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133582180</v>
+        <v>133582035</v>
       </c>
       <c r="B8" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,21 +1346,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1375,10 +1370,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484629</v>
+        <v>484926</v>
       </c>
       <c r="R8" t="n">
-        <v>7086008</v>
+        <v>7086214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1410,7 +1405,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1420,7 +1415,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>16:38</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack (års)färska och äldre</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1982,32 +1982,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133582078</v>
+        <v>133582058</v>
       </c>
       <c r="B14" t="n">
-        <v>92643</v>
+        <v>91920</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485145</v>
+        <v>484700</v>
       </c>
       <c r="R14" t="n">
-        <v>7086096</v>
+        <v>7085983</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,32 +2089,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133582094</v>
+        <v>133582207</v>
       </c>
       <c r="B15" t="n">
-        <v>92643</v>
+        <v>80439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2124,10 +2124,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484889</v>
+        <v>484790</v>
       </c>
       <c r="R15" t="n">
-        <v>7085970</v>
+        <v>7085985</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133582058</v>
+        <v>133582264</v>
       </c>
       <c r="B16" t="n">
-        <v>91920</v>
+        <v>80439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>484700</v>
+        <v>484985</v>
       </c>
       <c r="R16" t="n">
-        <v>7085983</v>
+        <v>7086052</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,7 +2303,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133582207</v>
+        <v>133582194</v>
       </c>
       <c r="B17" t="n">
         <v>80439</v>
@@ -2338,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484790</v>
+        <v>484693</v>
       </c>
       <c r="R17" t="n">
-        <v>7085985</v>
+        <v>7085982</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,10 +2410,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133582264</v>
+        <v>133582089</v>
       </c>
       <c r="B18" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,34 +2421,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484985</v>
+        <v>484911</v>
       </c>
       <c r="R18" t="n">
-        <v>7086052</v>
+        <v>7086064</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2488,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2490,7 +2498,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Troligt bohål, ca 1,7 m upp i tajgagrantickerötad död gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,32 +2530,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133582194</v>
+        <v>133582078</v>
       </c>
       <c r="B19" t="n">
-        <v>80439</v>
+        <v>92643</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484693</v>
+        <v>485145</v>
       </c>
       <c r="R19" t="n">
-        <v>7085982</v>
+        <v>7086096</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2587,7 +2600,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2597,7 +2610,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2624,53 +2637,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133582089</v>
+        <v>133582094</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>92643</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>484911</v>
+        <v>484889</v>
       </c>
       <c r="R20" t="n">
-        <v>7086064</v>
+        <v>7085970</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,7 +2707,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2712,12 +2717,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Troligt bohål, ca 1,7 m upp i tajgagrantickerötad död gran</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -8482,10 +8482,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>133582286</v>
+        <v>133582290</v>
       </c>
       <c r="B74" t="n">
-        <v>57958</v>
+        <v>79334</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8493,21 +8493,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8517,10 +8517,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>484903</v>
+        <v>484913</v>
       </c>
       <c r="R74" t="n">
-        <v>7086007</v>
+        <v>7085953</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8552,7 +8552,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran</t>
+          <t>Rikligt &gt;1000 bålar</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8594,7 +8594,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>133582290</v>
+        <v>133582166</v>
       </c>
       <c r="B75" t="n">
         <v>79334</v>
@@ -8629,10 +8629,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>484913</v>
+        <v>484622</v>
       </c>
       <c r="R75" t="n">
-        <v>7085953</v>
+        <v>7086030</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Rikligt &gt;1000 bålar</t>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8706,10 +8706,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>133582209</v>
+        <v>133582148</v>
       </c>
       <c r="B76" t="n">
-        <v>91934</v>
+        <v>80439</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8717,21 +8717,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8741,10 +8741,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>484821</v>
+        <v>484982</v>
       </c>
       <c r="R76" t="n">
-        <v>7085990</v>
+        <v>7086198</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:08</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8813,32 +8813,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>133582020</v>
+        <v>133582134</v>
       </c>
       <c r="B77" t="n">
-        <v>92643</v>
+        <v>80439</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8848,10 +8848,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>485070</v>
+        <v>485054</v>
       </c>
       <c r="R77" t="n">
-        <v>7086196</v>
+        <v>7086182</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8883,7 +8883,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8893,7 +8893,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>15:59</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8920,7 +8920,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>133582117</v>
+        <v>133582275</v>
       </c>
       <c r="B78" t="n">
         <v>80439</v>
@@ -8955,10 +8955,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>485166</v>
+        <v>484929</v>
       </c>
       <c r="R78" t="n">
-        <v>7086225</v>
+        <v>7086069</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8990,7 +8990,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -9000,7 +9000,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9027,32 +9027,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>133582099</v>
+        <v>133582020</v>
       </c>
       <c r="B79" t="n">
-        <v>80439</v>
+        <v>92643</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9062,10 +9062,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>484973</v>
+        <v>485070</v>
       </c>
       <c r="R79" t="n">
-        <v>7085799</v>
+        <v>7086196</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -9107,12 +9107,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>20:58</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:59</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9139,10 +9134,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>133582166</v>
+        <v>133582209</v>
       </c>
       <c r="B80" t="n">
-        <v>79334</v>
+        <v>91934</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9150,21 +9145,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9174,10 +9169,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>484622</v>
+        <v>484821</v>
       </c>
       <c r="R80" t="n">
-        <v>7086030</v>
+        <v>7085990</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9209,7 +9204,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9219,12 +9214,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:22</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9251,7 +9241,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>133582148</v>
+        <v>133582117</v>
       </c>
       <c r="B81" t="n">
         <v>80439</v>
@@ -9286,10 +9276,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>484982</v>
+        <v>485166</v>
       </c>
       <c r="R81" t="n">
-        <v>7086198</v>
+        <v>7086225</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9321,7 +9311,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9331,7 +9321,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9358,10 +9348,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>133582093</v>
+        <v>133582099</v>
       </c>
       <c r="B82" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9369,21 +9359,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9393,10 +9383,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>484893</v>
+        <v>484973</v>
       </c>
       <c r="R82" t="n">
-        <v>7085985</v>
+        <v>7085799</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9428,7 +9418,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9438,7 +9428,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr">
@@ -9470,10 +9460,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>133582134</v>
+        <v>133582093</v>
       </c>
       <c r="B83" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9481,21 +9471,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9505,10 +9495,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>485054</v>
+        <v>484893</v>
       </c>
       <c r="R83" t="n">
-        <v>7086182</v>
+        <v>7085985</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9540,7 +9530,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9550,7 +9540,12 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>16:17</t>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9577,7 +9572,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>133582275</v>
+        <v>133582213</v>
       </c>
       <c r="B84" t="n">
         <v>80439</v>
@@ -9612,10 +9607,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>484929</v>
+        <v>484826</v>
       </c>
       <c r="R84" t="n">
-        <v>7086069</v>
+        <v>7085982</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9647,7 +9642,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -9657,7 +9652,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:12</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9684,7 +9679,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>133582213</v>
+        <v>133582074</v>
       </c>
       <c r="B85" t="n">
         <v>80439</v>
@@ -9719,10 +9714,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>484826</v>
+        <v>485022</v>
       </c>
       <c r="R85" t="n">
-        <v>7085982</v>
+        <v>7086142</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9754,7 +9749,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9764,7 +9759,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>18:12</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9791,10 +9786,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>133582074</v>
+        <v>133582286</v>
       </c>
       <c r="B86" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9802,21 +9797,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9826,10 +9821,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>485022</v>
+        <v>484903</v>
       </c>
       <c r="R86" t="n">
-        <v>7086142</v>
+        <v>7086007</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9861,7 +9856,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9871,7 +9866,12 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10005,32 +10005,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133582109</v>
+        <v>133582170</v>
       </c>
       <c r="B88" t="n">
-        <v>91920</v>
+        <v>80399</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>1202</v>
+        <v>229497</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>485213</v>
+        <v>484639</v>
       </c>
       <c r="R88" t="n">
-        <v>7086209</v>
+        <v>7086021</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10112,10 +10112,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133582082</v>
+        <v>133582172</v>
       </c>
       <c r="B89" t="n">
-        <v>89302</v>
+        <v>80439</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10123,21 +10123,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>485082</v>
+        <v>484634</v>
       </c>
       <c r="R89" t="n">
-        <v>7086105</v>
+        <v>7086020</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10219,32 +10219,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133582018</v>
+        <v>133582100</v>
       </c>
       <c r="B90" t="n">
-        <v>91920</v>
+        <v>80468</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>485198</v>
+        <v>484979</v>
       </c>
       <c r="R90" t="n">
-        <v>7086232</v>
+        <v>7085799</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10326,32 +10326,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133582067</v>
+        <v>133582280</v>
       </c>
       <c r="B91" t="n">
-        <v>79493</v>
+        <v>92643</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>1249</v>
+        <v>3298</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10361,10 +10361,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>484880</v>
+        <v>484906</v>
       </c>
       <c r="R91" t="n">
-        <v>7086089</v>
+        <v>7086016</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10433,32 +10433,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133582280</v>
+        <v>133582109</v>
       </c>
       <c r="B92" t="n">
-        <v>92643</v>
+        <v>91920</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>3298</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>484906</v>
+        <v>485213</v>
       </c>
       <c r="R92" t="n">
-        <v>7086016</v>
+        <v>7086209</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10513,7 +10513,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10540,10 +10540,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133582052</v>
+        <v>133582082</v>
       </c>
       <c r="B93" t="n">
-        <v>80439</v>
+        <v>89302</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10551,21 +10551,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10575,10 +10575,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>484630</v>
+        <v>485082</v>
       </c>
       <c r="R93" t="n">
-        <v>7085961</v>
+        <v>7086105</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10610,7 +10610,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10620,7 +10620,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10647,10 +10647,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133582057</v>
+        <v>133582018</v>
       </c>
       <c r="B94" t="n">
-        <v>80439</v>
+        <v>91920</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10658,21 +10658,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10682,10 +10682,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>484692</v>
+        <v>485198</v>
       </c>
       <c r="R94" t="n">
-        <v>7085987</v>
+        <v>7086232</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10717,7 +10717,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10727,12 +10727,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10759,32 +10754,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133582172</v>
+        <v>133582067</v>
       </c>
       <c r="B95" t="n">
-        <v>80439</v>
+        <v>79493</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10794,10 +10789,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>484634</v>
+        <v>484880</v>
       </c>
       <c r="R95" t="n">
-        <v>7086020</v>
+        <v>7086089</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10829,7 +10824,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10839,7 +10834,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10866,7 +10861,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133582235</v>
+        <v>133582052</v>
       </c>
       <c r="B96" t="n">
         <v>80439</v>
@@ -10901,10 +10896,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>485030</v>
+        <v>484630</v>
       </c>
       <c r="R96" t="n">
-        <v>7086138</v>
+        <v>7085961</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10936,7 +10931,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10946,7 +10941,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10973,32 +10968,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133582100</v>
+        <v>133582057</v>
       </c>
       <c r="B97" t="n">
-        <v>80468</v>
+        <v>80439</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11008,10 +11003,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>484979</v>
+        <v>484692</v>
       </c>
       <c r="R97" t="n">
-        <v>7085799</v>
+        <v>7085987</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11043,7 +11038,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11053,7 +11048,12 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11080,7 +11080,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133582282</v>
+        <v>133582235</v>
       </c>
       <c r="B98" t="n">
         <v>80439</v>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>484917</v>
+        <v>485030</v>
       </c>
       <c r="R98" t="n">
-        <v>7086029</v>
+        <v>7086138</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11187,32 +11187,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133582170</v>
+        <v>133582282</v>
       </c>
       <c r="B99" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11222,10 +11222,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>484639</v>
+        <v>484917</v>
       </c>
       <c r="R99" t="n">
-        <v>7086021</v>
+        <v>7086029</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -16053,10 +16053,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>133582218</v>
+        <v>133582231</v>
       </c>
       <c r="B144" t="n">
-        <v>57958</v>
+        <v>83308</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16064,42 +16064,34 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>484905</v>
+        <v>485004</v>
       </c>
       <c r="R144" t="n">
-        <v>7086101</v>
+        <v>7086161</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -16131,7 +16123,7 @@
       </c>
       <c r="Z144" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -16141,12 +16133,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>18:17</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>Gammalt bohål i tajgagrantickerötad granhögstubbe</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16173,10 +16160,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>133582140</v>
+        <v>133582055</v>
       </c>
       <c r="B145" t="n">
-        <v>91934</v>
+        <v>79334</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16184,21 +16171,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -16208,10 +16195,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>485048</v>
+        <v>484664</v>
       </c>
       <c r="R145" t="n">
-        <v>7086195</v>
+        <v>7085961</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16243,7 +16230,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -16253,7 +16240,12 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>Ganska rikligt</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16280,10 +16272,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>133582069</v>
+        <v>133582276</v>
       </c>
       <c r="B146" t="n">
-        <v>91920</v>
+        <v>80439</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16291,21 +16283,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -16315,10 +16307,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>484935</v>
+        <v>484921</v>
       </c>
       <c r="R146" t="n">
-        <v>7086163</v>
+        <v>7086057</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16350,7 +16342,7 @@
       </c>
       <c r="Z146" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -16360,7 +16352,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16387,10 +16379,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>133582139</v>
+        <v>133582218</v>
       </c>
       <c r="B147" t="n">
-        <v>91934</v>
+        <v>57958</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16398,34 +16390,42 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>485039</v>
+        <v>484905</v>
       </c>
       <c r="R147" t="n">
-        <v>7086166</v>
+        <v>7086101</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16457,7 +16457,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -16467,7 +16467,12 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:17</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>Gammalt bohål i tajgagrantickerötad granhögstubbe</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16494,10 +16499,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>133582043</v>
+        <v>133582245</v>
       </c>
       <c r="B148" t="n">
-        <v>91920</v>
+        <v>78346</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16505,21 +16510,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>1202</v>
+        <v>228579</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16529,10 +16534,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>484642</v>
+        <v>485184</v>
       </c>
       <c r="R148" t="n">
-        <v>7086032</v>
+        <v>7086083</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16564,7 +16569,7 @@
       </c>
       <c r="Z148" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
@@ -16574,7 +16579,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>17:22</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16601,10 +16606,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>133582272</v>
+        <v>133582140</v>
       </c>
       <c r="B149" t="n">
-        <v>83182</v>
+        <v>91934</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16612,21 +16617,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -16636,10 +16641,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>484952</v>
+        <v>485048</v>
       </c>
       <c r="R149" t="n">
-        <v>7086063</v>
+        <v>7086195</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -16671,7 +16676,7 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
@@ -16681,7 +16686,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>20:24</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -16708,10 +16713,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>133582231</v>
+        <v>133582069</v>
       </c>
       <c r="B150" t="n">
-        <v>83308</v>
+        <v>91920</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -16719,21 +16724,21 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>308</v>
+        <v>1202</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -16743,10 +16748,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>485004</v>
+        <v>484935</v>
       </c>
       <c r="R150" t="n">
-        <v>7086161</v>
+        <v>7086163</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16778,7 +16783,7 @@
       </c>
       <c r="Z150" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -16788,7 +16793,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -16815,10 +16820,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>133582292</v>
+        <v>133582139</v>
       </c>
       <c r="B151" t="n">
-        <v>80439</v>
+        <v>91934</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -16826,21 +16831,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -16850,10 +16855,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>484915</v>
+        <v>485039</v>
       </c>
       <c r="R151" t="n">
-        <v>7085946</v>
+        <v>7086166</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -16885,7 +16890,7 @@
       </c>
       <c r="Z151" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
@@ -16895,7 +16900,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -16922,10 +16927,10 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>133582200</v>
+        <v>133582043</v>
       </c>
       <c r="B152" t="n">
-        <v>80439</v>
+        <v>91920</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -16933,21 +16938,21 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
@@ -16957,10 +16962,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>484741</v>
+        <v>484642</v>
       </c>
       <c r="R152" t="n">
-        <v>7085987</v>
+        <v>7086032</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16992,7 +16997,7 @@
       </c>
       <c r="Z152" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -17002,7 +17007,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>17:22</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17029,10 +17034,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>133582103</v>
+        <v>133582272</v>
       </c>
       <c r="B153" t="n">
-        <v>80439</v>
+        <v>83182</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17040,21 +17045,21 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -17064,10 +17069,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>485125</v>
+        <v>484952</v>
       </c>
       <c r="R153" t="n">
-        <v>7085888</v>
+        <v>7086063</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17099,7 +17104,7 @@
       </c>
       <c r="Z153" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
@@ -17109,7 +17114,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>21:08</t>
+          <t>20:24</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17136,7 +17141,7 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>133582201</v>
+        <v>133582292</v>
       </c>
       <c r="B154" t="n">
         <v>80439</v>
@@ -17171,10 +17176,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>484739</v>
+        <v>484915</v>
       </c>
       <c r="R154" t="n">
-        <v>7085996</v>
+        <v>7085946</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17206,7 +17211,7 @@
       </c>
       <c r="Z154" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -17216,7 +17221,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>17:55</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17243,7 +17248,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>133582265</v>
+        <v>133582200</v>
       </c>
       <c r="B155" t="n">
         <v>80439</v>
@@ -17278,10 +17283,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>484982</v>
+        <v>484741</v>
       </c>
       <c r="R155" t="n">
-        <v>7086052</v>
+        <v>7085987</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17313,7 +17318,7 @@
       </c>
       <c r="Z155" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
@@ -17323,7 +17328,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17350,10 +17355,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>133582055</v>
+        <v>133582103</v>
       </c>
       <c r="B156" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17361,21 +17366,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17385,10 +17390,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>484664</v>
+        <v>485125</v>
       </c>
       <c r="R156" t="n">
-        <v>7085961</v>
+        <v>7085888</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -17420,7 +17425,7 @@
       </c>
       <c r="Z156" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -17430,12 +17435,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AC156" t="inlineStr">
-        <is>
-          <t>Ganska rikligt</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17462,7 +17462,7 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>133582276</v>
+        <v>133582201</v>
       </c>
       <c r="B157" t="n">
         <v>80439</v>
@@ -17497,10 +17497,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>484921</v>
+        <v>484739</v>
       </c>
       <c r="R157" t="n">
-        <v>7086057</v>
+        <v>7085996</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="Z157" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
@@ -17542,7 +17542,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17569,10 +17569,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>133582245</v>
+        <v>133582265</v>
       </c>
       <c r="B158" t="n">
-        <v>78346</v>
+        <v>80439</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -17580,21 +17580,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>228579</v>
+        <v>6458</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -17604,10 +17604,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>485184</v>
+        <v>484982</v>
       </c>
       <c r="R158" t="n">
-        <v>7086083</v>
+        <v>7086052</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -17639,7 +17639,7 @@
       </c>
       <c r="Z158" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -17649,7 +17649,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -19072,32 +19072,32 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>133582152</v>
+        <v>133582041</v>
       </c>
       <c r="B172" t="n">
-        <v>80439</v>
+        <v>92643</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -19107,10 +19107,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>484963</v>
+        <v>484769</v>
       </c>
       <c r="R172" t="n">
-        <v>7086207</v>
+        <v>7086104</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="Z172" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -19152,7 +19152,7 @@
       </c>
       <c r="AB172" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -20040,32 +20040,32 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>133582041</v>
+        <v>133582176</v>
       </c>
       <c r="B181" t="n">
-        <v>92643</v>
+        <v>80439</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -20075,10 +20075,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>484769</v>
+        <v>484642</v>
       </c>
       <c r="R181" t="n">
-        <v>7086104</v>
+        <v>7086007</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -20110,7 +20110,7 @@
       </c>
       <c r="Z181" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
@@ -20120,7 +20120,7 @@
       </c>
       <c r="AB181" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -20147,10 +20147,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>133582176</v>
+        <v>133582095</v>
       </c>
       <c r="B182" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -20158,21 +20158,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -20182,10 +20182,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>484642</v>
+        <v>484865</v>
       </c>
       <c r="R182" t="n">
-        <v>7086007</v>
+        <v>7085963</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -20217,7 +20217,7 @@
       </c>
       <c r="Z182" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
@@ -20227,7 +20227,12 @@
       </c>
       <c r="AB182" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>20:42</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -20254,10 +20259,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>133582095</v>
+        <v>133582152</v>
       </c>
       <c r="B183" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -20265,21 +20270,21 @@
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -20289,10 +20294,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>484865</v>
+        <v>484963</v>
       </c>
       <c r="R183" t="n">
-        <v>7085963</v>
+        <v>7086207</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -20324,7 +20329,7 @@
       </c>
       <c r="Z183" t="inlineStr">
         <is>
-          <t>20:42</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA183" t="inlineStr">
@@ -20334,12 +20339,7 @@
       </c>
       <c r="AB183" t="inlineStr">
         <is>
-          <t>20:42</t>
-        </is>
-      </c>
-      <c r="AC183" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD183" t="b">
@@ -21561,10 +21561,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>133582310</v>
+        <v>133582038</v>
       </c>
       <c r="B195" t="n">
-        <v>91920</v>
+        <v>57958</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -21572,21 +21572,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -21596,10 +21596,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>484981</v>
+        <v>484815</v>
       </c>
       <c r="R195" t="n">
-        <v>7086019</v>
+        <v>7086160</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -21631,7 +21631,7 @@
       </c>
       <c r="Z195" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA195" t="inlineStr">
@@ -21641,7 +21641,12 @@
       </c>
       <c r="AB195" t="inlineStr">
         <is>
-          <t>21:09</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD195" t="b">
@@ -21668,10 +21673,10 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133582076</v>
+        <v>133582039</v>
       </c>
       <c r="B196" t="n">
-        <v>91934</v>
+        <v>57958</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -21679,21 +21684,21 @@
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
@@ -21703,10 +21708,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>485222</v>
+        <v>484820</v>
       </c>
       <c r="R196" t="n">
-        <v>7086147</v>
+        <v>7086145</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21738,7 +21743,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21748,7 +21753,12 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21775,10 +21785,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133582165</v>
+        <v>133582240</v>
       </c>
       <c r="B197" t="n">
-        <v>91934</v>
+        <v>80439</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -21786,21 +21796,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -21810,10 +21820,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>484635</v>
+        <v>485087</v>
       </c>
       <c r="R197" t="n">
-        <v>7086042</v>
+        <v>7086110</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21845,7 +21855,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21855,7 +21865,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21882,10 +21892,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133582192</v>
+        <v>133582310</v>
       </c>
       <c r="B198" t="n">
-        <v>80439</v>
+        <v>91920</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21893,21 +21903,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21917,10 +21927,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>484686</v>
+        <v>484981</v>
       </c>
       <c r="R198" t="n">
-        <v>7086001</v>
+        <v>7086019</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21952,7 +21962,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21962,7 +21972,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -21989,10 +21999,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133582240</v>
+        <v>133582076</v>
       </c>
       <c r="B199" t="n">
-        <v>80439</v>
+        <v>91934</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -22000,21 +22010,21 @@
         </is>
       </c>
       <c r="E199" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -22024,10 +22034,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>485087</v>
+        <v>485222</v>
       </c>
       <c r="R199" t="n">
-        <v>7086110</v>
+        <v>7086147</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22059,7 +22069,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22069,7 +22079,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22096,10 +22106,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133582111</v>
+        <v>133582165</v>
       </c>
       <c r="B200" t="n">
-        <v>80439</v>
+        <v>91934</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -22107,21 +22117,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -22131,10 +22141,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>485195</v>
+        <v>484635</v>
       </c>
       <c r="R200" t="n">
-        <v>7086212</v>
+        <v>7086042</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22166,7 +22176,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22176,7 +22186,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22203,7 +22213,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133582141</v>
+        <v>133582192</v>
       </c>
       <c r="B201" t="n">
         <v>80439</v>
@@ -22238,10 +22248,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>485018</v>
+        <v>484686</v>
       </c>
       <c r="R201" t="n">
-        <v>7086170</v>
+        <v>7086001</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22273,7 +22283,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22283,7 +22293,7 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22310,7 +22320,7 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>133582050</v>
+        <v>133582111</v>
       </c>
       <c r="B202" t="n">
         <v>80439</v>
@@ -22339,23 +22349,16 @@
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
-      <c r="J202" t="inlineStr"/>
-      <c r="K202" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N202" t="inlineStr"/>
       <c r="P202" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>484621</v>
+        <v>485195</v>
       </c>
       <c r="R202" t="n">
-        <v>7085976</v>
+        <v>7086212</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22387,7 +22390,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22397,12 +22400,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC202" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22411,7 +22409,6 @@
       <c r="AE202" t="b">
         <v>0</v>
       </c>
-      <c r="AF202" t="inlineStr"/>
       <c r="AG202" t="b">
         <v>0</v>
       </c>
@@ -22430,7 +22427,7 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>133582025</v>
+        <v>133582141</v>
       </c>
       <c r="B203" t="n">
         <v>80439</v>
@@ -22465,10 +22462,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>485061</v>
+        <v>485018</v>
       </c>
       <c r="R203" t="n">
-        <v>7086190</v>
+        <v>7086170</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22500,7 +22497,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22510,7 +22507,7 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22537,7 +22534,7 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>133582157</v>
+        <v>133582050</v>
       </c>
       <c r="B204" t="n">
         <v>80439</v>
@@ -22566,16 +22563,23 @@
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>484872</v>
+        <v>484621</v>
       </c>
       <c r="R204" t="n">
-        <v>7086175</v>
+        <v>7085976</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22607,7 +22611,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22617,7 +22621,12 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:38</t>
+        </is>
+      </c>
+      <c r="AC204" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22626,6 +22635,7 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
+      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -22644,10 +22654,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>133582038</v>
+        <v>133582025</v>
       </c>
       <c r="B205" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22655,21 +22665,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22679,10 +22689,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>484815</v>
+        <v>485061</v>
       </c>
       <c r="R205" t="n">
-        <v>7086160</v>
+        <v>7086190</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22714,7 +22724,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22724,12 +22734,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>17:04</t>
-        </is>
-      </c>
-      <c r="AC205" t="inlineStr">
-        <is>
-          <t>Ringhack färska och äldre</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22756,10 +22761,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>133582039</v>
+        <v>133582157</v>
       </c>
       <c r="B206" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22767,21 +22772,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22791,10 +22796,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>484820</v>
+        <v>484872</v>
       </c>
       <c r="R206" t="n">
-        <v>7086145</v>
+        <v>7086175</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22826,7 +22831,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22836,12 +22841,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24483,32 +24483,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>133582081</v>
+        <v>133582186</v>
       </c>
       <c r="B222" t="n">
-        <v>79334</v>
+        <v>80399</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24518,10 +24518,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>485108</v>
+        <v>484668</v>
       </c>
       <c r="R222" t="n">
-        <v>7086096</v>
+        <v>7085980</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24553,7 +24553,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24590,7 +24590,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>133582053</v>
+        <v>133582081</v>
       </c>
       <c r="B223" t="n">
         <v>79334</v>
@@ -24625,10 +24625,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>484633</v>
+        <v>485108</v>
       </c>
       <c r="R223" t="n">
-        <v>7085966</v>
+        <v>7086096</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24660,7 +24660,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24670,7 +24670,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24697,32 +24697,32 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>133582254</v>
+        <v>133582053</v>
       </c>
       <c r="B224" t="n">
-        <v>79493</v>
+        <v>79334</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -24732,10 +24732,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>485098</v>
+        <v>484633</v>
       </c>
       <c r="R224" t="n">
-        <v>7086073</v>
+        <v>7085966</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24767,7 +24767,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24777,7 +24777,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24804,32 +24804,32 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>133582112</v>
+        <v>133582254</v>
       </c>
       <c r="B225" t="n">
-        <v>80439</v>
+        <v>79493</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24839,10 +24839,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>485199</v>
+        <v>485098</v>
       </c>
       <c r="R225" t="n">
-        <v>7086220</v>
+        <v>7086073</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24911,7 +24911,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>133582126</v>
+        <v>133582112</v>
       </c>
       <c r="B226" t="n">
         <v>80439</v>
@@ -24946,10 +24946,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>485151</v>
+        <v>485199</v>
       </c>
       <c r="R226" t="n">
-        <v>7086178</v>
+        <v>7086220</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25018,7 +25018,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>133582215</v>
+        <v>133582126</v>
       </c>
       <c r="B227" t="n">
         <v>80439</v>
@@ -25053,10 +25053,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>484868</v>
+        <v>485151</v>
       </c>
       <c r="R227" t="n">
-        <v>7086047</v>
+        <v>7086178</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25088,7 +25088,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25125,32 +25125,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>133582186</v>
+        <v>133582215</v>
       </c>
       <c r="B228" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25160,10 +25160,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>484668</v>
+        <v>484868</v>
       </c>
       <c r="R228" t="n">
-        <v>7085980</v>
+        <v>7086047</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25205,7 +25205,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD228" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -4920,32 +4920,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133582091</v>
+        <v>133582202</v>
       </c>
       <c r="B41" t="n">
-        <v>80439</v>
+        <v>75361</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>229654</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>484893</v>
+        <v>484604</v>
       </c>
       <c r="R41" t="n">
-        <v>7086018</v>
+        <v>7086021</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5000,7 +5000,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På en rönn, kunde enbart se två bålar med skrovellav. Varav ena hade en skrovellavsknapp växande på sig!</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5027,7 +5032,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133582072</v>
+        <v>133582091</v>
       </c>
       <c r="B42" t="n">
         <v>80439</v>
@@ -5062,10 +5067,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484979</v>
+        <v>484893</v>
       </c>
       <c r="R42" t="n">
-        <v>7086133</v>
+        <v>7086018</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5097,7 +5102,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5107,7 +5112,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5134,7 +5139,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133582268</v>
+        <v>133582072</v>
       </c>
       <c r="B43" t="n">
         <v>80439</v>
@@ -5169,10 +5174,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>484974</v>
+        <v>484979</v>
       </c>
       <c r="R43" t="n">
-        <v>7086064</v>
+        <v>7086133</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5204,7 +5209,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5214,7 +5219,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5241,7 +5246,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133582198</v>
+        <v>133582268</v>
       </c>
       <c r="B44" t="n">
         <v>80439</v>
@@ -5276,10 +5281,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484719</v>
+        <v>484974</v>
       </c>
       <c r="R44" t="n">
-        <v>7085978</v>
+        <v>7086064</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5311,7 +5316,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5321,7 +5326,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5348,7 +5353,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133582059</v>
+        <v>133582198</v>
       </c>
       <c r="B45" t="n">
         <v>80439</v>
@@ -5383,10 +5388,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>484703</v>
+        <v>484719</v>
       </c>
       <c r="R45" t="n">
-        <v>7085994</v>
+        <v>7085978</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5418,7 +5423,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5428,7 +5433,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5455,32 +5460,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133582202</v>
+        <v>133582059</v>
       </c>
       <c r="B46" t="n">
-        <v>75361</v>
+        <v>80439</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>229654</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5490,10 +5495,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>484604</v>
+        <v>484703</v>
       </c>
       <c r="R46" t="n">
-        <v>7086021</v>
+        <v>7085994</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5525,7 +5530,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5535,12 +5540,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På en rönn, kunde enbart se två bålar med skrovellav. Varav ena hade en skrovellavsknapp växande på sig!</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -7412,32 +7412,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133582239</v>
+        <v>133582146</v>
       </c>
       <c r="B64" t="n">
-        <v>79493</v>
+        <v>80399</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>485081</v>
+        <v>485019</v>
       </c>
       <c r="R64" t="n">
-        <v>7086147</v>
+        <v>7086200</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7519,10 +7519,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133582288</v>
+        <v>133582124</v>
       </c>
       <c r="B65" t="n">
-        <v>92651</v>
+        <v>80399</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7530,21 +7530,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>484904</v>
+        <v>485137</v>
       </c>
       <c r="R65" t="n">
-        <v>7085957</v>
+        <v>7086195</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7626,32 +7626,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133582249</v>
+        <v>133582049</v>
       </c>
       <c r="B66" t="n">
-        <v>83183</v>
+        <v>80399</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>485150</v>
+        <v>484616</v>
       </c>
       <c r="R66" t="n">
-        <v>7086053</v>
+        <v>7085997</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8161,32 +8161,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133582146</v>
+        <v>133582239</v>
       </c>
       <c r="B71" t="n">
-        <v>80399</v>
+        <v>79493</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>485019</v>
+        <v>485081</v>
       </c>
       <c r="R71" t="n">
-        <v>7086200</v>
+        <v>7086147</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8268,10 +8268,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133582124</v>
+        <v>133582288</v>
       </c>
       <c r="B72" t="n">
-        <v>80399</v>
+        <v>92651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>485137</v>
+        <v>484904</v>
       </c>
       <c r="R72" t="n">
-        <v>7086195</v>
+        <v>7085957</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8375,32 +8375,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133582049</v>
+        <v>133582249</v>
       </c>
       <c r="B73" t="n">
-        <v>80399</v>
+        <v>83183</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>484616</v>
+        <v>485150</v>
       </c>
       <c r="R73" t="n">
-        <v>7085997</v>
+        <v>7086053</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10005,32 +10005,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>133582082</v>
+        <v>133582280</v>
       </c>
       <c r="B88" t="n">
-        <v>89310</v>
+        <v>92651</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>510</v>
+        <v>3298</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10040,10 +10040,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>485082</v>
+        <v>484906</v>
       </c>
       <c r="R88" t="n">
-        <v>7086105</v>
+        <v>7086016</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10112,32 +10112,32 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>133582280</v>
+        <v>133582067</v>
       </c>
       <c r="B89" t="n">
-        <v>92651</v>
+        <v>79493</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>3298</v>
+        <v>1249</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10147,10 +10147,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>484906</v>
+        <v>484880</v>
       </c>
       <c r="R89" t="n">
-        <v>7086016</v>
+        <v>7086089</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10182,7 +10182,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -10192,7 +10192,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10219,32 +10219,32 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>133582067</v>
+        <v>133582109</v>
       </c>
       <c r="B90" t="n">
-        <v>79493</v>
+        <v>91928</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10254,10 +10254,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>484880</v>
+        <v>485213</v>
       </c>
       <c r="R90" t="n">
-        <v>7086089</v>
+        <v>7086209</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10299,7 +10299,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10326,10 +10326,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>133582052</v>
+        <v>133582082</v>
       </c>
       <c r="B91" t="n">
-        <v>80439</v>
+        <v>89310</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10337,21 +10337,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10361,10 +10361,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>484630</v>
+        <v>485082</v>
       </c>
       <c r="R91" t="n">
-        <v>7085961</v>
+        <v>7086105</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10396,7 +10396,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10433,10 +10433,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>133582057</v>
+        <v>133582018</v>
       </c>
       <c r="B92" t="n">
-        <v>80439</v>
+        <v>91928</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10444,21 +10444,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10468,10 +10468,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>484692</v>
+        <v>485198</v>
       </c>
       <c r="R92" t="n">
-        <v>7085987</v>
+        <v>7086232</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10503,7 +10503,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10513,12 +10513,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>17:50</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10545,7 +10540,7 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>133582172</v>
+        <v>133582052</v>
       </c>
       <c r="B93" t="n">
         <v>80439</v>
@@ -10580,10 +10575,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>484634</v>
+        <v>484630</v>
       </c>
       <c r="R93" t="n">
-        <v>7086020</v>
+        <v>7085961</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10615,7 +10610,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10625,7 +10620,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10652,7 +10647,7 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>133582235</v>
+        <v>133582057</v>
       </c>
       <c r="B94" t="n">
         <v>80439</v>
@@ -10687,10 +10682,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>485030</v>
+        <v>484692</v>
       </c>
       <c r="R94" t="n">
-        <v>7086138</v>
+        <v>7085987</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10722,7 +10717,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10732,7 +10727,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10759,32 +10759,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>133582100</v>
+        <v>133582172</v>
       </c>
       <c r="B95" t="n">
-        <v>80468</v>
+        <v>80439</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10794,10 +10794,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>484979</v>
+        <v>484634</v>
       </c>
       <c r="R95" t="n">
-        <v>7085799</v>
+        <v>7086020</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10829,7 +10829,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10839,7 +10839,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10866,7 +10866,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133582282</v>
+        <v>133582235</v>
       </c>
       <c r="B96" t="n">
         <v>80439</v>
@@ -10901,10 +10901,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>484917</v>
+        <v>485030</v>
       </c>
       <c r="R96" t="n">
-        <v>7086029</v>
+        <v>7086138</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10973,32 +10973,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133582109</v>
+        <v>133582100</v>
       </c>
       <c r="B97" t="n">
-        <v>91928</v>
+        <v>80468</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11008,10 +11008,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>485213</v>
+        <v>484979</v>
       </c>
       <c r="R97" t="n">
-        <v>7086209</v>
+        <v>7085799</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11080,10 +11080,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133582018</v>
+        <v>133582282</v>
       </c>
       <c r="B98" t="n">
-        <v>91928</v>
+        <v>80439</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11091,21 +11091,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>485198</v>
+        <v>484917</v>
       </c>
       <c r="R98" t="n">
-        <v>7086232</v>
+        <v>7086029</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -13225,65 +13225,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133582153</v>
+        <v>133582022</v>
       </c>
       <c r="B118" t="n">
-        <v>57958</v>
+        <v>92153</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>484961</v>
+        <v>485091</v>
       </c>
       <c r="R118" t="n">
-        <v>7086205</v>
+        <v>7086182</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13315,7 +13295,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13325,20 +13305,16 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Trummande och födosökande</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13357,45 +13333,65 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133582022</v>
+        <v>133582153</v>
       </c>
       <c r="B119" t="n">
-        <v>92153</v>
+        <v>57958</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>485091</v>
+        <v>484961</v>
       </c>
       <c r="R119" t="n">
-        <v>7086182</v>
+        <v>7086205</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13427,7 +13423,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13437,16 +13433,20 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Trummande och födosökande</t>
         </is>
       </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF119" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -18216,10 +18216,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>133582311</v>
+        <v>133582130</v>
       </c>
       <c r="B164" t="n">
-        <v>91942</v>
+        <v>91924</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18227,21 +18227,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>1204</v>
+        <v>1108</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18251,10 +18251,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>484937</v>
+        <v>485082</v>
       </c>
       <c r="R164" t="n">
-        <v>7086009</v>
+        <v>7086189</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18296,7 +18296,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18323,10 +18323,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>133582119</v>
+        <v>133582311</v>
       </c>
       <c r="B165" t="n">
-        <v>79334</v>
+        <v>91942</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18334,21 +18334,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -18358,10 +18358,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>485161</v>
+        <v>484937</v>
       </c>
       <c r="R165" t="n">
-        <v>7086201</v>
+        <v>7086009</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -18393,7 +18393,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18403,7 +18403,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18430,10 +18430,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>133582019</v>
+        <v>133582119</v>
       </c>
       <c r="B166" t="n">
-        <v>91942</v>
+        <v>79334</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18441,21 +18441,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -18465,10 +18465,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>485182</v>
+        <v>485161</v>
       </c>
       <c r="R166" t="n">
-        <v>7086232</v>
+        <v>7086201</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="Z166" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -18510,7 +18510,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18537,10 +18537,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>133582257</v>
+        <v>133582019</v>
       </c>
       <c r="B167" t="n">
-        <v>80439</v>
+        <v>91942</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -18548,21 +18548,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -18572,10 +18572,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>485063</v>
+        <v>485182</v>
       </c>
       <c r="R167" t="n">
-        <v>7086069</v>
+        <v>7086232</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -18617,7 +18617,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -18644,7 +18644,7 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>133582196</v>
+        <v>133582257</v>
       </c>
       <c r="B168" t="n">
         <v>80439</v>
@@ -18679,10 +18679,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>484701</v>
+        <v>485063</v>
       </c>
       <c r="R168" t="n">
-        <v>7085982</v>
+        <v>7086069</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18714,7 +18714,7 @@
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -18724,7 +18724,7 @@
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -18751,7 +18751,7 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>133582160</v>
+        <v>133582196</v>
       </c>
       <c r="B169" t="n">
         <v>80439</v>
@@ -18786,10 +18786,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>484827</v>
+        <v>484701</v>
       </c>
       <c r="R169" t="n">
-        <v>7086151</v>
+        <v>7085982</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -18821,7 +18821,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -18831,7 +18831,7 @@
       </c>
       <c r="AB169" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -18858,10 +18858,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>133582130</v>
+        <v>133582160</v>
       </c>
       <c r="B170" t="n">
-        <v>91924</v>
+        <v>80439</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -18869,21 +18869,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -18893,10 +18893,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>485082</v>
+        <v>484827</v>
       </c>
       <c r="R170" t="n">
-        <v>7086189</v>
+        <v>7086151</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -18928,7 +18928,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -18938,7 +18938,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -20687,32 +20687,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133582237</v>
+        <v>133582263</v>
       </c>
       <c r="B187" t="n">
-        <v>80439</v>
+        <v>79493</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20722,10 +20722,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>485067</v>
+        <v>484998</v>
       </c>
       <c r="R187" t="n">
-        <v>7086146</v>
+        <v>7086055</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20767,7 +20767,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20794,32 +20794,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133582300</v>
+        <v>133582066</v>
       </c>
       <c r="B188" t="n">
-        <v>80474</v>
+        <v>91928</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20829,10 +20829,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>484976</v>
+        <v>484881</v>
       </c>
       <c r="R188" t="n">
-        <v>7085795</v>
+        <v>7086060</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20864,7 +20864,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20901,10 +20901,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133582208</v>
+        <v>133582298</v>
       </c>
       <c r="B189" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20912,21 +20912,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20936,10 +20936,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>484791</v>
+        <v>484895</v>
       </c>
       <c r="R189" t="n">
-        <v>7085988</v>
+        <v>7085846</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20971,7 +20971,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20981,7 +20981,12 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Rikligt &gt; 1000 bålar</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21008,7 +21013,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133582048</v>
+        <v>133582237</v>
       </c>
       <c r="B190" t="n">
         <v>80439</v>
@@ -21037,23 +21042,16 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>484618</v>
+        <v>485067</v>
       </c>
       <c r="R190" t="n">
-        <v>7085997</v>
+        <v>7086146</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21085,7 +21083,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21095,12 +21093,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21109,7 +21102,6 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
-      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
@@ -21128,32 +21120,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133582225</v>
+        <v>133582300</v>
       </c>
       <c r="B191" t="n">
-        <v>80439</v>
+        <v>80474</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21163,10 +21155,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>484969</v>
+        <v>484976</v>
       </c>
       <c r="R191" t="n">
-        <v>7086169</v>
+        <v>7085795</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21198,7 +21190,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21208,7 +21200,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21235,32 +21227,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133582263</v>
+        <v>133582208</v>
       </c>
       <c r="B192" t="n">
-        <v>79493</v>
+        <v>80439</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21270,10 +21262,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>484998</v>
+        <v>484791</v>
       </c>
       <c r="R192" t="n">
-        <v>7086055</v>
+        <v>7085988</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21305,7 +21297,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21315,7 +21307,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21342,10 +21334,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133582066</v>
+        <v>133582048</v>
       </c>
       <c r="B193" t="n">
-        <v>91928</v>
+        <v>80439</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21353,34 +21345,41 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>484881</v>
+        <v>484618</v>
       </c>
       <c r="R193" t="n">
-        <v>7086060</v>
+        <v>7085997</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21412,7 +21411,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21422,7 +21421,12 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21431,6 +21435,7 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -21449,10 +21454,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133582298</v>
+        <v>133582225</v>
       </c>
       <c r="B194" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21460,21 +21465,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21484,10 +21489,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>484895</v>
+        <v>484969</v>
       </c>
       <c r="R194" t="n">
-        <v>7085846</v>
+        <v>7086169</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21519,7 +21524,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21529,12 +21534,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>20:50</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Rikligt &gt; 1000 bålar</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -22868,10 +22868,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>133582296</v>
+        <v>133582173</v>
       </c>
       <c r="B207" t="n">
-        <v>80439</v>
+        <v>80440</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -22879,21 +22879,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -22903,10 +22903,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>484845</v>
+        <v>484630</v>
       </c>
       <c r="R207" t="n">
-        <v>7085934</v>
+        <v>7086019</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -22938,7 +22938,7 @@
       </c>
       <c r="Z207" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA207" t="inlineStr">
@@ -22948,7 +22948,7 @@
       </c>
       <c r="AB207" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD207" t="b">
@@ -22975,10 +22975,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>133582051</v>
+        <v>133582092</v>
       </c>
       <c r="B208" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -22986,21 +22986,21 @@
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -23010,10 +23010,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>484623</v>
+        <v>484910</v>
       </c>
       <c r="R208" t="n">
-        <v>7085960</v>
+        <v>7085990</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -23045,7 +23045,7 @@
       </c>
       <c r="Z208" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:37</t>
         </is>
       </c>
       <c r="AA208" t="inlineStr">
@@ -23055,7 +23055,12 @@
       </c>
       <c r="AB208" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:37</t>
+        </is>
+      </c>
+      <c r="AC208" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD208" t="b">
@@ -23082,10 +23087,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>133582122</v>
+        <v>133582056</v>
       </c>
       <c r="B209" t="n">
-        <v>80439</v>
+        <v>91942</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -23093,21 +23098,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -23117,10 +23122,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>485143</v>
+        <v>484670</v>
       </c>
       <c r="R209" t="n">
-        <v>7086201</v>
+        <v>7085973</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -23152,7 +23157,7 @@
       </c>
       <c r="Z209" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA209" t="inlineStr">
@@ -23162,7 +23167,7 @@
       </c>
       <c r="AB209" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD209" t="b">
@@ -23189,10 +23194,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>133582204</v>
+        <v>133582149</v>
       </c>
       <c r="B210" t="n">
-        <v>80474</v>
+        <v>92651</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -23200,21 +23205,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>6463</v>
+        <v>3298</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -23224,10 +23229,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>484777</v>
+        <v>484989</v>
       </c>
       <c r="R210" t="n">
-        <v>7085989</v>
+        <v>7086182</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -23259,7 +23264,7 @@
       </c>
       <c r="Z210" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AA210" t="inlineStr">
@@ -23269,7 +23274,7 @@
       </c>
       <c r="AB210" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:33</t>
         </is>
       </c>
       <c r="AD210" t="b">
@@ -23296,10 +23301,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>133582047</v>
+        <v>133582252</v>
       </c>
       <c r="B211" t="n">
-        <v>80439</v>
+        <v>80440</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -23307,21 +23312,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -23331,10 +23336,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>484606</v>
+        <v>485119</v>
       </c>
       <c r="R211" t="n">
-        <v>7085997</v>
+        <v>7086079</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -23366,7 +23371,7 @@
       </c>
       <c r="Z211" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA211" t="inlineStr">
@@ -23376,7 +23381,7 @@
       </c>
       <c r="AB211" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -23403,32 +23408,32 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>133582229</v>
+        <v>133582190</v>
       </c>
       <c r="B212" t="n">
-        <v>80439</v>
+        <v>79493</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E212" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -23438,10 +23443,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>484994</v>
+        <v>484688</v>
       </c>
       <c r="R212" t="n">
-        <v>7086157</v>
+        <v>7085978</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -23473,7 +23478,7 @@
       </c>
       <c r="Z212" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA212" t="inlineStr">
@@ -23483,7 +23488,7 @@
       </c>
       <c r="AB212" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD212" t="b">
@@ -23510,32 +23515,32 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>133582301</v>
+        <v>133582212</v>
       </c>
       <c r="B213" t="n">
-        <v>80439</v>
+        <v>91891</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -23545,10 +23550,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>485003</v>
+        <v>484829</v>
       </c>
       <c r="R213" t="n">
-        <v>7085818</v>
+        <v>7085996</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -23580,7 +23585,7 @@
       </c>
       <c r="Z213" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA213" t="inlineStr">
@@ -23590,7 +23595,7 @@
       </c>
       <c r="AB213" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD213" t="b">
@@ -23617,10 +23622,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>133582173</v>
+        <v>133582097</v>
       </c>
       <c r="B214" t="n">
-        <v>80440</v>
+        <v>57958</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23628,21 +23633,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23652,10 +23657,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>484630</v>
+        <v>484907</v>
       </c>
       <c r="R214" t="n">
-        <v>7086019</v>
+        <v>7085829</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23687,7 +23692,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23697,7 +23702,12 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23724,10 +23734,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>133582092</v>
+        <v>133582296</v>
       </c>
       <c r="B215" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -23735,21 +23745,21 @@
         </is>
       </c>
       <c r="E215" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -23759,10 +23769,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>484910</v>
+        <v>484845</v>
       </c>
       <c r="R215" t="n">
-        <v>7085990</v>
+        <v>7085934</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23794,7 +23804,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>20:37</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23804,12 +23814,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>20:37</t>
-        </is>
-      </c>
-      <c r="AC215" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23836,10 +23841,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>133582056</v>
+        <v>133582051</v>
       </c>
       <c r="B216" t="n">
-        <v>91942</v>
+        <v>80439</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -23847,21 +23852,21 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -23871,10 +23876,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>484670</v>
+        <v>484623</v>
       </c>
       <c r="R216" t="n">
-        <v>7085973</v>
+        <v>7085960</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23906,7 +23911,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23916,7 +23921,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23943,32 +23948,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>133582149</v>
+        <v>133582122</v>
       </c>
       <c r="B217" t="n">
-        <v>92651</v>
+        <v>80439</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23978,10 +23983,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>484989</v>
+        <v>485143</v>
       </c>
       <c r="R217" t="n">
-        <v>7086182</v>
+        <v>7086201</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24013,7 +24018,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24023,7 +24028,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>16:33</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24050,32 +24055,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>133582252</v>
+        <v>133582204</v>
       </c>
       <c r="B218" t="n">
-        <v>80440</v>
+        <v>80474</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>2081</v>
+        <v>6463</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24085,10 +24090,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>485119</v>
+        <v>484777</v>
       </c>
       <c r="R218" t="n">
-        <v>7086079</v>
+        <v>7085989</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24120,7 +24125,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24130,7 +24135,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>20:02</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24157,32 +24162,32 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>133582190</v>
+        <v>133582047</v>
       </c>
       <c r="B219" t="n">
-        <v>79493</v>
+        <v>80439</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E219" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -24192,10 +24197,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>484688</v>
+        <v>484606</v>
       </c>
       <c r="R219" t="n">
-        <v>7085978</v>
+        <v>7085997</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24227,7 +24232,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24237,7 +24242,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24264,32 +24269,32 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>133582212</v>
+        <v>133582229</v>
       </c>
       <c r="B220" t="n">
-        <v>91891</v>
+        <v>80439</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E220" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -24299,10 +24304,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>484829</v>
+        <v>484994</v>
       </c>
       <c r="R220" t="n">
-        <v>7085996</v>
+        <v>7086157</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24334,7 +24339,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -24344,7 +24349,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24371,10 +24376,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>133582097</v>
+        <v>133582301</v>
       </c>
       <c r="B221" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24382,21 +24387,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24406,10 +24411,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>484907</v>
+        <v>485003</v>
       </c>
       <c r="R221" t="n">
-        <v>7085829</v>
+        <v>7085818</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24441,7 +24446,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24451,12 +24456,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>20:51</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD221" t="b">
@@ -24483,32 +24483,32 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>133582254</v>
+        <v>133582186</v>
       </c>
       <c r="B222" t="n">
-        <v>79493</v>
+        <v>80399</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -24518,10 +24518,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>485098</v>
+        <v>484668</v>
       </c>
       <c r="R222" t="n">
-        <v>7086073</v>
+        <v>7085980</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -24553,7 +24553,7 @@
       </c>
       <c r="Z222" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -24563,7 +24563,7 @@
       </c>
       <c r="AB222" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -24590,32 +24590,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>133582081</v>
+        <v>133582254</v>
       </c>
       <c r="B223" t="n">
-        <v>79334</v>
+        <v>79493</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>6425</v>
+        <v>1249</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -24625,10 +24625,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>485108</v>
+        <v>485098</v>
       </c>
       <c r="R223" t="n">
-        <v>7086096</v>
+        <v>7086073</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24660,7 +24660,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24670,7 +24670,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24697,7 +24697,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>133582053</v>
+        <v>133582081</v>
       </c>
       <c r="B224" t="n">
         <v>79334</v>
@@ -24732,10 +24732,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>484633</v>
+        <v>485108</v>
       </c>
       <c r="R224" t="n">
-        <v>7085966</v>
+        <v>7086096</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24767,7 +24767,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24777,7 +24777,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24804,10 +24804,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>133582112</v>
+        <v>133582053</v>
       </c>
       <c r="B225" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -24815,21 +24815,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -24839,10 +24839,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>485199</v>
+        <v>484633</v>
       </c>
       <c r="R225" t="n">
-        <v>7086220</v>
+        <v>7085966</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>15:29</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24911,7 +24911,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>133582126</v>
+        <v>133582112</v>
       </c>
       <c r="B226" t="n">
         <v>80439</v>
@@ -24946,10 +24946,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>485151</v>
+        <v>485199</v>
       </c>
       <c r="R226" t="n">
-        <v>7086178</v>
+        <v>7086220</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25018,7 +25018,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>133582215</v>
+        <v>133582126</v>
       </c>
       <c r="B227" t="n">
         <v>80439</v>
@@ -25053,10 +25053,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>484868</v>
+        <v>485151</v>
       </c>
       <c r="R227" t="n">
-        <v>7086047</v>
+        <v>7086178</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25088,7 +25088,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25125,32 +25125,32 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>133582186</v>
+        <v>133582215</v>
       </c>
       <c r="B228" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -25160,10 +25160,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>484668</v>
+        <v>484868</v>
       </c>
       <c r="R228" t="n">
-        <v>7085980</v>
+        <v>7086047</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25205,7 +25205,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD228" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133582136</v>
+        <v>133582217</v>
       </c>
       <c r="B2" t="n">
-        <v>79493</v>
+        <v>80439</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>485044</v>
+        <v>484892</v>
       </c>
       <c r="R2" t="n">
-        <v>7086195</v>
+        <v>7086073</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133582307</v>
+        <v>133582295</v>
       </c>
       <c r="B3" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>485011</v>
+        <v>484865</v>
       </c>
       <c r="R3" t="n">
-        <v>7085969</v>
+        <v>7085940</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>21:05</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;1000 bålar</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133582217</v>
+        <v>133582161</v>
       </c>
       <c r="B4" t="n">
         <v>80439</v>
@@ -929,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484892</v>
+        <v>484823</v>
       </c>
       <c r="R4" t="n">
-        <v>7086073</v>
+        <v>7086116</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,7 +996,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133582295</v>
+        <v>133582180</v>
       </c>
       <c r="B5" t="n">
         <v>80439</v>
@@ -1036,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484865</v>
+        <v>484629</v>
       </c>
       <c r="R5" t="n">
-        <v>7085940</v>
+        <v>7086008</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133582161</v>
+        <v>133582210</v>
       </c>
       <c r="B6" t="n">
-        <v>80439</v>
+        <v>91928</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484823</v>
+        <v>484827</v>
       </c>
       <c r="R6" t="n">
-        <v>7086116</v>
+        <v>7085987</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1178,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133582180</v>
+        <v>133582080</v>
       </c>
       <c r="B7" t="n">
-        <v>80439</v>
+        <v>91924</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1108</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>484629</v>
+        <v>485117</v>
       </c>
       <c r="R7" t="n">
-        <v>7086008</v>
+        <v>7086099</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,32 +1317,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133582210</v>
+        <v>133582136</v>
       </c>
       <c r="B8" t="n">
-        <v>91928</v>
+        <v>79493</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1249</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>484827</v>
+        <v>485044</v>
       </c>
       <c r="R8" t="n">
-        <v>7085987</v>
+        <v>7086195</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1392,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1424,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133582080</v>
+        <v>133582307</v>
       </c>
       <c r="B9" t="n">
-        <v>91924</v>
+        <v>79334</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,21 +1435,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1464,10 +1459,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485117</v>
+        <v>485011</v>
       </c>
       <c r="R9" t="n">
-        <v>7086099</v>
+        <v>7085969</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,7 +1494,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,7 +1504,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;1000 bålar</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -4920,32 +4920,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133582202</v>
+        <v>133582091</v>
       </c>
       <c r="B41" t="n">
-        <v>75361</v>
+        <v>80439</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>229654</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Skrovellavsknapp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Plectocarpon scrobiculatae</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Diederich &amp; Etayo</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4955,10 +4955,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>484604</v>
+        <v>484893</v>
       </c>
       <c r="R41" t="n">
-        <v>7086021</v>
+        <v>7086018</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>17:59</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5000,12 +5000,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>17:59</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På en rönn, kunde enbart se två bålar med skrovellav. Varav ena hade en skrovellavsknapp växande på sig!</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5032,7 +5027,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133582091</v>
+        <v>133582072</v>
       </c>
       <c r="B42" t="n">
         <v>80439</v>
@@ -5067,10 +5062,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484893</v>
+        <v>484979</v>
       </c>
       <c r="R42" t="n">
-        <v>7086018</v>
+        <v>7086133</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5102,7 +5097,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5112,7 +5107,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5139,7 +5134,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133582072</v>
+        <v>133582268</v>
       </c>
       <c r="B43" t="n">
         <v>80439</v>
@@ -5174,10 +5169,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>484979</v>
+        <v>484974</v>
       </c>
       <c r="R43" t="n">
-        <v>7086133</v>
+        <v>7086064</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5209,7 +5204,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5219,7 +5214,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5246,7 +5241,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133582268</v>
+        <v>133582198</v>
       </c>
       <c r="B44" t="n">
         <v>80439</v>
@@ -5281,10 +5276,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484974</v>
+        <v>484719</v>
       </c>
       <c r="R44" t="n">
-        <v>7086064</v>
+        <v>7085978</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5316,7 +5311,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5326,7 +5321,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5353,7 +5348,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133582198</v>
+        <v>133582059</v>
       </c>
       <c r="B45" t="n">
         <v>80439</v>
@@ -5388,10 +5383,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>484719</v>
+        <v>484703</v>
       </c>
       <c r="R45" t="n">
-        <v>7085978</v>
+        <v>7085994</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5423,7 +5418,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5433,7 +5428,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5460,32 +5455,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133582059</v>
+        <v>133582202</v>
       </c>
       <c r="B46" t="n">
-        <v>80439</v>
+        <v>75361</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>229654</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellavsknapp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Plectocarpon scrobiculatae</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Diederich &amp; Etayo</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5495,10 +5490,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>484703</v>
+        <v>484604</v>
       </c>
       <c r="R46" t="n">
-        <v>7085994</v>
+        <v>7086021</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,7 +5525,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:59</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5540,7 +5535,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>17:59</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en rönn, kunde enbart se två bålar med skrovellav. Varav ena hade en skrovellavsknapp växande på sig!</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -11294,10 +11294,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133582163</v>
+        <v>133582042</v>
       </c>
       <c r="B100" t="n">
-        <v>91942</v>
+        <v>57958</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11305,21 +11305,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11329,10 +11329,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>484703</v>
+        <v>484762</v>
       </c>
       <c r="R100" t="n">
-        <v>7086043</v>
+        <v>7086084</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11374,7 +11374,12 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11401,32 +11406,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133582105</v>
+        <v>133582163</v>
       </c>
       <c r="B101" t="n">
-        <v>92651</v>
+        <v>91942</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11436,10 +11441,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>485150</v>
+        <v>484703</v>
       </c>
       <c r="R101" t="n">
-        <v>7085949</v>
+        <v>7086043</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11471,7 +11476,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11481,7 +11486,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11508,32 +11513,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133582234</v>
+        <v>133582105</v>
       </c>
       <c r="B102" t="n">
-        <v>91942</v>
+        <v>92651</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11543,10 +11548,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>485009</v>
+        <v>485150</v>
       </c>
       <c r="R102" t="n">
-        <v>7086144</v>
+        <v>7085949</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11578,7 +11583,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11588,7 +11593,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11615,10 +11620,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133582042</v>
+        <v>133582234</v>
       </c>
       <c r="B103" t="n">
-        <v>57958</v>
+        <v>91942</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11626,21 +11631,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11650,10 +11655,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>484762</v>
+        <v>485009</v>
       </c>
       <c r="R103" t="n">
-        <v>7086084</v>
+        <v>7086144</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11685,7 +11690,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11695,12 +11700,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11727,32 +11727,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133582179</v>
+        <v>133582233</v>
       </c>
       <c r="B104" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11762,10 +11762,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>484623</v>
+        <v>485025</v>
       </c>
       <c r="R104" t="n">
-        <v>7086004</v>
+        <v>7086137</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11834,7 +11834,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133582233</v>
+        <v>133582224</v>
       </c>
       <c r="B105" t="n">
         <v>80439</v>
@@ -11869,10 +11869,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>485025</v>
+        <v>484963</v>
       </c>
       <c r="R105" t="n">
-        <v>7086137</v>
+        <v>7086155</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11904,7 +11904,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11941,7 +11941,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133582224</v>
+        <v>133582145</v>
       </c>
       <c r="B106" t="n">
         <v>80439</v>
@@ -11976,10 +11976,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>484963</v>
+        <v>485022</v>
       </c>
       <c r="R106" t="n">
-        <v>7086155</v>
+        <v>7086194</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12048,7 +12048,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133582145</v>
+        <v>133582144</v>
       </c>
       <c r="B107" t="n">
         <v>80439</v>
@@ -12083,10 +12083,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>485022</v>
+        <v>485024</v>
       </c>
       <c r="R107" t="n">
-        <v>7086194</v>
+        <v>7086180</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12118,7 +12118,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12155,7 +12155,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133582144</v>
+        <v>133582255</v>
       </c>
       <c r="B108" t="n">
         <v>80439</v>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>485024</v>
+        <v>485082</v>
       </c>
       <c r="R108" t="n">
-        <v>7086180</v>
+        <v>7086082</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12262,7 +12262,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133582255</v>
+        <v>133582034</v>
       </c>
       <c r="B109" t="n">
         <v>80439</v>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>485082</v>
+        <v>484996</v>
       </c>
       <c r="R109" t="n">
-        <v>7086082</v>
+        <v>7086209</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12369,7 +12369,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133582034</v>
+        <v>133582195</v>
       </c>
       <c r="B110" t="n">
         <v>80439</v>
@@ -12404,10 +12404,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>484996</v>
+        <v>484677</v>
       </c>
       <c r="R110" t="n">
-        <v>7086209</v>
+        <v>7085977</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12476,7 +12476,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133582195</v>
+        <v>133582188</v>
       </c>
       <c r="B111" t="n">
         <v>80439</v>
@@ -12511,10 +12511,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>484677</v>
+        <v>484675</v>
       </c>
       <c r="R111" t="n">
-        <v>7085977</v>
+        <v>7085987</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12583,7 +12583,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133582188</v>
+        <v>133582184</v>
       </c>
       <c r="B112" t="n">
         <v>80439</v>
@@ -12618,10 +12618,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>484675</v>
+        <v>484657</v>
       </c>
       <c r="R112" t="n">
-        <v>7085987</v>
+        <v>7085984</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12690,32 +12690,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133582184</v>
+        <v>133582179</v>
       </c>
       <c r="B113" t="n">
-        <v>80439</v>
+        <v>80399</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12725,10 +12725,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>484657</v>
+        <v>484623</v>
       </c>
       <c r="R113" t="n">
-        <v>7085984</v>
+        <v>7086004</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12760,7 +12760,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13465,32 +13465,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133582075</v>
+        <v>133582133</v>
       </c>
       <c r="B120" t="n">
-        <v>91928</v>
+        <v>80474</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485160</v>
+        <v>485084</v>
       </c>
       <c r="R120" t="n">
-        <v>7086132</v>
+        <v>7086179</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13572,32 +13572,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133582211</v>
+        <v>133582026</v>
       </c>
       <c r="B121" t="n">
-        <v>92624</v>
+        <v>80439</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>484833</v>
+        <v>485057</v>
       </c>
       <c r="R121" t="n">
-        <v>7085991</v>
+        <v>7086210</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13679,32 +13679,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133582044</v>
+        <v>133582185</v>
       </c>
       <c r="B122" t="n">
-        <v>92624</v>
+        <v>80439</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>484638</v>
+        <v>484663</v>
       </c>
       <c r="R122" t="n">
-        <v>7086023</v>
+        <v>7085977</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13898,32 +13898,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133582230</v>
+        <v>133582116</v>
       </c>
       <c r="B124" t="n">
-        <v>80399</v>
+        <v>79493</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13933,10 +13933,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485000</v>
+        <v>485168</v>
       </c>
       <c r="R124" t="n">
-        <v>7086155</v>
+        <v>7086214</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14005,32 +14005,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133582205</v>
+        <v>133582314</v>
       </c>
       <c r="B125" t="n">
-        <v>80399</v>
+        <v>79334</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14040,10 +14040,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>484779</v>
+        <v>485031</v>
       </c>
       <c r="R125" t="n">
-        <v>7085989</v>
+        <v>7085985</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14075,7 +14075,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14085,7 +14085,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14112,32 +14117,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133582101</v>
+        <v>133582162</v>
       </c>
       <c r="B126" t="n">
-        <v>80399</v>
+        <v>79493</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14147,10 +14152,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>484978</v>
+        <v>484794</v>
       </c>
       <c r="R126" t="n">
-        <v>7085798</v>
+        <v>7086094</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14182,7 +14187,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14192,7 +14197,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14219,32 +14224,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133582116</v>
+        <v>133582085</v>
       </c>
       <c r="B127" t="n">
-        <v>79493</v>
+        <v>91942</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14254,10 +14259,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>485168</v>
+        <v>484920</v>
       </c>
       <c r="R127" t="n">
-        <v>7086214</v>
+        <v>7086079</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14289,7 +14294,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14299,7 +14304,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14326,10 +14331,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133582314</v>
+        <v>133582075</v>
       </c>
       <c r="B128" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14337,21 +14342,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14361,10 +14366,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485031</v>
+        <v>485160</v>
       </c>
       <c r="R128" t="n">
-        <v>7085985</v>
+        <v>7086132</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14396,7 +14401,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14406,12 +14411,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>21:13</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14438,10 +14438,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133582162</v>
+        <v>133582211</v>
       </c>
       <c r="B129" t="n">
-        <v>79493</v>
+        <v>92624</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14449,21 +14449,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1249</v>
+        <v>898</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14473,10 +14473,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>484794</v>
+        <v>484833</v>
       </c>
       <c r="R129" t="n">
-        <v>7086094</v>
+        <v>7085991</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14545,32 +14545,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133582085</v>
+        <v>133582044</v>
       </c>
       <c r="B130" t="n">
-        <v>91942</v>
+        <v>92624</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14580,10 +14580,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>484920</v>
+        <v>484638</v>
       </c>
       <c r="R130" t="n">
-        <v>7086079</v>
+        <v>7086023</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14652,10 +14652,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133582133</v>
+        <v>133582230</v>
       </c>
       <c r="B131" t="n">
-        <v>80474</v>
+        <v>80399</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14663,21 +14663,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14687,10 +14687,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>485084</v>
+        <v>485000</v>
       </c>
       <c r="R131" t="n">
-        <v>7086179</v>
+        <v>7086155</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14722,7 +14722,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14759,32 +14759,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133582026</v>
+        <v>133582205</v>
       </c>
       <c r="B132" t="n">
-        <v>80439</v>
+        <v>80399</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14794,10 +14794,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>485057</v>
+        <v>484779</v>
       </c>
       <c r="R132" t="n">
-        <v>7086210</v>
+        <v>7085989</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14866,32 +14866,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133582185</v>
+        <v>133582101</v>
       </c>
       <c r="B133" t="n">
-        <v>80439</v>
+        <v>80399</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>484663</v>
+        <v>484978</v>
       </c>
       <c r="R133" t="n">
-        <v>7085977</v>
+        <v>7085798</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14973,10 +14973,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133582206</v>
+        <v>133582299</v>
       </c>
       <c r="B134" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14984,21 +14984,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>484786</v>
+        <v>484915</v>
       </c>
       <c r="R134" t="n">
-        <v>7085991</v>
+        <v>7085804</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15053,7 +15053,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15080,10 +15085,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133582266</v>
+        <v>133582220</v>
       </c>
       <c r="B135" t="n">
-        <v>80439</v>
+        <v>91942</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15091,21 +15096,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15115,10 +15120,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>484970</v>
+        <v>484884</v>
       </c>
       <c r="R135" t="n">
-        <v>7086056</v>
+        <v>7086115</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15150,7 +15155,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15160,7 +15165,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15187,10 +15192,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133582256</v>
+        <v>133582221</v>
       </c>
       <c r="B136" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15198,21 +15203,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15222,10 +15227,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>485049</v>
+        <v>484871</v>
       </c>
       <c r="R136" t="n">
-        <v>7086092</v>
+        <v>7086160</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15257,7 +15262,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15267,7 +15272,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15294,10 +15299,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133582086</v>
+        <v>133582168</v>
       </c>
       <c r="B137" t="n">
-        <v>80439</v>
+        <v>91942</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15305,21 +15310,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15329,10 +15334,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>484918</v>
+        <v>484620</v>
       </c>
       <c r="R137" t="n">
-        <v>7086067</v>
+        <v>7086031</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15364,7 +15369,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15374,7 +15379,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15401,7 +15406,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133582274</v>
+        <v>133582206</v>
       </c>
       <c r="B138" t="n">
         <v>80439</v>
@@ -15436,10 +15441,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>484927</v>
+        <v>484786</v>
       </c>
       <c r="R138" t="n">
-        <v>7086073</v>
+        <v>7085991</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15471,7 +15476,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15481,7 +15486,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15508,7 +15513,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133582073</v>
+        <v>133582266</v>
       </c>
       <c r="B139" t="n">
         <v>80439</v>
@@ -15543,10 +15548,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>484980</v>
+        <v>484970</v>
       </c>
       <c r="R139" t="n">
-        <v>7086124</v>
+        <v>7086056</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15578,7 +15583,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15588,12 +15593,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>18:34</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15620,10 +15620,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133582299</v>
+        <v>133582256</v>
       </c>
       <c r="B140" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15631,21 +15631,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>484915</v>
+        <v>485049</v>
       </c>
       <c r="R140" t="n">
-        <v>7085804</v>
+        <v>7086092</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15700,12 +15700,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15732,10 +15727,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133582220</v>
+        <v>133582086</v>
       </c>
       <c r="B141" t="n">
-        <v>91942</v>
+        <v>80439</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15743,21 +15738,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15767,10 +15762,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>484884</v>
+        <v>484918</v>
       </c>
       <c r="R141" t="n">
-        <v>7086115</v>
+        <v>7086067</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15802,7 +15797,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15812,7 +15807,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15839,10 +15834,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133582221</v>
+        <v>133582274</v>
       </c>
       <c r="B142" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15850,21 +15845,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15874,10 +15869,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>484871</v>
+        <v>484927</v>
       </c>
       <c r="R142" t="n">
-        <v>7086160</v>
+        <v>7086073</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15909,7 +15904,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15919,7 +15914,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15946,10 +15941,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133582168</v>
+        <v>133582073</v>
       </c>
       <c r="B143" t="n">
-        <v>91942</v>
+        <v>80439</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15957,21 +15952,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15981,10 +15976,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>484620</v>
+        <v>484980</v>
       </c>
       <c r="R143" t="n">
-        <v>7086031</v>
+        <v>7086124</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16016,7 +16011,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16026,7 +16021,12 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -23622,10 +23622,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>133582097</v>
+        <v>133582296</v>
       </c>
       <c r="B214" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23633,21 +23633,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23657,10 +23657,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>484907</v>
+        <v>484845</v>
       </c>
       <c r="R214" t="n">
-        <v>7085829</v>
+        <v>7085934</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23692,7 +23692,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23702,12 +23702,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>20:51</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23734,7 +23729,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>133582296</v>
+        <v>133582051</v>
       </c>
       <c r="B215" t="n">
         <v>80439</v>
@@ -23769,10 +23764,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>484845</v>
+        <v>484623</v>
       </c>
       <c r="R215" t="n">
-        <v>7085934</v>
+        <v>7085960</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23804,7 +23799,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23814,7 +23809,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23841,7 +23836,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>133582051</v>
+        <v>133582122</v>
       </c>
       <c r="B216" t="n">
         <v>80439</v>
@@ -23876,10 +23871,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>484623</v>
+        <v>485143</v>
       </c>
       <c r="R216" t="n">
-        <v>7085960</v>
+        <v>7086201</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23911,7 +23906,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23921,7 +23916,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23948,32 +23943,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>133582122</v>
+        <v>133582204</v>
       </c>
       <c r="B217" t="n">
-        <v>80439</v>
+        <v>80474</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23983,10 +23978,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>485143</v>
+        <v>484777</v>
       </c>
       <c r="R217" t="n">
-        <v>7086201</v>
+        <v>7085989</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24018,7 +24013,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24028,7 +24023,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24055,32 +24050,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>133582204</v>
+        <v>133582047</v>
       </c>
       <c r="B218" t="n">
-        <v>80474</v>
+        <v>80439</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24090,10 +24085,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>484777</v>
+        <v>484606</v>
       </c>
       <c r="R218" t="n">
-        <v>7085989</v>
+        <v>7085997</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24125,7 +24120,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24135,7 +24130,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24162,7 +24157,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>133582047</v>
+        <v>133582229</v>
       </c>
       <c r="B219" t="n">
         <v>80439</v>
@@ -24197,10 +24192,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>484606</v>
+        <v>484994</v>
       </c>
       <c r="R219" t="n">
-        <v>7085997</v>
+        <v>7086157</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24232,7 +24227,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24242,7 +24237,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24269,7 +24264,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>133582229</v>
+        <v>133582301</v>
       </c>
       <c r="B220" t="n">
         <v>80439</v>
@@ -24304,10 +24299,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>484994</v>
+        <v>485003</v>
       </c>
       <c r="R220" t="n">
-        <v>7086157</v>
+        <v>7085818</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24339,7 +24334,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -24349,7 +24344,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24376,10 +24371,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>133582301</v>
+        <v>133582097</v>
       </c>
       <c r="B221" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24387,21 +24382,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24411,10 +24406,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>485003</v>
+        <v>484907</v>
       </c>
       <c r="R221" t="n">
-        <v>7085818</v>
+        <v>7085829</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24446,7 +24441,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24456,7 +24451,12 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD221" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133582217</v>
+        <v>133582136</v>
       </c>
       <c r="B2" t="n">
-        <v>80439</v>
+        <v>79493</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>484892</v>
+        <v>485044</v>
       </c>
       <c r="R2" t="n">
-        <v>7086073</v>
+        <v>7086195</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133582295</v>
+        <v>133582307</v>
       </c>
       <c r="B3" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>484865</v>
+        <v>485011</v>
       </c>
       <c r="R3" t="n">
-        <v>7085940</v>
+        <v>7085969</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:43</t>
+          <t>21:05</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;1000 bålar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133582161</v>
+        <v>133582217</v>
       </c>
       <c r="B4" t="n">
         <v>80439</v>
@@ -924,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>484823</v>
+        <v>484892</v>
       </c>
       <c r="R4" t="n">
-        <v>7086116</v>
+        <v>7086073</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>17:09</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,7 +1001,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133582180</v>
+        <v>133582295</v>
       </c>
       <c r="B5" t="n">
         <v>80439</v>
@@ -1031,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>484629</v>
+        <v>484865</v>
       </c>
       <c r="R5" t="n">
-        <v>7086008</v>
+        <v>7085940</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1066,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1076,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1103,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133582210</v>
+        <v>133582161</v>
       </c>
       <c r="B6" t="n">
-        <v>91928</v>
+        <v>80439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1114,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1138,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>484827</v>
+        <v>484823</v>
       </c>
       <c r="R6" t="n">
-        <v>7085987</v>
+        <v>7086116</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1183,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133582080</v>
+        <v>133582180</v>
       </c>
       <c r="B7" t="n">
-        <v>91924</v>
+        <v>80439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1108</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>485117</v>
+        <v>484629</v>
       </c>
       <c r="R7" t="n">
-        <v>7086099</v>
+        <v>7086008</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,32 +1322,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133582136</v>
+        <v>133582210</v>
       </c>
       <c r="B8" t="n">
-        <v>79493</v>
+        <v>91928</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1249</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1352,10 +1357,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>485044</v>
+        <v>484827</v>
       </c>
       <c r="R8" t="n">
-        <v>7086195</v>
+        <v>7085987</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1387,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1397,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:18</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1424,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133582307</v>
+        <v>133582080</v>
       </c>
       <c r="B9" t="n">
-        <v>79334</v>
+        <v>91924</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1435,21 +1440,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1459,10 +1464,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>485011</v>
+        <v>485117</v>
       </c>
       <c r="R9" t="n">
-        <v>7085969</v>
+        <v>7086099</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>21:05</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1504,12 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>21:05</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;1000 bålar</t>
+          <t>20:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -7412,32 +7412,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133582146</v>
+        <v>133582239</v>
       </c>
       <c r="B64" t="n">
-        <v>80399</v>
+        <v>79493</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>485019</v>
+        <v>485081</v>
       </c>
       <c r="R64" t="n">
-        <v>7086200</v>
+        <v>7086147</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7519,10 +7519,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133582124</v>
+        <v>133582288</v>
       </c>
       <c r="B65" t="n">
-        <v>80399</v>
+        <v>92651</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7530,21 +7530,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>485137</v>
+        <v>484904</v>
       </c>
       <c r="R65" t="n">
-        <v>7086195</v>
+        <v>7085957</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7626,32 +7626,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133582049</v>
+        <v>133582249</v>
       </c>
       <c r="B66" t="n">
-        <v>80399</v>
+        <v>83183</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>484616</v>
+        <v>485150</v>
       </c>
       <c r="R66" t="n">
-        <v>7085997</v>
+        <v>7086053</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8161,32 +8161,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133582239</v>
+        <v>133582146</v>
       </c>
       <c r="B71" t="n">
-        <v>79493</v>
+        <v>80399</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>485081</v>
+        <v>485019</v>
       </c>
       <c r="R71" t="n">
-        <v>7086147</v>
+        <v>7086200</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8268,10 +8268,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133582288</v>
+        <v>133582124</v>
       </c>
       <c r="B72" t="n">
-        <v>92651</v>
+        <v>80399</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>484904</v>
+        <v>485137</v>
       </c>
       <c r="R72" t="n">
-        <v>7085957</v>
+        <v>7086195</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8375,32 +8375,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133582249</v>
+        <v>133582049</v>
       </c>
       <c r="B73" t="n">
-        <v>83183</v>
+        <v>80399</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>485150</v>
+        <v>484616</v>
       </c>
       <c r="R73" t="n">
-        <v>7086053</v>
+        <v>7085997</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -11294,10 +11294,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133582042</v>
+        <v>133582163</v>
       </c>
       <c r="B100" t="n">
-        <v>57958</v>
+        <v>91942</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11305,21 +11305,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11329,10 +11329,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>484762</v>
+        <v>484703</v>
       </c>
       <c r="R100" t="n">
-        <v>7086084</v>
+        <v>7086043</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11374,12 +11374,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11406,32 +11401,32 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133582163</v>
+        <v>133582105</v>
       </c>
       <c r="B101" t="n">
-        <v>91942</v>
+        <v>92651</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1204</v>
+        <v>3298</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11441,10 +11436,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>484703</v>
+        <v>485150</v>
       </c>
       <c r="R101" t="n">
-        <v>7086043</v>
+        <v>7085949</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11476,7 +11471,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11486,7 +11481,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11513,32 +11508,32 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133582105</v>
+        <v>133582234</v>
       </c>
       <c r="B102" t="n">
-        <v>92651</v>
+        <v>91942</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>3298</v>
+        <v>1204</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11548,10 +11543,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>485150</v>
+        <v>485009</v>
       </c>
       <c r="R102" t="n">
-        <v>7085949</v>
+        <v>7086144</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11583,7 +11578,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11593,7 +11588,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11620,10 +11615,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133582234</v>
+        <v>133582042</v>
       </c>
       <c r="B103" t="n">
-        <v>91942</v>
+        <v>57958</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11631,21 +11626,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11655,10 +11650,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>485009</v>
+        <v>484762</v>
       </c>
       <c r="R103" t="n">
-        <v>7086144</v>
+        <v>7086084</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11690,7 +11685,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11700,7 +11695,12 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11727,32 +11727,32 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133582233</v>
+        <v>133582179</v>
       </c>
       <c r="B104" t="n">
-        <v>80439</v>
+        <v>80399</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11762,10 +11762,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>485025</v>
+        <v>484623</v>
       </c>
       <c r="R104" t="n">
-        <v>7086137</v>
+        <v>7086004</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11797,7 +11797,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11807,7 +11807,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11834,7 +11834,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133582224</v>
+        <v>133582233</v>
       </c>
       <c r="B105" t="n">
         <v>80439</v>
@@ -11869,10 +11869,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>484963</v>
+        <v>485025</v>
       </c>
       <c r="R105" t="n">
-        <v>7086155</v>
+        <v>7086137</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11904,7 +11904,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11941,7 +11941,7 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133582145</v>
+        <v>133582224</v>
       </c>
       <c r="B106" t="n">
         <v>80439</v>
@@ -11976,10 +11976,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>485022</v>
+        <v>484963</v>
       </c>
       <c r="R106" t="n">
-        <v>7086194</v>
+        <v>7086155</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12048,7 +12048,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133582144</v>
+        <v>133582145</v>
       </c>
       <c r="B107" t="n">
         <v>80439</v>
@@ -12083,10 +12083,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>485024</v>
+        <v>485022</v>
       </c>
       <c r="R107" t="n">
-        <v>7086180</v>
+        <v>7086194</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12118,7 +12118,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12155,7 +12155,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133582255</v>
+        <v>133582144</v>
       </c>
       <c r="B108" t="n">
         <v>80439</v>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>485082</v>
+        <v>485024</v>
       </c>
       <c r="R108" t="n">
-        <v>7086082</v>
+        <v>7086180</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12262,7 +12262,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133582034</v>
+        <v>133582255</v>
       </c>
       <c r="B109" t="n">
         <v>80439</v>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>484996</v>
+        <v>485082</v>
       </c>
       <c r="R109" t="n">
-        <v>7086209</v>
+        <v>7086082</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12369,7 +12369,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133582195</v>
+        <v>133582034</v>
       </c>
       <c r="B110" t="n">
         <v>80439</v>
@@ -12404,10 +12404,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>484677</v>
+        <v>484996</v>
       </c>
       <c r="R110" t="n">
-        <v>7085977</v>
+        <v>7086209</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12476,7 +12476,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133582188</v>
+        <v>133582195</v>
       </c>
       <c r="B111" t="n">
         <v>80439</v>
@@ -12511,10 +12511,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>484675</v>
+        <v>484677</v>
       </c>
       <c r="R111" t="n">
-        <v>7085987</v>
+        <v>7085977</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12583,7 +12583,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133582184</v>
+        <v>133582188</v>
       </c>
       <c r="B112" t="n">
         <v>80439</v>
@@ -12618,10 +12618,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>484657</v>
+        <v>484675</v>
       </c>
       <c r="R112" t="n">
-        <v>7085984</v>
+        <v>7085987</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12690,32 +12690,32 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133582179</v>
+        <v>133582184</v>
       </c>
       <c r="B113" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12725,10 +12725,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>484623</v>
+        <v>484657</v>
       </c>
       <c r="R113" t="n">
-        <v>7086004</v>
+        <v>7085984</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12760,7 +12760,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13225,45 +13225,65 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133582022</v>
+        <v>133582153</v>
       </c>
       <c r="B118" t="n">
-        <v>92153</v>
+        <v>57958</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>485091</v>
+        <v>484961</v>
       </c>
       <c r="R118" t="n">
-        <v>7086182</v>
+        <v>7086205</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13295,7 +13315,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13305,16 +13325,20 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Trummande och födosökande</t>
         </is>
       </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF118" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13333,65 +13357,45 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133582153</v>
+        <v>133582022</v>
       </c>
       <c r="B119" t="n">
-        <v>57958</v>
+        <v>92153</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K119" t="inlineStr"/>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>484961</v>
+        <v>485091</v>
       </c>
       <c r="R119" t="n">
-        <v>7086205</v>
+        <v>7086182</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13423,7 +13427,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13433,20 +13437,16 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Trummande och födosökande</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133582133</v>
+        <v>133582075</v>
       </c>
       <c r="B120" t="n">
-        <v>80474</v>
+        <v>91928</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485084</v>
+        <v>485160</v>
       </c>
       <c r="R120" t="n">
-        <v>7086179</v>
+        <v>7086132</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13572,32 +13572,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133582026</v>
+        <v>133582211</v>
       </c>
       <c r="B121" t="n">
-        <v>80439</v>
+        <v>92624</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>485057</v>
+        <v>484833</v>
       </c>
       <c r="R121" t="n">
-        <v>7086210</v>
+        <v>7085991</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13679,32 +13679,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133582185</v>
+        <v>133582044</v>
       </c>
       <c r="B122" t="n">
-        <v>80439</v>
+        <v>92624</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>484663</v>
+        <v>484638</v>
       </c>
       <c r="R122" t="n">
-        <v>7085977</v>
+        <v>7086023</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13898,32 +13898,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133582116</v>
+        <v>133582230</v>
       </c>
       <c r="B124" t="n">
-        <v>79493</v>
+        <v>80399</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13933,10 +13933,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485168</v>
+        <v>485000</v>
       </c>
       <c r="R124" t="n">
-        <v>7086214</v>
+        <v>7086155</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14005,32 +14005,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133582314</v>
+        <v>133582205</v>
       </c>
       <c r="B125" t="n">
-        <v>79334</v>
+        <v>80399</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14040,10 +14040,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>485031</v>
+        <v>484779</v>
       </c>
       <c r="R125" t="n">
-        <v>7085985</v>
+        <v>7085989</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14075,7 +14075,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14085,12 +14085,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>21:13</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14117,32 +14112,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133582162</v>
+        <v>133582101</v>
       </c>
       <c r="B126" t="n">
-        <v>79493</v>
+        <v>80399</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14152,10 +14147,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>484794</v>
+        <v>484978</v>
       </c>
       <c r="R126" t="n">
-        <v>7086094</v>
+        <v>7085798</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14187,7 +14182,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14197,7 +14192,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14224,32 +14219,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133582085</v>
+        <v>133582116</v>
       </c>
       <c r="B127" t="n">
-        <v>91942</v>
+        <v>79493</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14259,10 +14254,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>484920</v>
+        <v>485168</v>
       </c>
       <c r="R127" t="n">
-        <v>7086079</v>
+        <v>7086214</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14294,7 +14289,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14304,7 +14299,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14331,10 +14326,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133582075</v>
+        <v>133582314</v>
       </c>
       <c r="B128" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14342,21 +14337,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14366,10 +14361,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485160</v>
+        <v>485031</v>
       </c>
       <c r="R128" t="n">
-        <v>7086132</v>
+        <v>7085985</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14401,7 +14396,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14411,7 +14406,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14438,10 +14438,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133582211</v>
+        <v>133582162</v>
       </c>
       <c r="B129" t="n">
-        <v>92624</v>
+        <v>79493</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14449,21 +14449,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>898</v>
+        <v>1249</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14473,10 +14473,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>484833</v>
+        <v>484794</v>
       </c>
       <c r="R129" t="n">
-        <v>7085991</v>
+        <v>7086094</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14545,32 +14545,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133582044</v>
+        <v>133582085</v>
       </c>
       <c r="B130" t="n">
-        <v>92624</v>
+        <v>91942</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14580,10 +14580,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>484638</v>
+        <v>484920</v>
       </c>
       <c r="R130" t="n">
-        <v>7086023</v>
+        <v>7086079</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14652,10 +14652,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133582230</v>
+        <v>133582133</v>
       </c>
       <c r="B131" t="n">
-        <v>80399</v>
+        <v>80474</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14663,21 +14663,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14687,10 +14687,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>485000</v>
+        <v>485084</v>
       </c>
       <c r="R131" t="n">
-        <v>7086155</v>
+        <v>7086179</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14722,7 +14722,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14759,32 +14759,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133582205</v>
+        <v>133582026</v>
       </c>
       <c r="B132" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14794,10 +14794,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>484779</v>
+        <v>485057</v>
       </c>
       <c r="R132" t="n">
-        <v>7085989</v>
+        <v>7086210</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14866,32 +14866,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133582101</v>
+        <v>133582185</v>
       </c>
       <c r="B133" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>484978</v>
+        <v>484663</v>
       </c>
       <c r="R133" t="n">
-        <v>7085798</v>
+        <v>7085977</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14973,10 +14973,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133582299</v>
+        <v>133582206</v>
       </c>
       <c r="B134" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14984,21 +14984,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>484915</v>
+        <v>484786</v>
       </c>
       <c r="R134" t="n">
-        <v>7085804</v>
+        <v>7085991</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15053,12 +15053,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15085,10 +15080,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133582220</v>
+        <v>133582266</v>
       </c>
       <c r="B135" t="n">
-        <v>91942</v>
+        <v>80439</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15096,21 +15091,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15120,10 +15115,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>484884</v>
+        <v>484970</v>
       </c>
       <c r="R135" t="n">
-        <v>7086115</v>
+        <v>7086056</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15155,7 +15150,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15165,7 +15160,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15192,10 +15187,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133582221</v>
+        <v>133582256</v>
       </c>
       <c r="B136" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15203,21 +15198,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15227,10 +15222,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>484871</v>
+        <v>485049</v>
       </c>
       <c r="R136" t="n">
-        <v>7086160</v>
+        <v>7086092</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15262,7 +15257,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15272,7 +15267,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15299,10 +15294,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133582168</v>
+        <v>133582086</v>
       </c>
       <c r="B137" t="n">
-        <v>91942</v>
+        <v>80439</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15310,21 +15305,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15334,10 +15329,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>484620</v>
+        <v>484918</v>
       </c>
       <c r="R137" t="n">
-        <v>7086031</v>
+        <v>7086067</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15369,7 +15364,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15379,7 +15374,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15406,7 +15401,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133582206</v>
+        <v>133582274</v>
       </c>
       <c r="B138" t="n">
         <v>80439</v>
@@ -15441,10 +15436,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>484786</v>
+        <v>484927</v>
       </c>
       <c r="R138" t="n">
-        <v>7085991</v>
+        <v>7086073</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15476,7 +15471,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15486,7 +15481,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15513,7 +15508,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133582266</v>
+        <v>133582073</v>
       </c>
       <c r="B139" t="n">
         <v>80439</v>
@@ -15548,10 +15543,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>484970</v>
+        <v>484980</v>
       </c>
       <c r="R139" t="n">
-        <v>7086056</v>
+        <v>7086124</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15583,7 +15578,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15593,7 +15588,12 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15620,10 +15620,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133582256</v>
+        <v>133582299</v>
       </c>
       <c r="B140" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15631,21 +15631,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>485049</v>
+        <v>484915</v>
       </c>
       <c r="R140" t="n">
-        <v>7086092</v>
+        <v>7085804</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15700,7 +15700,12 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15727,10 +15732,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133582086</v>
+        <v>133582220</v>
       </c>
       <c r="B141" t="n">
-        <v>80439</v>
+        <v>91942</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15738,21 +15743,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15762,10 +15767,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>484918</v>
+        <v>484884</v>
       </c>
       <c r="R141" t="n">
-        <v>7086067</v>
+        <v>7086115</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15797,7 +15802,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15807,7 +15812,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15834,10 +15839,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133582274</v>
+        <v>133582221</v>
       </c>
       <c r="B142" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15845,21 +15850,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15869,10 +15874,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>484927</v>
+        <v>484871</v>
       </c>
       <c r="R142" t="n">
-        <v>7086073</v>
+        <v>7086160</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15904,7 +15909,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15914,7 +15919,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15941,10 +15946,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133582073</v>
+        <v>133582168</v>
       </c>
       <c r="B143" t="n">
-        <v>80439</v>
+        <v>91942</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15952,21 +15957,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15976,10 +15981,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>484980</v>
+        <v>484620</v>
       </c>
       <c r="R143" t="n">
-        <v>7086124</v>
+        <v>7086031</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16011,7 +16016,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16021,12 +16026,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>18:34</t>
-        </is>
-      </c>
-      <c r="AC143" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -20687,32 +20687,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133582263</v>
+        <v>133582237</v>
       </c>
       <c r="B187" t="n">
-        <v>79493</v>
+        <v>80439</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20722,10 +20722,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>484998</v>
+        <v>485067</v>
       </c>
       <c r="R187" t="n">
-        <v>7086055</v>
+        <v>7086146</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20767,7 +20767,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20794,32 +20794,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133582066</v>
+        <v>133582300</v>
       </c>
       <c r="B188" t="n">
-        <v>91928</v>
+        <v>80474</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20829,10 +20829,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>484881</v>
+        <v>484976</v>
       </c>
       <c r="R188" t="n">
-        <v>7086060</v>
+        <v>7085795</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20864,7 +20864,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20901,10 +20901,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133582298</v>
+        <v>133582208</v>
       </c>
       <c r="B189" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20912,21 +20912,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20936,10 +20936,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>484895</v>
+        <v>484791</v>
       </c>
       <c r="R189" t="n">
-        <v>7085846</v>
+        <v>7085988</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20971,7 +20971,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20981,12 +20981,7 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>20:50</t>
-        </is>
-      </c>
-      <c r="AC189" t="inlineStr">
-        <is>
-          <t>Rikligt &gt; 1000 bålar</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21013,7 +21008,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133582237</v>
+        <v>133582048</v>
       </c>
       <c r="B190" t="n">
         <v>80439</v>
@@ -21042,16 +21037,23 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
+      <c r="J190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>485067</v>
+        <v>484618</v>
       </c>
       <c r="R190" t="n">
-        <v>7086146</v>
+        <v>7085997</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21083,7 +21085,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21093,7 +21095,12 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21102,6 +21109,7 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
+      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
@@ -21120,32 +21128,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133582300</v>
+        <v>133582225</v>
       </c>
       <c r="B191" t="n">
-        <v>80474</v>
+        <v>80439</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21155,10 +21163,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>484976</v>
+        <v>484969</v>
       </c>
       <c r="R191" t="n">
-        <v>7085795</v>
+        <v>7086169</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21190,7 +21198,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21200,7 +21208,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21227,32 +21235,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133582208</v>
+        <v>133582263</v>
       </c>
       <c r="B192" t="n">
-        <v>80439</v>
+        <v>79493</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21262,10 +21270,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>484791</v>
+        <v>484998</v>
       </c>
       <c r="R192" t="n">
-        <v>7085988</v>
+        <v>7086055</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21297,7 +21305,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21307,7 +21315,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21334,10 +21342,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133582048</v>
+        <v>133582066</v>
       </c>
       <c r="B193" t="n">
-        <v>80439</v>
+        <v>91928</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21345,41 +21353,34 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>484618</v>
+        <v>484881</v>
       </c>
       <c r="R193" t="n">
-        <v>7085997</v>
+        <v>7086060</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21411,7 +21412,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21421,12 +21422,7 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC193" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21435,7 +21431,6 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
-      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -21454,10 +21449,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133582225</v>
+        <v>133582298</v>
       </c>
       <c r="B194" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21465,21 +21460,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21489,10 +21484,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>484969</v>
+        <v>484895</v>
       </c>
       <c r="R194" t="n">
-        <v>7086169</v>
+        <v>7085846</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21524,7 +21519,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21534,7 +21529,12 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>Rikligt &gt; 1000 bålar</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23622,10 +23622,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>133582296</v>
+        <v>133582097</v>
       </c>
       <c r="B214" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23633,21 +23633,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23657,10 +23657,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>484845</v>
+        <v>484907</v>
       </c>
       <c r="R214" t="n">
-        <v>7085934</v>
+        <v>7085829</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23692,7 +23692,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23702,7 +23702,12 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="AC214" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23729,7 +23734,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>133582051</v>
+        <v>133582296</v>
       </c>
       <c r="B215" t="n">
         <v>80439</v>
@@ -23764,10 +23769,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>484623</v>
+        <v>484845</v>
       </c>
       <c r="R215" t="n">
-        <v>7085960</v>
+        <v>7085934</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23799,7 +23804,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23809,7 +23814,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23836,7 +23841,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>133582122</v>
+        <v>133582051</v>
       </c>
       <c r="B216" t="n">
         <v>80439</v>
@@ -23871,10 +23876,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>485143</v>
+        <v>484623</v>
       </c>
       <c r="R216" t="n">
-        <v>7086201</v>
+        <v>7085960</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23906,7 +23911,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23916,7 +23921,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23943,32 +23948,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>133582204</v>
+        <v>133582122</v>
       </c>
       <c r="B217" t="n">
-        <v>80474</v>
+        <v>80439</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23978,10 +23983,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>484777</v>
+        <v>485143</v>
       </c>
       <c r="R217" t="n">
-        <v>7085989</v>
+        <v>7086201</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24013,7 +24018,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24023,7 +24028,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24050,32 +24055,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>133582047</v>
+        <v>133582204</v>
       </c>
       <c r="B218" t="n">
-        <v>80439</v>
+        <v>80474</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24085,10 +24090,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>484606</v>
+        <v>484777</v>
       </c>
       <c r="R218" t="n">
-        <v>7085997</v>
+        <v>7085989</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24120,7 +24125,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24130,7 +24135,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24157,7 +24162,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>133582229</v>
+        <v>133582047</v>
       </c>
       <c r="B219" t="n">
         <v>80439</v>
@@ -24192,10 +24197,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>484994</v>
+        <v>484606</v>
       </c>
       <c r="R219" t="n">
-        <v>7086157</v>
+        <v>7085997</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24227,7 +24232,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24237,7 +24242,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24264,7 +24269,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>133582301</v>
+        <v>133582229</v>
       </c>
       <c r="B220" t="n">
         <v>80439</v>
@@ -24299,10 +24304,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>485003</v>
+        <v>484994</v>
       </c>
       <c r="R220" t="n">
-        <v>7085818</v>
+        <v>7086157</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24334,7 +24339,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -24344,7 +24349,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24371,10 +24376,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>133582097</v>
+        <v>133582301</v>
       </c>
       <c r="B221" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24382,21 +24387,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24406,10 +24411,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>484907</v>
+        <v>485003</v>
       </c>
       <c r="R221" t="n">
-        <v>7085829</v>
+        <v>7085818</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24441,7 +24446,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24451,12 +24456,7 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>20:51</t>
-        </is>
-      </c>
-      <c r="AC221" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD221" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -7412,32 +7412,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133582239</v>
+        <v>133582146</v>
       </c>
       <c r="B64" t="n">
-        <v>79493</v>
+        <v>80399</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>485081</v>
+        <v>485019</v>
       </c>
       <c r="R64" t="n">
-        <v>7086147</v>
+        <v>7086200</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7519,10 +7519,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133582288</v>
+        <v>133582124</v>
       </c>
       <c r="B65" t="n">
-        <v>92651</v>
+        <v>80399</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7530,21 +7530,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>484904</v>
+        <v>485137</v>
       </c>
       <c r="R65" t="n">
-        <v>7085957</v>
+        <v>7086195</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7626,32 +7626,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133582249</v>
+        <v>133582049</v>
       </c>
       <c r="B66" t="n">
-        <v>83183</v>
+        <v>80399</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>485150</v>
+        <v>484616</v>
       </c>
       <c r="R66" t="n">
-        <v>7086053</v>
+        <v>7085997</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8161,32 +8161,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133582146</v>
+        <v>133582239</v>
       </c>
       <c r="B71" t="n">
-        <v>80399</v>
+        <v>79493</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>485019</v>
+        <v>485081</v>
       </c>
       <c r="R71" t="n">
-        <v>7086200</v>
+        <v>7086147</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8268,10 +8268,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133582124</v>
+        <v>133582288</v>
       </c>
       <c r="B72" t="n">
-        <v>80399</v>
+        <v>92651</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>485137</v>
+        <v>484904</v>
       </c>
       <c r="R72" t="n">
-        <v>7086195</v>
+        <v>7085957</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8375,32 +8375,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133582049</v>
+        <v>133582249</v>
       </c>
       <c r="B73" t="n">
-        <v>80399</v>
+        <v>83183</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>484616</v>
+        <v>485150</v>
       </c>
       <c r="R73" t="n">
-        <v>7085997</v>
+        <v>7086053</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -13225,65 +13225,45 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133582153</v>
+        <v>133582022</v>
       </c>
       <c r="B118" t="n">
-        <v>57958</v>
+        <v>92153</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>1106</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>484961</v>
+        <v>485091</v>
       </c>
       <c r="R118" t="n">
-        <v>7086205</v>
+        <v>7086182</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13315,7 +13295,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13325,20 +13305,16 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Trummande och födosökande</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -13357,45 +13333,65 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133582022</v>
+        <v>133582153</v>
       </c>
       <c r="B119" t="n">
-        <v>92153</v>
+        <v>57958</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1106</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P119" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>485091</v>
+        <v>484961</v>
       </c>
       <c r="R119" t="n">
-        <v>7086182</v>
+        <v>7086205</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13427,7 +13423,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13437,16 +13433,20 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Trummande och födosökande</t>
         </is>
       </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF119" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG119" t="b">
         <v>0</v>
       </c>
@@ -13465,32 +13465,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133582075</v>
+        <v>133582133</v>
       </c>
       <c r="B120" t="n">
-        <v>91928</v>
+        <v>80474</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>1202</v>
+        <v>6463</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485160</v>
+        <v>485084</v>
       </c>
       <c r="R120" t="n">
-        <v>7086132</v>
+        <v>7086179</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13572,32 +13572,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133582211</v>
+        <v>133582026</v>
       </c>
       <c r="B121" t="n">
-        <v>92624</v>
+        <v>80439</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>484833</v>
+        <v>485057</v>
       </c>
       <c r="R121" t="n">
-        <v>7085991</v>
+        <v>7086210</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13679,32 +13679,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133582044</v>
+        <v>133582185</v>
       </c>
       <c r="B122" t="n">
-        <v>92624</v>
+        <v>80439</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>484638</v>
+        <v>484663</v>
       </c>
       <c r="R122" t="n">
-        <v>7086023</v>
+        <v>7085977</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13898,32 +13898,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133582230</v>
+        <v>133582116</v>
       </c>
       <c r="B124" t="n">
-        <v>80399</v>
+        <v>79493</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13933,10 +13933,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485000</v>
+        <v>485168</v>
       </c>
       <c r="R124" t="n">
-        <v>7086155</v>
+        <v>7086214</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14005,32 +14005,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133582205</v>
+        <v>133582314</v>
       </c>
       <c r="B125" t="n">
-        <v>80399</v>
+        <v>79334</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>229497</v>
+        <v>6425</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14040,10 +14040,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>484779</v>
+        <v>485031</v>
       </c>
       <c r="R125" t="n">
-        <v>7085989</v>
+        <v>7085985</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14075,7 +14075,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14085,7 +14085,12 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14112,32 +14117,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133582101</v>
+        <v>133582162</v>
       </c>
       <c r="B126" t="n">
-        <v>80399</v>
+        <v>79493</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14147,10 +14152,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>484978</v>
+        <v>484794</v>
       </c>
       <c r="R126" t="n">
-        <v>7085798</v>
+        <v>7086094</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14182,7 +14187,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14192,7 +14197,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14219,32 +14224,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133582116</v>
+        <v>133582085</v>
       </c>
       <c r="B127" t="n">
-        <v>79493</v>
+        <v>91942</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14254,10 +14259,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>485168</v>
+        <v>484920</v>
       </c>
       <c r="R127" t="n">
-        <v>7086214</v>
+        <v>7086079</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14289,7 +14294,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14299,7 +14304,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14326,10 +14331,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133582314</v>
+        <v>133582075</v>
       </c>
       <c r="B128" t="n">
-        <v>79334</v>
+        <v>91928</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14337,21 +14342,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14361,10 +14366,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485031</v>
+        <v>485160</v>
       </c>
       <c r="R128" t="n">
-        <v>7085985</v>
+        <v>7086132</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14396,7 +14401,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14406,12 +14411,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>21:13</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14438,10 +14438,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133582162</v>
+        <v>133582211</v>
       </c>
       <c r="B129" t="n">
-        <v>79493</v>
+        <v>92624</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14449,21 +14449,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>1249</v>
+        <v>898</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14473,10 +14473,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>484794</v>
+        <v>484833</v>
       </c>
       <c r="R129" t="n">
-        <v>7086094</v>
+        <v>7085991</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14545,32 +14545,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133582085</v>
+        <v>133582044</v>
       </c>
       <c r="B130" t="n">
-        <v>91942</v>
+        <v>92624</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1204</v>
+        <v>898</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14580,10 +14580,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>484920</v>
+        <v>484638</v>
       </c>
       <c r="R130" t="n">
-        <v>7086079</v>
+        <v>7086023</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14652,10 +14652,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133582133</v>
+        <v>133582230</v>
       </c>
       <c r="B131" t="n">
-        <v>80474</v>
+        <v>80399</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14663,21 +14663,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6463</v>
+        <v>229497</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14687,10 +14687,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>485084</v>
+        <v>485000</v>
       </c>
       <c r="R131" t="n">
-        <v>7086179</v>
+        <v>7086155</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14722,7 +14722,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14759,32 +14759,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133582026</v>
+        <v>133582205</v>
       </c>
       <c r="B132" t="n">
-        <v>80439</v>
+        <v>80399</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14794,10 +14794,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>485057</v>
+        <v>484779</v>
       </c>
       <c r="R132" t="n">
-        <v>7086210</v>
+        <v>7085989</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14866,32 +14866,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133582185</v>
+        <v>133582101</v>
       </c>
       <c r="B133" t="n">
-        <v>80439</v>
+        <v>80399</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>484663</v>
+        <v>484978</v>
       </c>
       <c r="R133" t="n">
-        <v>7085977</v>
+        <v>7085798</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14973,10 +14973,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>133582206</v>
+        <v>133582299</v>
       </c>
       <c r="B134" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14984,21 +14984,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15008,10 +15008,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>484786</v>
+        <v>484915</v>
       </c>
       <c r="R134" t="n">
-        <v>7085991</v>
+        <v>7085804</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:55</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15053,7 +15053,12 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>18:03</t>
+          <t>20:55</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15080,10 +15085,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>133582266</v>
+        <v>133582220</v>
       </c>
       <c r="B135" t="n">
-        <v>80439</v>
+        <v>91942</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15091,21 +15096,21 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -15115,10 +15120,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>484970</v>
+        <v>484884</v>
       </c>
       <c r="R135" t="n">
-        <v>7086056</v>
+        <v>7086115</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15150,7 +15155,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -15160,7 +15165,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15187,10 +15192,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>133582256</v>
+        <v>133582221</v>
       </c>
       <c r="B136" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15198,21 +15203,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -15222,10 +15227,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>485049</v>
+        <v>484871</v>
       </c>
       <c r="R136" t="n">
-        <v>7086092</v>
+        <v>7086160</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15257,7 +15262,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -15267,7 +15272,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15294,10 +15299,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>133582086</v>
+        <v>133582168</v>
       </c>
       <c r="B137" t="n">
-        <v>80439</v>
+        <v>91942</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15305,21 +15310,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15329,10 +15334,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>484918</v>
+        <v>484620</v>
       </c>
       <c r="R137" t="n">
-        <v>7086067</v>
+        <v>7086031</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15364,7 +15369,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15374,7 +15379,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>20:27</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15401,7 +15406,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>133582274</v>
+        <v>133582206</v>
       </c>
       <c r="B138" t="n">
         <v>80439</v>
@@ -15436,10 +15441,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>484927</v>
+        <v>484786</v>
       </c>
       <c r="R138" t="n">
-        <v>7086073</v>
+        <v>7085991</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15471,7 +15476,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15481,7 +15486,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>18:03</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15508,7 +15513,7 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>133582073</v>
+        <v>133582266</v>
       </c>
       <c r="B139" t="n">
         <v>80439</v>
@@ -15543,10 +15548,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>484980</v>
+        <v>484970</v>
       </c>
       <c r="R139" t="n">
-        <v>7086124</v>
+        <v>7086056</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15578,7 +15583,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15588,12 +15593,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>18:34</t>
-        </is>
-      </c>
-      <c r="AC139" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15620,10 +15620,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>133582299</v>
+        <v>133582256</v>
       </c>
       <c r="B140" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15631,21 +15631,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15655,10 +15655,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>484915</v>
+        <v>485049</v>
       </c>
       <c r="R140" t="n">
-        <v>7085804</v>
+        <v>7086092</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15690,7 +15690,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>20:55</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15700,12 +15700,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>20:55</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15732,10 +15727,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>133582220</v>
+        <v>133582086</v>
       </c>
       <c r="B141" t="n">
-        <v>91942</v>
+        <v>80439</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15743,21 +15738,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15767,10 +15762,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>484884</v>
+        <v>484918</v>
       </c>
       <c r="R141" t="n">
-        <v>7086115</v>
+        <v>7086067</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -15802,7 +15797,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -15812,7 +15807,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>20:27</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15839,10 +15834,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>133582221</v>
+        <v>133582274</v>
       </c>
       <c r="B142" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15850,21 +15845,21 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15874,10 +15869,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>484871</v>
+        <v>484927</v>
       </c>
       <c r="R142" t="n">
-        <v>7086160</v>
+        <v>7086073</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15909,7 +15904,7 @@
       </c>
       <c r="Z142" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -15919,7 +15914,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15946,10 +15941,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>133582168</v>
+        <v>133582073</v>
       </c>
       <c r="B143" t="n">
-        <v>91942</v>
+        <v>80439</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15957,21 +15952,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15981,10 +15976,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>484620</v>
+        <v>484980</v>
       </c>
       <c r="R143" t="n">
-        <v>7086031</v>
+        <v>7086124</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16016,7 +16011,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -16026,7 +16021,12 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>17:24</t>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -20687,32 +20687,32 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>133582237</v>
+        <v>133582263</v>
       </c>
       <c r="B187" t="n">
-        <v>80439</v>
+        <v>79493</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -20722,10 +20722,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>485067</v>
+        <v>484998</v>
       </c>
       <c r="R187" t="n">
-        <v>7086146</v>
+        <v>7086055</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20757,7 +20757,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -20767,7 +20767,7 @@
       </c>
       <c r="AB187" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>20:18</t>
         </is>
       </c>
       <c r="AD187" t="b">
@@ -20794,32 +20794,32 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>133582300</v>
+        <v>133582066</v>
       </c>
       <c r="B188" t="n">
-        <v>80474</v>
+        <v>91928</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -20829,10 +20829,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>484976</v>
+        <v>484881</v>
       </c>
       <c r="R188" t="n">
-        <v>7085795</v>
+        <v>7086060</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -20864,7 +20864,7 @@
       </c>
       <c r="Z188" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="AB188" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>18:16</t>
         </is>
       </c>
       <c r="AD188" t="b">
@@ -20901,10 +20901,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>133582208</v>
+        <v>133582298</v>
       </c>
       <c r="B189" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -20912,21 +20912,21 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -20936,10 +20936,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>484791</v>
+        <v>484895</v>
       </c>
       <c r="R189" t="n">
-        <v>7085988</v>
+        <v>7085846</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -20971,7 +20971,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -20981,7 +20981,12 @@
       </c>
       <c r="AB189" t="inlineStr">
         <is>
-          <t>18:05</t>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="AC189" t="inlineStr">
+        <is>
+          <t>Rikligt &gt; 1000 bålar</t>
         </is>
       </c>
       <c r="AD189" t="b">
@@ -21008,7 +21013,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>133582048</v>
+        <v>133582237</v>
       </c>
       <c r="B190" t="n">
         <v>80439</v>
@@ -21037,23 +21042,16 @@
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
-      <c r="J190" t="inlineStr"/>
-      <c r="K190" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N190" t="inlineStr"/>
       <c r="P190" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>484618</v>
+        <v>485067</v>
       </c>
       <c r="R190" t="n">
-        <v>7085997</v>
+        <v>7086146</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -21085,7 +21083,7 @@
       </c>
       <c r="Z190" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -21095,12 +21093,7 @@
       </c>
       <c r="AB190" t="inlineStr">
         <is>
-          <t>17:36</t>
-        </is>
-      </c>
-      <c r="AC190" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD190" t="b">
@@ -21109,7 +21102,6 @@
       <c r="AE190" t="b">
         <v>0</v>
       </c>
-      <c r="AF190" t="inlineStr"/>
       <c r="AG190" t="b">
         <v>0</v>
       </c>
@@ -21128,32 +21120,32 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>133582225</v>
+        <v>133582300</v>
       </c>
       <c r="B191" t="n">
-        <v>80439</v>
+        <v>80474</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -21163,10 +21155,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>484969</v>
+        <v>484976</v>
       </c>
       <c r="R191" t="n">
-        <v>7086169</v>
+        <v>7085795</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -21198,7 +21190,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -21208,7 +21200,7 @@
       </c>
       <c r="AB191" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD191" t="b">
@@ -21235,32 +21227,32 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>133582263</v>
+        <v>133582208</v>
       </c>
       <c r="B192" t="n">
-        <v>79493</v>
+        <v>80439</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -21270,10 +21262,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>484998</v>
+        <v>484791</v>
       </c>
       <c r="R192" t="n">
-        <v>7086055</v>
+        <v>7085988</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -21305,7 +21297,7 @@
       </c>
       <c r="Z192" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -21315,7 +21307,7 @@
       </c>
       <c r="AB192" t="inlineStr">
         <is>
-          <t>20:18</t>
+          <t>18:05</t>
         </is>
       </c>
       <c r="AD192" t="b">
@@ -21342,10 +21334,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>133582066</v>
+        <v>133582048</v>
       </c>
       <c r="B193" t="n">
-        <v>91928</v>
+        <v>80439</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -21353,34 +21345,41 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
+      <c r="J193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N193" t="inlineStr"/>
       <c r="P193" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>484881</v>
+        <v>484618</v>
       </c>
       <c r="R193" t="n">
-        <v>7086060</v>
+        <v>7085997</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -21412,7 +21411,7 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
@@ -21422,7 +21421,12 @@
       </c>
       <c r="AB193" t="inlineStr">
         <is>
-          <t>18:16</t>
+          <t>17:36</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -21431,6 +21435,7 @@
       <c r="AE193" t="b">
         <v>0</v>
       </c>
+      <c r="AF193" t="inlineStr"/>
       <c r="AG193" t="b">
         <v>0</v>
       </c>
@@ -21449,10 +21454,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>133582298</v>
+        <v>133582225</v>
       </c>
       <c r="B194" t="n">
-        <v>79334</v>
+        <v>80439</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -21460,21 +21465,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -21484,10 +21489,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>484895</v>
+        <v>484969</v>
       </c>
       <c r="R194" t="n">
-        <v>7085846</v>
+        <v>7086169</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -21519,7 +21524,7 @@
       </c>
       <c r="Z194" t="inlineStr">
         <is>
-          <t>20:50</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -21529,12 +21534,7 @@
       </c>
       <c r="AB194" t="inlineStr">
         <is>
-          <t>20:50</t>
-        </is>
-      </c>
-      <c r="AC194" t="inlineStr">
-        <is>
-          <t>Rikligt &gt; 1000 bålar</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD194" t="b">
@@ -23622,10 +23622,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>133582097</v>
+        <v>133582296</v>
       </c>
       <c r="B214" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -23633,21 +23633,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -23657,10 +23657,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>484907</v>
+        <v>484845</v>
       </c>
       <c r="R214" t="n">
-        <v>7085829</v>
+        <v>7085934</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23692,7 +23692,7 @@
       </c>
       <c r="Z214" t="inlineStr">
         <is>
-          <t>20:51</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AA214" t="inlineStr">
@@ -23702,12 +23702,7 @@
       </c>
       <c r="AB214" t="inlineStr">
         <is>
-          <t>20:51</t>
-        </is>
-      </c>
-      <c r="AC214" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>20:44</t>
         </is>
       </c>
       <c r="AD214" t="b">
@@ -23734,7 +23729,7 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>133582296</v>
+        <v>133582051</v>
       </c>
       <c r="B215" t="n">
         <v>80439</v>
@@ -23769,10 +23764,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>484845</v>
+        <v>484623</v>
       </c>
       <c r="R215" t="n">
-        <v>7085934</v>
+        <v>7085960</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -23804,7 +23799,7 @@
       </c>
       <c r="Z215" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA215" t="inlineStr">
@@ -23814,7 +23809,7 @@
       </c>
       <c r="AB215" t="inlineStr">
         <is>
-          <t>20:44</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD215" t="b">
@@ -23841,7 +23836,7 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>133582051</v>
+        <v>133582122</v>
       </c>
       <c r="B216" t="n">
         <v>80439</v>
@@ -23876,10 +23871,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>484623</v>
+        <v>485143</v>
       </c>
       <c r="R216" t="n">
-        <v>7085960</v>
+        <v>7086201</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -23911,7 +23906,7 @@
       </c>
       <c r="Z216" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA216" t="inlineStr">
@@ -23921,7 +23916,7 @@
       </c>
       <c r="AB216" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD216" t="b">
@@ -23948,32 +23943,32 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>133582122</v>
+        <v>133582204</v>
       </c>
       <c r="B217" t="n">
-        <v>80439</v>
+        <v>80474</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E217" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -23983,10 +23978,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>485143</v>
+        <v>484777</v>
       </c>
       <c r="R217" t="n">
-        <v>7086201</v>
+        <v>7085989</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -24018,7 +24013,7 @@
       </c>
       <c r="Z217" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA217" t="inlineStr">
@@ -24028,7 +24023,7 @@
       </c>
       <c r="AB217" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD217" t="b">
@@ -24055,32 +24050,32 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>133582204</v>
+        <v>133582047</v>
       </c>
       <c r="B218" t="n">
-        <v>80474</v>
+        <v>80439</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -24090,10 +24085,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>484777</v>
+        <v>484606</v>
       </c>
       <c r="R218" t="n">
-        <v>7085989</v>
+        <v>7085997</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -24125,7 +24120,7 @@
       </c>
       <c r="Z218" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AA218" t="inlineStr">
@@ -24135,7 +24130,7 @@
       </c>
       <c r="AB218" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="AD218" t="b">
@@ -24162,7 +24157,7 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>133582047</v>
+        <v>133582229</v>
       </c>
       <c r="B219" t="n">
         <v>80439</v>
@@ -24197,10 +24192,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>484606</v>
+        <v>484994</v>
       </c>
       <c r="R219" t="n">
-        <v>7085997</v>
+        <v>7086157</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -24232,7 +24227,7 @@
       </c>
       <c r="Z219" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA219" t="inlineStr">
@@ -24242,7 +24237,7 @@
       </c>
       <c r="AB219" t="inlineStr">
         <is>
-          <t>17:35</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD219" t="b">
@@ -24269,7 +24264,7 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>133582229</v>
+        <v>133582301</v>
       </c>
       <c r="B220" t="n">
         <v>80439</v>
@@ -24304,10 +24299,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>484994</v>
+        <v>485003</v>
       </c>
       <c r="R220" t="n">
-        <v>7086157</v>
+        <v>7085818</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -24339,7 +24334,7 @@
       </c>
       <c r="Z220" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -24349,7 +24344,7 @@
       </c>
       <c r="AB220" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="AD220" t="b">
@@ -24376,10 +24371,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>133582301</v>
+        <v>133582097</v>
       </c>
       <c r="B221" t="n">
-        <v>80439</v>
+        <v>57958</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -24387,21 +24382,21 @@
         </is>
       </c>
       <c r="E221" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -24411,10 +24406,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>485003</v>
+        <v>484907</v>
       </c>
       <c r="R221" t="n">
-        <v>7085818</v>
+        <v>7085829</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -24446,7 +24441,7 @@
       </c>
       <c r="Z221" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:51</t>
         </is>
       </c>
       <c r="AA221" t="inlineStr">
@@ -24456,7 +24451,12 @@
       </c>
       <c r="AB221" t="inlineStr">
         <is>
-          <t>21:01</t>
+          <t>20:51</t>
+        </is>
+      </c>
+      <c r="AC221" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD221" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -5567,32 +5567,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133582070</v>
+        <v>133582046</v>
       </c>
       <c r="B47" t="n">
-        <v>91942</v>
+        <v>80399</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>484969</v>
+        <v>484605</v>
       </c>
       <c r="R47" t="n">
-        <v>7086150</v>
+        <v>7086015</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5674,32 +5674,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133582065</v>
+        <v>133582115</v>
       </c>
       <c r="B48" t="n">
-        <v>91942</v>
+        <v>80399</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>484873</v>
+        <v>485166</v>
       </c>
       <c r="R48" t="n">
-        <v>7086047</v>
+        <v>7086199</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5781,32 +5781,32 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133582223</v>
+        <v>133582110</v>
       </c>
       <c r="B49" t="n">
-        <v>83183</v>
+        <v>80399</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>484876</v>
+        <v>485191</v>
       </c>
       <c r="R49" t="n">
-        <v>7086138</v>
+        <v>7086213</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,7 +5888,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133582106</v>
+        <v>133582070</v>
       </c>
       <c r="B50" t="n">
         <v>91942</v>
@@ -5923,10 +5923,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>485052</v>
+        <v>484969</v>
       </c>
       <c r="R50" t="n">
-        <v>7085993</v>
+        <v>7086150</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5995,10 +5995,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133582156</v>
+        <v>133582065</v>
       </c>
       <c r="B51" t="n">
-        <v>79334</v>
+        <v>91942</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6006,21 +6006,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6030,10 +6030,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>484918</v>
+        <v>484873</v>
       </c>
       <c r="R51" t="n">
-        <v>7086183</v>
+        <v>7086047</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6065,7 +6065,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6102,32 +6102,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133582121</v>
+        <v>133582223</v>
       </c>
       <c r="B52" t="n">
-        <v>91891</v>
+        <v>83183</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6137,10 +6137,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485166</v>
+        <v>484876</v>
       </c>
       <c r="R52" t="n">
-        <v>7086186</v>
+        <v>7086138</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6209,10 +6209,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133582251</v>
+        <v>133582106</v>
       </c>
       <c r="B53" t="n">
-        <v>83183</v>
+        <v>91942</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6220,21 +6220,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6244,10 +6244,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>485137</v>
+        <v>485052</v>
       </c>
       <c r="R53" t="n">
-        <v>7086066</v>
+        <v>7085993</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6316,7 +6316,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133582098</v>
+        <v>133582156</v>
       </c>
       <c r="B54" t="n">
         <v>79334</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>484881</v>
+        <v>484918</v>
       </c>
       <c r="R54" t="n">
-        <v>7085801</v>
+        <v>7086183</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6386,7 +6386,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6396,12 +6396,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>20:53</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6428,32 +6423,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133582083</v>
+        <v>133582121</v>
       </c>
       <c r="B55" t="n">
-        <v>79493</v>
+        <v>91891</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1249</v>
+        <v>5447</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6463,10 +6458,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>484926</v>
+        <v>485166</v>
       </c>
       <c r="R55" t="n">
-        <v>7086090</v>
+        <v>7086186</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6498,7 +6493,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6508,7 +6503,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6535,10 +6530,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133582021</v>
+        <v>133582251</v>
       </c>
       <c r="B56" t="n">
-        <v>91942</v>
+        <v>83183</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6546,21 +6541,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6570,10 +6565,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>485082</v>
+        <v>485137</v>
       </c>
       <c r="R56" t="n">
-        <v>7086186</v>
+        <v>7086066</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6605,7 +6600,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6615,7 +6610,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6642,10 +6637,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133582273</v>
+        <v>133582098</v>
       </c>
       <c r="B57" t="n">
-        <v>80439</v>
+        <v>79334</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6653,21 +6648,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6677,10 +6672,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>484937</v>
+        <v>484881</v>
       </c>
       <c r="R57" t="n">
-        <v>7086072</v>
+        <v>7085801</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6712,7 +6707,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6722,7 +6717,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6749,32 +6749,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133582261</v>
+        <v>133582083</v>
       </c>
       <c r="B58" t="n">
-        <v>80439</v>
+        <v>79493</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485011</v>
+        <v>484926</v>
       </c>
       <c r="R58" t="n">
-        <v>7086069</v>
+        <v>7086090</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6819,7 +6819,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6856,10 +6856,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133582248</v>
+        <v>133582021</v>
       </c>
       <c r="B59" t="n">
-        <v>83311</v>
+        <v>91942</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6867,21 +6867,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>308</v>
+        <v>1204</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6891,10 +6891,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>485157</v>
+        <v>485082</v>
       </c>
       <c r="R59" t="n">
-        <v>7086076</v>
+        <v>7086186</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6963,10 +6963,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133582036</v>
+        <v>133582273</v>
       </c>
       <c r="B60" t="n">
-        <v>57958</v>
+        <v>80439</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6974,50 +6974,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>484867</v>
+        <v>484937</v>
       </c>
       <c r="R60" t="n">
-        <v>7086182</v>
+        <v>7086072</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7049,7 +7033,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7059,12 +7043,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Bohål, flertalet i tajgagrantickerötad granhögstubbe.  Hane ser ut att färdigställa bohål vid besöket.</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7091,32 +7070,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133582046</v>
+        <v>133582261</v>
       </c>
       <c r="B61" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7126,10 +7105,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>484605</v>
+        <v>485011</v>
       </c>
       <c r="R61" t="n">
-        <v>7086015</v>
+        <v>7086069</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7161,7 +7140,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7171,7 +7150,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7198,32 +7177,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133582115</v>
+        <v>133582248</v>
       </c>
       <c r="B62" t="n">
-        <v>80399</v>
+        <v>83311</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>229497</v>
+        <v>308</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7233,10 +7212,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>485166</v>
+        <v>485157</v>
       </c>
       <c r="R62" t="n">
-        <v>7086199</v>
+        <v>7086076</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7268,7 +7247,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7278,7 +7257,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7305,45 +7284,61 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133582110</v>
+        <v>133582036</v>
       </c>
       <c r="B63" t="n">
-        <v>80399</v>
+        <v>57958</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>485191</v>
+        <v>484867</v>
       </c>
       <c r="R63" t="n">
-        <v>7086213</v>
+        <v>7086182</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7375,7 +7370,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7385,7 +7380,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Bohål, flertalet i tajgagrantickerötad granhögstubbe.  Hane ser ut att färdigställa bohål vid besöket.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7412,32 +7412,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133582146</v>
+        <v>133582239</v>
       </c>
       <c r="B64" t="n">
-        <v>80399</v>
+        <v>79493</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7447,10 +7447,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>485019</v>
+        <v>485081</v>
       </c>
       <c r="R64" t="n">
-        <v>7086200</v>
+        <v>7086147</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7482,7 +7482,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7492,7 +7492,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7519,10 +7519,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>133582124</v>
+        <v>133582288</v>
       </c>
       <c r="B65" t="n">
-        <v>80399</v>
+        <v>92651</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7530,21 +7530,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7554,10 +7554,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>485137</v>
+        <v>484904</v>
       </c>
       <c r="R65" t="n">
-        <v>7086195</v>
+        <v>7085957</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7589,7 +7589,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>20:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7626,32 +7626,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>133582049</v>
+        <v>133582249</v>
       </c>
       <c r="B66" t="n">
-        <v>80399</v>
+        <v>83183</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>229497</v>
+        <v>1312</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7661,10 +7661,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>484616</v>
+        <v>485150</v>
       </c>
       <c r="R66" t="n">
-        <v>7085997</v>
+        <v>7086053</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8161,32 +8161,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>133582239</v>
+        <v>133582146</v>
       </c>
       <c r="B71" t="n">
-        <v>79493</v>
+        <v>80399</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8196,10 +8196,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>485081</v>
+        <v>485019</v>
       </c>
       <c r="R71" t="n">
-        <v>7086147</v>
+        <v>7086200</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8241,7 +8241,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>18:41</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8268,10 +8268,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>133582288</v>
+        <v>133582124</v>
       </c>
       <c r="B72" t="n">
-        <v>92651</v>
+        <v>80399</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8279,21 +8279,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8303,10 +8303,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>484904</v>
+        <v>485137</v>
       </c>
       <c r="R72" t="n">
-        <v>7085957</v>
+        <v>7086195</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8338,7 +8338,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>20:39</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8375,32 +8375,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>133582249</v>
+        <v>133582049</v>
       </c>
       <c r="B73" t="n">
-        <v>83183</v>
+        <v>80399</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>1312</v>
+        <v>229497</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8410,10 +8410,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>485150</v>
+        <v>484616</v>
       </c>
       <c r="R73" t="n">
-        <v>7086053</v>
+        <v>7085997</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8445,7 +8445,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8455,7 +8455,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -13465,32 +13465,32 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>133582133</v>
+        <v>133582075</v>
       </c>
       <c r="B120" t="n">
-        <v>80474</v>
+        <v>91928</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6463</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13500,10 +13500,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>485084</v>
+        <v>485160</v>
       </c>
       <c r="R120" t="n">
-        <v>7086179</v>
+        <v>7086132</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13535,7 +13535,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13545,7 +13545,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13572,32 +13572,32 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>133582026</v>
+        <v>133582211</v>
       </c>
       <c r="B121" t="n">
-        <v>80439</v>
+        <v>92624</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13607,10 +13607,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>485057</v>
+        <v>484833</v>
       </c>
       <c r="R121" t="n">
-        <v>7086210</v>
+        <v>7085991</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13642,7 +13642,7 @@
       </c>
       <c r="Z121" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
@@ -13652,7 +13652,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13679,32 +13679,32 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>133582185</v>
+        <v>133582044</v>
       </c>
       <c r="B122" t="n">
-        <v>80439</v>
+        <v>92624</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13714,10 +13714,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>484663</v>
+        <v>484638</v>
       </c>
       <c r="R122" t="n">
-        <v>7085977</v>
+        <v>7086023</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13749,7 +13749,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13759,7 +13759,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13898,32 +13898,32 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>133582116</v>
+        <v>133582230</v>
       </c>
       <c r="B124" t="n">
-        <v>79493</v>
+        <v>80399</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13933,10 +13933,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>485168</v>
+        <v>485000</v>
       </c>
       <c r="R124" t="n">
-        <v>7086214</v>
+        <v>7086155</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13968,7 +13968,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13978,7 +13978,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14005,32 +14005,32 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>133582314</v>
+        <v>133582205</v>
       </c>
       <c r="B125" t="n">
-        <v>79334</v>
+        <v>80399</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6425</v>
+        <v>229497</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -14040,10 +14040,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>485031</v>
+        <v>484779</v>
       </c>
       <c r="R125" t="n">
-        <v>7085985</v>
+        <v>7085989</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14075,7 +14075,7 @@
       </c>
       <c r="Z125" t="inlineStr">
         <is>
-          <t>21:13</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
@@ -14085,12 +14085,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>21:13</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;500 bålar</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14117,32 +14112,32 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>133582162</v>
+        <v>133582101</v>
       </c>
       <c r="B126" t="n">
-        <v>79493</v>
+        <v>80399</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -14152,10 +14147,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>484794</v>
+        <v>484978</v>
       </c>
       <c r="R126" t="n">
-        <v>7086094</v>
+        <v>7085798</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14187,7 +14182,7 @@
       </c>
       <c r="Z126" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
@@ -14197,7 +14192,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>20:59</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14224,32 +14219,32 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>133582085</v>
+        <v>133582116</v>
       </c>
       <c r="B127" t="n">
-        <v>91942</v>
+        <v>79493</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14259,10 +14254,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>484920</v>
+        <v>485168</v>
       </c>
       <c r="R127" t="n">
-        <v>7086079</v>
+        <v>7086214</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14294,7 +14289,7 @@
       </c>
       <c r="Z127" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
@@ -14304,7 +14299,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>20:26</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14331,10 +14326,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>133582075</v>
+        <v>133582314</v>
       </c>
       <c r="B128" t="n">
-        <v>91928</v>
+        <v>79334</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14342,21 +14337,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -14366,10 +14361,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>485160</v>
+        <v>485031</v>
       </c>
       <c r="R128" t="n">
-        <v>7086132</v>
+        <v>7085985</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14401,7 +14396,7 @@
       </c>
       <c r="Z128" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>21:13</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
@@ -14411,7 +14406,12 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>21:13</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;500 bålar</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14438,10 +14438,10 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>133582211</v>
+        <v>133582162</v>
       </c>
       <c r="B129" t="n">
-        <v>92624</v>
+        <v>79493</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14449,21 +14449,21 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>898</v>
+        <v>1249</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
@@ -14473,10 +14473,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>484833</v>
+        <v>484794</v>
       </c>
       <c r="R129" t="n">
-        <v>7085991</v>
+        <v>7086094</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14508,7 +14508,7 @@
       </c>
       <c r="Z129" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
@@ -14518,7 +14518,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14545,32 +14545,32 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>133582044</v>
+        <v>133582085</v>
       </c>
       <c r="B130" t="n">
-        <v>92624</v>
+        <v>91942</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>898</v>
+        <v>1204</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr"/>
@@ -14580,10 +14580,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>484638</v>
+        <v>484920</v>
       </c>
       <c r="R130" t="n">
-        <v>7086023</v>
+        <v>7086079</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14615,7 +14615,7 @@
       </c>
       <c r="Z130" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
@@ -14625,7 +14625,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>20:26</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14652,10 +14652,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>133582230</v>
+        <v>133582133</v>
       </c>
       <c r="B131" t="n">
-        <v>80399</v>
+        <v>80474</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14663,21 +14663,21 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>229497</v>
+        <v>6463</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -14687,10 +14687,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>485000</v>
+        <v>485084</v>
       </c>
       <c r="R131" t="n">
-        <v>7086155</v>
+        <v>7086179</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -14722,7 +14722,7 @@
       </c>
       <c r="Z131" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
@@ -14732,7 +14732,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14759,32 +14759,32 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>133582205</v>
+        <v>133582026</v>
       </c>
       <c r="B132" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14794,10 +14794,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>484779</v>
+        <v>485057</v>
       </c>
       <c r="R132" t="n">
-        <v>7085989</v>
+        <v>7086210</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14829,7 +14829,7 @@
       </c>
       <c r="Z132" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
@@ -14839,7 +14839,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14866,32 +14866,32 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>133582101</v>
+        <v>133582185</v>
       </c>
       <c r="B133" t="n">
-        <v>80399</v>
+        <v>80439</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14901,10 +14901,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>484978</v>
+        <v>484663</v>
       </c>
       <c r="R133" t="n">
-        <v>7085798</v>
+        <v>7085977</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14936,7 +14936,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14946,7 +14946,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>20:59</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD133" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133582027</v>
+        <v>133582094</v>
       </c>
       <c r="B14" t="n">
-        <v>80423</v>
+        <v>92182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>485054</v>
+        <v>484889</v>
       </c>
       <c r="R14" t="n">
-        <v>7086211</v>
+        <v>7085970</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133582264</v>
+        <v>133582089</v>
       </c>
       <c r="B15" t="n">
-        <v>80473</v>
+        <v>57975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,34 +2100,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484985</v>
+        <v>484911</v>
       </c>
       <c r="R15" t="n">
-        <v>7086052</v>
+        <v>7086064</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2159,7 +2167,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2169,7 +2177,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Troligt bohål, ca 1,7 m upp i tajgagrantickerötad död gran</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2196,10 +2209,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133582078</v>
+        <v>133582027</v>
       </c>
       <c r="B16" t="n">
-        <v>92182</v>
+        <v>80423</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2207,21 +2220,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2231,10 +2244,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485145</v>
+        <v>485054</v>
       </c>
       <c r="R16" t="n">
-        <v>7086096</v>
+        <v>7086211</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2266,7 +2279,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2276,7 +2289,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2303,32 +2316,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133582094</v>
+        <v>133582264</v>
       </c>
       <c r="B17" t="n">
-        <v>92182</v>
+        <v>80473</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2338,10 +2351,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484889</v>
+        <v>484985</v>
       </c>
       <c r="R17" t="n">
-        <v>7085970</v>
+        <v>7086052</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2373,7 +2386,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2383,7 +2396,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2410,32 +2423,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133582194</v>
+        <v>133582078</v>
       </c>
       <c r="B18" t="n">
-        <v>80473</v>
+        <v>92182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2445,10 +2458,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>484693</v>
+        <v>485145</v>
       </c>
       <c r="R18" t="n">
-        <v>7085982</v>
+        <v>7086096</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2480,7 +2493,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2490,7 +2503,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2517,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133582058</v>
+        <v>133582194</v>
       </c>
       <c r="B19" t="n">
-        <v>91957</v>
+        <v>80473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2528,21 +2541,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2552,10 +2565,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484700</v>
+        <v>484693</v>
       </c>
       <c r="R19" t="n">
-        <v>7085983</v>
+        <v>7085982</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2624,10 +2637,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133582089</v>
+        <v>133582058</v>
       </c>
       <c r="B20" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2635,42 +2648,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>484911</v>
+        <v>484700</v>
       </c>
       <c r="R20" t="n">
-        <v>7086064</v>
+        <v>7085983</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2702,7 +2707,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2712,12 +2717,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Troligt bohål, ca 1,7 m upp i tajgagrantickerötad död gran</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -5567,32 +5567,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133582070</v>
+        <v>133582046</v>
       </c>
       <c r="B47" t="n">
-        <v>91971</v>
+        <v>80423</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>484969</v>
+        <v>484605</v>
       </c>
       <c r="R47" t="n">
-        <v>7086150</v>
+        <v>7086015</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5674,32 +5674,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133582046</v>
+        <v>133582065</v>
       </c>
       <c r="B48" t="n">
-        <v>80423</v>
+        <v>91971</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>484605</v>
+        <v>484873</v>
       </c>
       <c r="R48" t="n">
-        <v>7086015</v>
+        <v>7086047</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5781,10 +5781,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133582065</v>
+        <v>133582223</v>
       </c>
       <c r="B49" t="n">
-        <v>91971</v>
+        <v>83207</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>484873</v>
+        <v>484876</v>
       </c>
       <c r="R49" t="n">
-        <v>7086047</v>
+        <v>7086138</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,10 +5888,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133582223</v>
+        <v>133582036</v>
       </c>
       <c r="B50" t="n">
-        <v>83207</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5899,34 +5899,50 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>484876</v>
+        <v>484867</v>
       </c>
       <c r="R50" t="n">
-        <v>7086138</v>
+        <v>7086182</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5958,7 +5974,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5968,7 +5984,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Bohål, flertalet i tajgagrantickerötad granhögstubbe.  Hane ser ut att färdigställa bohål vid besöket.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5995,10 +6016,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133582036</v>
+        <v>133582106</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>91971</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6006,50 +6027,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>484867</v>
+        <v>485052</v>
       </c>
       <c r="R51" t="n">
-        <v>7086182</v>
+        <v>7085993</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6081,7 +6086,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6091,12 +6096,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Bohål, flertalet i tajgagrantickerötad granhögstubbe.  Hane ser ut att färdigställa bohål vid besöket.</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133582106</v>
+        <v>133582156</v>
       </c>
       <c r="B52" t="n">
-        <v>91971</v>
+        <v>79358</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485052</v>
+        <v>484918</v>
       </c>
       <c r="R52" t="n">
-        <v>7085993</v>
+        <v>7086183</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6230,10 +6230,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133582273</v>
+        <v>133582248</v>
       </c>
       <c r="B53" t="n">
-        <v>80473</v>
+        <v>83335</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6241,21 +6241,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>484937</v>
+        <v>485157</v>
       </c>
       <c r="R53" t="n">
-        <v>7086072</v>
+        <v>7086076</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6337,32 +6337,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133582156</v>
+        <v>133582121</v>
       </c>
       <c r="B54" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>484918</v>
+        <v>485166</v>
       </c>
       <c r="R54" t="n">
-        <v>7086183</v>
+        <v>7086186</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6444,10 +6444,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133582248</v>
+        <v>133582261</v>
       </c>
       <c r="B55" t="n">
-        <v>83335</v>
+        <v>80473</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6455,21 +6455,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485157</v>
+        <v>485011</v>
       </c>
       <c r="R55" t="n">
-        <v>7086076</v>
+        <v>7086069</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6551,10 +6551,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133582121</v>
+        <v>133582115</v>
       </c>
       <c r="B56" t="n">
-        <v>91920</v>
+        <v>80423</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6562,21 +6562,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6589,7 +6589,7 @@
         <v>485166</v>
       </c>
       <c r="R56" t="n">
-        <v>7086186</v>
+        <v>7086199</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6658,10 +6658,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133582261</v>
+        <v>133582251</v>
       </c>
       <c r="B57" t="n">
-        <v>80473</v>
+        <v>83207</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6669,21 +6669,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485011</v>
+        <v>485137</v>
       </c>
       <c r="R57" t="n">
-        <v>7086069</v>
+        <v>7086066</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6765,7 +6765,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133582115</v>
+        <v>133582110</v>
       </c>
       <c r="B58" t="n">
         <v>80423</v>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485166</v>
+        <v>485191</v>
       </c>
       <c r="R58" t="n">
-        <v>7086199</v>
+        <v>7086213</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6872,10 +6872,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133582251</v>
+        <v>133582098</v>
       </c>
       <c r="B59" t="n">
-        <v>83207</v>
+        <v>79358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6883,21 +6883,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>485137</v>
+        <v>484881</v>
       </c>
       <c r="R59" t="n">
-        <v>7086066</v>
+        <v>7085801</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6952,7 +6952,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6979,32 +6984,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133582110</v>
+        <v>133582083</v>
       </c>
       <c r="B60" t="n">
-        <v>80423</v>
+        <v>79517</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7014,10 +7019,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>485191</v>
+        <v>484926</v>
       </c>
       <c r="R60" t="n">
-        <v>7086213</v>
+        <v>7086090</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7049,7 +7054,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7059,7 +7064,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7086,10 +7091,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133582098</v>
+        <v>133582021</v>
       </c>
       <c r="B61" t="n">
-        <v>79358</v>
+        <v>91971</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7097,21 +7102,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7121,10 +7126,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>484881</v>
+        <v>485082</v>
       </c>
       <c r="R61" t="n">
-        <v>7085801</v>
+        <v>7086186</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7156,7 +7161,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7166,12 +7171,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>20:53</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7198,32 +7198,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133582083</v>
+        <v>133582070</v>
       </c>
       <c r="B62" t="n">
-        <v>79517</v>
+        <v>91971</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>484926</v>
+        <v>484969</v>
       </c>
       <c r="R62" t="n">
-        <v>7086090</v>
+        <v>7086150</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7305,10 +7305,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133582021</v>
+        <v>133582273</v>
       </c>
       <c r="B63" t="n">
-        <v>91971</v>
+        <v>80473</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7316,21 +7316,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>485082</v>
+        <v>484937</v>
       </c>
       <c r="R63" t="n">
-        <v>7086186</v>
+        <v>7086072</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -10866,32 +10866,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133582100</v>
+        <v>133582235</v>
       </c>
       <c r="B96" t="n">
-        <v>80478</v>
+        <v>80473</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10901,10 +10901,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>484979</v>
+        <v>485030</v>
       </c>
       <c r="R96" t="n">
-        <v>7085799</v>
+        <v>7086138</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10973,32 +10973,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133582282</v>
+        <v>133582067</v>
       </c>
       <c r="B97" t="n">
-        <v>80473</v>
+        <v>79517</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11008,10 +11008,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>484917</v>
+        <v>484880</v>
       </c>
       <c r="R97" t="n">
-        <v>7086029</v>
+        <v>7086089</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11080,32 +11080,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133582235</v>
+        <v>133582100</v>
       </c>
       <c r="B98" t="n">
-        <v>80473</v>
+        <v>80478</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>485030</v>
+        <v>484979</v>
       </c>
       <c r="R98" t="n">
-        <v>7086138</v>
+        <v>7085799</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11187,32 +11187,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133582067</v>
+        <v>133582282</v>
       </c>
       <c r="B99" t="n">
-        <v>79517</v>
+        <v>80473</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11222,10 +11222,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>484880</v>
+        <v>484917</v>
       </c>
       <c r="R99" t="n">
-        <v>7086089</v>
+        <v>7086029</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11294,32 +11294,32 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>133582105</v>
+        <v>133582233</v>
       </c>
       <c r="B100" t="n">
-        <v>92182</v>
+        <v>80473</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11329,10 +11329,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>485150</v>
+        <v>485025</v>
       </c>
       <c r="R100" t="n">
-        <v>7085949</v>
+        <v>7086137</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11364,7 +11364,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>21:10</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11401,10 +11401,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>133582042</v>
+        <v>133582163</v>
       </c>
       <c r="B101" t="n">
-        <v>57975</v>
+        <v>91971</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11412,21 +11412,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11436,10 +11436,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>484762</v>
+        <v>484703</v>
       </c>
       <c r="R101" t="n">
-        <v>7086084</v>
+        <v>7086043</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:12</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11481,12 +11481,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:12</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack färska</t>
+          <t>17:17</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11513,10 +11508,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>133582234</v>
+        <v>133582224</v>
       </c>
       <c r="B102" t="n">
-        <v>91971</v>
+        <v>80473</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11524,21 +11519,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11548,10 +11543,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>485009</v>
+        <v>484963</v>
       </c>
       <c r="R102" t="n">
-        <v>7086144</v>
+        <v>7086155</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11583,7 +11578,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11593,7 +11588,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11620,10 +11615,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133582179</v>
+        <v>133582105</v>
       </c>
       <c r="B103" t="n">
-        <v>80423</v>
+        <v>92182</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11631,21 +11626,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11655,10 +11650,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>484623</v>
+        <v>485150</v>
       </c>
       <c r="R103" t="n">
-        <v>7086004</v>
+        <v>7085949</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11690,7 +11685,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11700,7 +11695,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>21:10</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11727,10 +11722,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>133582188</v>
+        <v>133582042</v>
       </c>
       <c r="B104" t="n">
-        <v>80473</v>
+        <v>57975</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11738,21 +11733,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11762,10 +11757,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>484675</v>
+        <v>484762</v>
       </c>
       <c r="R104" t="n">
-        <v>7085987</v>
+        <v>7086084</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11797,7 +11792,7 @@
       </c>
       <c r="Z104" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:12</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
@@ -11807,7 +11802,12 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>17:47</t>
+          <t>17:12</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack färska</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11834,10 +11834,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>133582184</v>
+        <v>133582234</v>
       </c>
       <c r="B105" t="n">
-        <v>80473</v>
+        <v>91971</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11845,21 +11845,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11869,10 +11869,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>484657</v>
+        <v>485009</v>
       </c>
       <c r="R105" t="n">
-        <v>7085984</v>
+        <v>7086144</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11904,7 +11904,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11941,32 +11941,32 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>133582233</v>
+        <v>133582179</v>
       </c>
       <c r="B106" t="n">
-        <v>80473</v>
+        <v>80423</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11976,10 +11976,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>485025</v>
+        <v>484623</v>
       </c>
       <c r="R106" t="n">
-        <v>7086137</v>
+        <v>7086004</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12011,7 +12011,7 @@
       </c>
       <c r="Z106" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12048,10 +12048,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>133582163</v>
+        <v>133582145</v>
       </c>
       <c r="B107" t="n">
-        <v>91971</v>
+        <v>80473</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12059,21 +12059,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12083,10 +12083,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>484703</v>
+        <v>485022</v>
       </c>
       <c r="R107" t="n">
-        <v>7086043</v>
+        <v>7086194</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12118,7 +12118,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12128,7 +12128,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:17</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12155,7 +12155,7 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>133582224</v>
+        <v>133582144</v>
       </c>
       <c r="B108" t="n">
         <v>80473</v>
@@ -12190,10 +12190,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>484963</v>
+        <v>485024</v>
       </c>
       <c r="R108" t="n">
-        <v>7086155</v>
+        <v>7086180</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12225,7 +12225,7 @@
       </c>
       <c r="Z108" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
@@ -12235,7 +12235,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12262,7 +12262,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>133582145</v>
+        <v>133582255</v>
       </c>
       <c r="B109" t="n">
         <v>80473</v>
@@ -12297,10 +12297,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>485022</v>
+        <v>485082</v>
       </c>
       <c r="R109" t="n">
-        <v>7086194</v>
+        <v>7086082</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12332,7 +12332,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12342,7 +12342,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12369,7 +12369,7 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>133582144</v>
+        <v>133582034</v>
       </c>
       <c r="B110" t="n">
         <v>80473</v>
@@ -12404,10 +12404,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>485024</v>
+        <v>484996</v>
       </c>
       <c r="R110" t="n">
-        <v>7086180</v>
+        <v>7086209</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12439,7 +12439,7 @@
       </c>
       <c r="Z110" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12476,7 +12476,7 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>133582255</v>
+        <v>133582195</v>
       </c>
       <c r="B111" t="n">
         <v>80473</v>
@@ -12511,10 +12511,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>485082</v>
+        <v>484677</v>
       </c>
       <c r="R111" t="n">
-        <v>7086082</v>
+        <v>7085977</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12546,7 +12546,7 @@
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
@@ -12556,7 +12556,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12583,7 +12583,7 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>133582034</v>
+        <v>133582188</v>
       </c>
       <c r="B112" t="n">
         <v>80473</v>
@@ -12618,10 +12618,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>484996</v>
+        <v>484675</v>
       </c>
       <c r="R112" t="n">
-        <v>7086209</v>
+        <v>7085987</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12653,7 +12653,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12663,7 +12663,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>17:47</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12690,7 +12690,7 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>133582195</v>
+        <v>133582184</v>
       </c>
       <c r="B113" t="n">
         <v>80473</v>
@@ -12725,10 +12725,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>484677</v>
+        <v>484657</v>
       </c>
       <c r="R113" t="n">
-        <v>7085977</v>
+        <v>7085984</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12760,7 +12760,7 @@
       </c>
       <c r="Z113" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12797,10 +12797,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>133582193</v>
+        <v>133582153</v>
       </c>
       <c r="B114" t="n">
-        <v>80473</v>
+        <v>57975</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12808,34 +12808,54 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P114" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>484684</v>
+        <v>484961</v>
       </c>
       <c r="R114" t="n">
-        <v>7085987</v>
+        <v>7086205</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12867,7 +12887,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:37</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12877,7 +12897,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>16:37</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Trummande och födosökande</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12904,32 +12929,32 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>133582022</v>
+        <v>133582227</v>
       </c>
       <c r="B115" t="n">
-        <v>92579</v>
+        <v>80473</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1106</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12939,10 +12964,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>485091</v>
+        <v>484991</v>
       </c>
       <c r="R115" t="n">
-        <v>7086182</v>
+        <v>7086162</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12974,7 +12999,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12984,16 +13009,15 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD115" t="b">
         <v>0</v>
       </c>
       <c r="AE115" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF115" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -13012,65 +13036,45 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>133582153</v>
+        <v>133582283</v>
       </c>
       <c r="B116" t="n">
-        <v>57975</v>
+        <v>79517</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100109</v>
+        <v>1249</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>484961</v>
+        <v>484915</v>
       </c>
       <c r="R116" t="n">
-        <v>7086205</v>
+        <v>7086011</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13102,7 +13106,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:37</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -13112,12 +13116,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:37</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Trummande och födosökande</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13144,7 +13143,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>133582227</v>
+        <v>133582193</v>
       </c>
       <c r="B117" t="n">
         <v>80473</v>
@@ -13179,10 +13178,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>484991</v>
+        <v>484684</v>
       </c>
       <c r="R117" t="n">
-        <v>7086162</v>
+        <v>7085987</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13214,7 +13213,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -13224,7 +13223,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13251,10 +13250,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>133582283</v>
+        <v>133582022</v>
       </c>
       <c r="B118" t="n">
-        <v>79517</v>
+        <v>92579</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13262,21 +13261,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>1249</v>
+        <v>1106</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13286,10 +13285,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>484915</v>
+        <v>485091</v>
       </c>
       <c r="R118" t="n">
-        <v>7086011</v>
+        <v>7086182</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13321,7 +13320,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13331,15 +13330,16 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -21668,7 +21668,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>133582050</v>
+        <v>133582192</v>
       </c>
       <c r="B196" t="n">
         <v>80473</v>
@@ -21697,23 +21697,16 @@
         </is>
       </c>
       <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
-      <c r="K196" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
-      <c r="N196" t="inlineStr"/>
       <c r="P196" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>484621</v>
+        <v>484686</v>
       </c>
       <c r="R196" t="n">
-        <v>7085976</v>
+        <v>7086001</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -21745,7 +21738,7 @@
       </c>
       <c r="Z196" t="inlineStr">
         <is>
-          <t>17:38</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AA196" t="inlineStr">
@@ -21755,12 +21748,7 @@
       </c>
       <c r="AB196" t="inlineStr">
         <is>
-          <t>17:38</t>
-        </is>
-      </c>
-      <c r="AC196" t="inlineStr">
-        <is>
-          <t>Med apothecier</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="AD196" t="b">
@@ -21769,7 +21757,6 @@
       <c r="AE196" t="b">
         <v>0</v>
       </c>
-      <c r="AF196" t="inlineStr"/>
       <c r="AG196" t="b">
         <v>0</v>
       </c>
@@ -21788,7 +21775,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>133582025</v>
+        <v>133582240</v>
       </c>
       <c r="B197" t="n">
         <v>80473</v>
@@ -21823,10 +21810,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>485061</v>
+        <v>485087</v>
       </c>
       <c r="R197" t="n">
-        <v>7086190</v>
+        <v>7086110</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -21858,7 +21845,7 @@
       </c>
       <c r="Z197" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AA197" t="inlineStr">
@@ -21868,7 +21855,7 @@
       </c>
       <c r="AB197" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="AD197" t="b">
@@ -21895,10 +21882,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>133582157</v>
+        <v>133582076</v>
       </c>
       <c r="B198" t="n">
-        <v>80473</v>
+        <v>91971</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -21906,21 +21893,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -21930,10 +21917,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>484872</v>
+        <v>485222</v>
       </c>
       <c r="R198" t="n">
-        <v>7086175</v>
+        <v>7086147</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -21965,7 +21952,7 @@
       </c>
       <c r="Z198" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -21975,7 +21962,7 @@
       </c>
       <c r="AB198" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="AD198" t="b">
@@ -22002,7 +21989,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>133582192</v>
+        <v>133582111</v>
       </c>
       <c r="B199" t="n">
         <v>80473</v>
@@ -22037,10 +22024,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>484686</v>
+        <v>485195</v>
       </c>
       <c r="R199" t="n">
-        <v>7086001</v>
+        <v>7086212</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -22072,7 +22059,7 @@
       </c>
       <c r="Z199" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA199" t="inlineStr">
@@ -22082,7 +22069,7 @@
       </c>
       <c r="AB199" t="inlineStr">
         <is>
-          <t>17:50</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD199" t="b">
@@ -22109,7 +22096,7 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>133582240</v>
+        <v>133582141</v>
       </c>
       <c r="B200" t="n">
         <v>80473</v>
@@ -22144,10 +22131,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>485087</v>
+        <v>485018</v>
       </c>
       <c r="R200" t="n">
-        <v>7086110</v>
+        <v>7086170</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -22179,7 +22166,7 @@
       </c>
       <c r="Z200" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA200" t="inlineStr">
@@ -22189,7 +22176,7 @@
       </c>
       <c r="AB200" t="inlineStr">
         <is>
-          <t>18:42</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD200" t="b">
@@ -22216,10 +22203,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>133582076</v>
+        <v>133582038</v>
       </c>
       <c r="B201" t="n">
-        <v>91971</v>
+        <v>57975</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -22227,21 +22214,21 @@
         </is>
       </c>
       <c r="E201" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -22251,10 +22238,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>485222</v>
+        <v>484815</v>
       </c>
       <c r="R201" t="n">
-        <v>7086147</v>
+        <v>7086160</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -22286,7 +22273,7 @@
       </c>
       <c r="Z201" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA201" t="inlineStr">
@@ -22296,7 +22283,12 @@
       </c>
       <c r="AB201" t="inlineStr">
         <is>
-          <t>18:51</t>
+          <t>17:04</t>
+        </is>
+      </c>
+      <c r="AC201" t="inlineStr">
+        <is>
+          <t>Ringhack färska och äldre</t>
         </is>
       </c>
       <c r="AD201" t="b">
@@ -22323,10 +22315,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>133582111</v>
+        <v>133582165</v>
       </c>
       <c r="B202" t="n">
-        <v>80473</v>
+        <v>91971</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -22334,21 +22326,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -22358,10 +22350,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>485195</v>
+        <v>484635</v>
       </c>
       <c r="R202" t="n">
-        <v>7086212</v>
+        <v>7086042</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -22393,7 +22385,7 @@
       </c>
       <c r="Z202" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA202" t="inlineStr">
@@ -22403,7 +22395,7 @@
       </c>
       <c r="AB202" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AD202" t="b">
@@ -22430,10 +22422,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>133582141</v>
+        <v>133582039</v>
       </c>
       <c r="B203" t="n">
-        <v>80473</v>
+        <v>57975</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -22441,21 +22433,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -22465,10 +22457,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>485018</v>
+        <v>484820</v>
       </c>
       <c r="R203" t="n">
-        <v>7086170</v>
+        <v>7086145</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -22500,7 +22492,7 @@
       </c>
       <c r="Z203" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:06</t>
         </is>
       </c>
       <c r="AA203" t="inlineStr">
@@ -22510,7 +22502,12 @@
       </c>
       <c r="AB203" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:06</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD203" t="b">
@@ -22537,10 +22534,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>133582038</v>
+        <v>133582050</v>
       </c>
       <c r="B204" t="n">
-        <v>57975</v>
+        <v>80473</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -22548,34 +22545,41 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
+      <c r="J204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N204" t="inlineStr"/>
       <c r="P204" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>484815</v>
+        <v>484621</v>
       </c>
       <c r="R204" t="n">
-        <v>7086160</v>
+        <v>7085976</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -22607,7 +22611,7 @@
       </c>
       <c r="Z204" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AA204" t="inlineStr">
@@ -22617,12 +22621,12 @@
       </c>
       <c r="AB204" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:38</t>
         </is>
       </c>
       <c r="AC204" t="inlineStr">
         <is>
-          <t>Ringhack färska och äldre</t>
+          <t>Med apothecier</t>
         </is>
       </c>
       <c r="AD204" t="b">
@@ -22631,6 +22635,7 @@
       <c r="AE204" t="b">
         <v>0</v>
       </c>
+      <c r="AF204" t="inlineStr"/>
       <c r="AG204" t="b">
         <v>0</v>
       </c>
@@ -22649,10 +22654,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>133582165</v>
+        <v>133582025</v>
       </c>
       <c r="B205" t="n">
-        <v>91971</v>
+        <v>80473</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -22660,21 +22665,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -22684,10 +22689,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>484635</v>
+        <v>485061</v>
       </c>
       <c r="R205" t="n">
-        <v>7086042</v>
+        <v>7086190</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -22719,7 +22724,7 @@
       </c>
       <c r="Z205" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA205" t="inlineStr">
@@ -22729,7 +22734,7 @@
       </c>
       <c r="AB205" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD205" t="b">
@@ -22756,10 +22761,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>133582039</v>
+        <v>133582157</v>
       </c>
       <c r="B206" t="n">
-        <v>57975</v>
+        <v>80473</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -22767,21 +22772,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -22791,10 +22796,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>484820</v>
+        <v>484872</v>
       </c>
       <c r="R206" t="n">
-        <v>7086145</v>
+        <v>7086175</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -22826,7 +22831,7 @@
       </c>
       <c r="Z206" t="inlineStr">
         <is>
-          <t>17:06</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AA206" t="inlineStr">
@@ -22836,12 +22841,7 @@
       </c>
       <c r="AB206" t="inlineStr">
         <is>
-          <t>17:06</t>
-        </is>
-      </c>
-      <c r="AC206" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="AD206" t="b">
@@ -24590,32 +24590,32 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>133582254</v>
+        <v>133582186</v>
       </c>
       <c r="B223" t="n">
-        <v>79517</v>
+        <v>80423</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -24625,10 +24625,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>485098</v>
+        <v>484668</v>
       </c>
       <c r="R223" t="n">
-        <v>7086073</v>
+        <v>7085980</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -24660,7 +24660,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -24670,7 +24670,7 @@
       </c>
       <c r="AB223" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -24697,7 +24697,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>133582081</v>
+        <v>133582053</v>
       </c>
       <c r="B224" t="n">
         <v>79358</v>
@@ -24732,10 +24732,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>485108</v>
+        <v>484633</v>
       </c>
       <c r="R224" t="n">
-        <v>7086096</v>
+        <v>7085966</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -24767,7 +24767,7 @@
       </c>
       <c r="Z224" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -24777,7 +24777,7 @@
       </c>
       <c r="AB224" t="inlineStr">
         <is>
-          <t>20:04</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="AD224" t="b">
@@ -24804,7 +24804,7 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>133582126</v>
+        <v>133582215</v>
       </c>
       <c r="B225" t="n">
         <v>80473</v>
@@ -24839,10 +24839,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>485151</v>
+        <v>484868</v>
       </c>
       <c r="R225" t="n">
-        <v>7086178</v>
+        <v>7086047</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -24874,7 +24874,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="AB225" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD225" t="b">
@@ -24911,32 +24911,32 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>133582186</v>
+        <v>133582254</v>
       </c>
       <c r="B226" t="n">
-        <v>80423</v>
+        <v>79517</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -24946,10 +24946,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>484668</v>
+        <v>485098</v>
       </c>
       <c r="R226" t="n">
-        <v>7085980</v>
+        <v>7086073</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -24981,7 +24981,7 @@
       </c>
       <c r="Z226" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -24991,7 +24991,7 @@
       </c>
       <c r="AB226" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -25018,7 +25018,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>133582053</v>
+        <v>133582081</v>
       </c>
       <c r="B227" t="n">
         <v>79358</v>
@@ -25053,10 +25053,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>484633</v>
+        <v>485108</v>
       </c>
       <c r="R227" t="n">
-        <v>7085966</v>
+        <v>7086096</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -25088,7 +25088,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -25098,7 +25098,7 @@
       </c>
       <c r="AB227" t="inlineStr">
         <is>
-          <t>17:41</t>
+          <t>20:04</t>
         </is>
       </c>
       <c r="AD227" t="b">
@@ -25125,7 +25125,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>133582215</v>
+        <v>133582126</v>
       </c>
       <c r="B228" t="n">
         <v>80473</v>
@@ -25160,10 +25160,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>484868</v>
+        <v>485151</v>
       </c>
       <c r="R228" t="n">
-        <v>7086047</v>
+        <v>7086178</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -25195,7 +25195,7 @@
       </c>
       <c r="Z228" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
@@ -25205,7 +25205,7 @@
       </c>
       <c r="AB228" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="AD228" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -1982,10 +1982,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133582094</v>
+        <v>133582027</v>
       </c>
       <c r="B14" t="n">
-        <v>92182</v>
+        <v>80423</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
+        <v>229497</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>484889</v>
+        <v>485054</v>
       </c>
       <c r="R14" t="n">
-        <v>7085970</v>
+        <v>7086211</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>20:40</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2089,10 +2089,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133582089</v>
+        <v>133582264</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>80473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,42 +2100,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>484911</v>
+        <v>484985</v>
       </c>
       <c r="R15" t="n">
-        <v>7086064</v>
+        <v>7086052</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2167,7 +2159,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>20:29</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2177,12 +2169,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>20:29</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Troligt bohål, ca 1,7 m upp i tajgagrantickerötad död gran</t>
+          <t>20:19</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,10 +2196,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133582027</v>
+        <v>133582078</v>
       </c>
       <c r="B16" t="n">
-        <v>80423</v>
+        <v>92182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2220,21 +2207,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229497</v>
+        <v>3298</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2244,10 +2231,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>485054</v>
+        <v>485145</v>
       </c>
       <c r="R16" t="n">
-        <v>7086211</v>
+        <v>7086096</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2279,7 +2266,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2289,7 +2276,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,32 +2303,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133582264</v>
+        <v>133582094</v>
       </c>
       <c r="B17" t="n">
-        <v>80473</v>
+        <v>92182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>3298</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2351,10 +2338,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>484985</v>
+        <v>484889</v>
       </c>
       <c r="R17" t="n">
-        <v>7086052</v>
+        <v>7085970</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2386,7 +2373,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2396,7 +2383,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>20:19</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2423,32 +2410,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133582078</v>
+        <v>133582194</v>
       </c>
       <c r="B18" t="n">
-        <v>92182</v>
+        <v>80473</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2458,10 +2445,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>485145</v>
+        <v>484693</v>
       </c>
       <c r="R18" t="n">
-        <v>7086096</v>
+        <v>7085982</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2493,7 +2480,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2503,7 +2490,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2530,10 +2517,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133582194</v>
+        <v>133582058</v>
       </c>
       <c r="B19" t="n">
-        <v>80473</v>
+        <v>91957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2541,21 +2528,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,10 +2552,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>484693</v>
+        <v>484700</v>
       </c>
       <c r="R19" t="n">
-        <v>7085982</v>
+        <v>7085983</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2637,10 +2624,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133582058</v>
+        <v>133582089</v>
       </c>
       <c r="B20" t="n">
-        <v>91957</v>
+        <v>57975</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2648,34 +2635,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>484700</v>
+        <v>484911</v>
       </c>
       <c r="R20" t="n">
-        <v>7085983</v>
+        <v>7086064</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2707,7 +2702,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2717,7 +2712,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>20:29</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Troligt bohål, ca 1,7 m upp i tajgagrantickerötad död gran</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -5567,32 +5567,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133582046</v>
+        <v>133582070</v>
       </c>
       <c r="B47" t="n">
-        <v>80423</v>
+        <v>91971</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>484605</v>
+        <v>484969</v>
       </c>
       <c r="R47" t="n">
-        <v>7086015</v>
+        <v>7086150</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5674,32 +5674,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133582065</v>
+        <v>133582046</v>
       </c>
       <c r="B48" t="n">
-        <v>91971</v>
+        <v>80423</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1204</v>
+        <v>229497</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>484873</v>
+        <v>484605</v>
       </c>
       <c r="R48" t="n">
-        <v>7086047</v>
+        <v>7086015</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5781,10 +5781,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133582223</v>
+        <v>133582065</v>
       </c>
       <c r="B49" t="n">
-        <v>83207</v>
+        <v>91971</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>484876</v>
+        <v>484873</v>
       </c>
       <c r="R49" t="n">
-        <v>7086138</v>
+        <v>7086047</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,10 +5888,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133582036</v>
+        <v>133582223</v>
       </c>
       <c r="B50" t="n">
-        <v>57975</v>
+        <v>83207</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5899,50 +5899,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>484867</v>
+        <v>484876</v>
       </c>
       <c r="R50" t="n">
-        <v>7086182</v>
+        <v>7086138</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5974,7 +5958,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5984,12 +5968,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Bohål, flertalet i tajgagrantickerötad granhögstubbe.  Hane ser ut att färdigställa bohål vid besöket.</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6016,10 +5995,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133582106</v>
+        <v>133582036</v>
       </c>
       <c r="B51" t="n">
-        <v>91971</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6027,34 +6006,50 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>485052</v>
+        <v>484867</v>
       </c>
       <c r="R51" t="n">
-        <v>7085993</v>
+        <v>7086182</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6086,7 +6081,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6096,7 +6091,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Bohål, flertalet i tajgagrantickerötad granhögstubbe.  Hane ser ut att färdigställa bohål vid besöket.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133582156</v>
+        <v>133582106</v>
       </c>
       <c r="B52" t="n">
-        <v>79358</v>
+        <v>91971</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>484918</v>
+        <v>485052</v>
       </c>
       <c r="R52" t="n">
-        <v>7086183</v>
+        <v>7085993</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6230,10 +6230,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133582248</v>
+        <v>133582273</v>
       </c>
       <c r="B53" t="n">
-        <v>83335</v>
+        <v>80473</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6241,21 +6241,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>485157</v>
+        <v>484937</v>
       </c>
       <c r="R53" t="n">
-        <v>7086076</v>
+        <v>7086072</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6337,32 +6337,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133582121</v>
+        <v>133582156</v>
       </c>
       <c r="B54" t="n">
-        <v>91920</v>
+        <v>79358</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>485166</v>
+        <v>484918</v>
       </c>
       <c r="R54" t="n">
-        <v>7086186</v>
+        <v>7086183</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6444,10 +6444,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133582261</v>
+        <v>133582248</v>
       </c>
       <c r="B55" t="n">
-        <v>80473</v>
+        <v>83335</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6455,21 +6455,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485011</v>
+        <v>485157</v>
       </c>
       <c r="R55" t="n">
-        <v>7086069</v>
+        <v>7086076</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6551,10 +6551,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133582115</v>
+        <v>133582121</v>
       </c>
       <c r="B56" t="n">
-        <v>80423</v>
+        <v>91920</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6562,21 +6562,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229497</v>
+        <v>5447</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6589,7 +6589,7 @@
         <v>485166</v>
       </c>
       <c r="R56" t="n">
-        <v>7086199</v>
+        <v>7086186</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6658,10 +6658,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133582251</v>
+        <v>133582261</v>
       </c>
       <c r="B57" t="n">
-        <v>83207</v>
+        <v>80473</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6669,21 +6669,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485137</v>
+        <v>485011</v>
       </c>
       <c r="R57" t="n">
-        <v>7086066</v>
+        <v>7086069</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6765,7 +6765,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133582110</v>
+        <v>133582115</v>
       </c>
       <c r="B58" t="n">
         <v>80423</v>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485191</v>
+        <v>485166</v>
       </c>
       <c r="R58" t="n">
-        <v>7086213</v>
+        <v>7086199</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6872,10 +6872,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133582098</v>
+        <v>133582251</v>
       </c>
       <c r="B59" t="n">
-        <v>79358</v>
+        <v>83207</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6883,21 +6883,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>484881</v>
+        <v>485137</v>
       </c>
       <c r="R59" t="n">
-        <v>7085801</v>
+        <v>7086066</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6952,12 +6952,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:53</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6984,32 +6979,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133582083</v>
+        <v>133582110</v>
       </c>
       <c r="B60" t="n">
-        <v>79517</v>
+        <v>80423</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1249</v>
+        <v>229497</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7019,10 +7014,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>484926</v>
+        <v>485191</v>
       </c>
       <c r="R60" t="n">
-        <v>7086090</v>
+        <v>7086213</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7054,7 +7049,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7064,7 +7059,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7091,10 +7086,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133582021</v>
+        <v>133582098</v>
       </c>
       <c r="B61" t="n">
-        <v>91971</v>
+        <v>79358</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7102,21 +7097,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7126,10 +7121,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>485082</v>
+        <v>484881</v>
       </c>
       <c r="R61" t="n">
-        <v>7086186</v>
+        <v>7085801</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7161,7 +7156,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7171,7 +7166,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7198,32 +7198,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133582070</v>
+        <v>133582083</v>
       </c>
       <c r="B62" t="n">
-        <v>91971</v>
+        <v>79517</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>484969</v>
+        <v>484926</v>
       </c>
       <c r="R62" t="n">
-        <v>7086150</v>
+        <v>7086090</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7305,10 +7305,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133582273</v>
+        <v>133582021</v>
       </c>
       <c r="B63" t="n">
-        <v>80473</v>
+        <v>91971</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7316,21 +7316,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>484937</v>
+        <v>485082</v>
       </c>
       <c r="R63" t="n">
-        <v>7086072</v>
+        <v>7086186</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -10866,32 +10866,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>133582235</v>
+        <v>133582100</v>
       </c>
       <c r="B96" t="n">
-        <v>80473</v>
+        <v>80478</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10901,10 +10901,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>485030</v>
+        <v>484979</v>
       </c>
       <c r="R96" t="n">
-        <v>7086138</v>
+        <v>7085799</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10936,7 +10936,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10946,7 +10946,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10973,32 +10973,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>133582067</v>
+        <v>133582282</v>
       </c>
       <c r="B97" t="n">
-        <v>79517</v>
+        <v>80473</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -11008,10 +11008,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>484880</v>
+        <v>484917</v>
       </c>
       <c r="R97" t="n">
-        <v>7086089</v>
+        <v>7086029</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11043,7 +11043,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>18:17</t>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11080,32 +11080,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>133582100</v>
+        <v>133582235</v>
       </c>
       <c r="B98" t="n">
-        <v>80478</v>
+        <v>80473</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11115,10 +11115,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>484979</v>
+        <v>485030</v>
       </c>
       <c r="R98" t="n">
-        <v>7085799</v>
+        <v>7086138</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11150,7 +11150,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11160,7 +11160,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11187,32 +11187,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>133582282</v>
+        <v>133582067</v>
       </c>
       <c r="B99" t="n">
-        <v>80473</v>
+        <v>79517</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11222,10 +11222,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>484917</v>
+        <v>484880</v>
       </c>
       <c r="R99" t="n">
-        <v>7086029</v>
+        <v>7086089</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11257,7 +11257,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -2744,10 +2744,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133582315</v>
+        <v>133582187</v>
       </c>
       <c r="B21" t="n">
-        <v>83207</v>
+        <v>79358</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2755,21 +2755,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>485148</v>
+        <v>484646</v>
       </c>
       <c r="R21" t="n">
-        <v>7086030</v>
+        <v>7085969</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2824,7 +2824,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>21:19</t>
+          <t>17:46</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt &gt;1000 bålar</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2851,10 +2856,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133582197</v>
+        <v>133582315</v>
       </c>
       <c r="B22" t="n">
-        <v>80473</v>
+        <v>83207</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2862,21 +2867,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2886,10 +2891,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>484679</v>
+        <v>485148</v>
       </c>
       <c r="R22" t="n">
-        <v>7085977</v>
+        <v>7086030</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,7 +2926,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2931,7 +2936,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:51</t>
+          <t>21:19</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2958,10 +2963,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>133582132</v>
+        <v>133582197</v>
       </c>
       <c r="B23" t="n">
-        <v>80474</v>
+        <v>80473</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2969,21 +2974,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2993,10 +2998,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>485087</v>
+        <v>484679</v>
       </c>
       <c r="R23" t="n">
-        <v>7086182</v>
+        <v>7085977</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3028,7 +3033,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3038,7 +3043,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:14</t>
+          <t>17:51</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,10 +3070,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>133582087</v>
+        <v>133582132</v>
       </c>
       <c r="B24" t="n">
-        <v>91957</v>
+        <v>80474</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3076,21 +3081,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3100,10 +3105,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>484913</v>
+        <v>485087</v>
       </c>
       <c r="R24" t="n">
-        <v>7086067</v>
+        <v>7086182</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3135,7 +3140,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3145,7 +3150,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>20:28</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3172,10 +3177,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>133582129</v>
+        <v>133582087</v>
       </c>
       <c r="B25" t="n">
-        <v>57975</v>
+        <v>91957</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3183,50 +3188,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>485095</v>
+        <v>484913</v>
       </c>
       <c r="R25" t="n">
-        <v>7086152</v>
+        <v>7086067</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3258,7 +3247,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3268,12 +3257,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:58</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Trummande och födosökande</t>
+          <t>20:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3300,10 +3284,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>133582182</v>
+        <v>133582129</v>
       </c>
       <c r="B26" t="n">
-        <v>80473</v>
+        <v>57975</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3311,34 +3295,50 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>484666</v>
+        <v>485095</v>
       </c>
       <c r="R26" t="n">
-        <v>7086016</v>
+        <v>7086152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3370,7 +3370,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3380,7 +3380,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:40</t>
+          <t>15:58</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Trummande och födosökande</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3407,10 +3412,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>133582291</v>
+        <v>133582182</v>
       </c>
       <c r="B27" t="n">
-        <v>83348</v>
+        <v>80473</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3418,21 +3423,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1467</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rödbrun blekspik</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sclerophora coniophaea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Norman) J.Mattsson &amp; Middelb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3442,10 +3447,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>484929</v>
+        <v>484666</v>
       </c>
       <c r="R27" t="n">
-        <v>7085958</v>
+        <v>7086016</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3477,7 +3482,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3487,7 +3492,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>20:41</t>
+          <t>17:40</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3514,10 +3519,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>133582228</v>
+        <v>133582291</v>
       </c>
       <c r="B28" t="n">
-        <v>80474</v>
+        <v>83348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3525,21 +3530,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>1467</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Rödbrun blekspik</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Sclerophora coniophaea</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Norman) J.Mattsson &amp; Middelb.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3549,10 +3554,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>484994</v>
+        <v>484929</v>
       </c>
       <c r="R28" t="n">
-        <v>7086155</v>
+        <v>7085958</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3584,7 +3589,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3594,7 +3599,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:32</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3621,10 +3626,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>133582258</v>
+        <v>133582228</v>
       </c>
       <c r="B29" t="n">
-        <v>91971</v>
+        <v>80474</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3632,21 +3637,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3656,10 +3661,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>485063</v>
+        <v>484994</v>
       </c>
       <c r="R29" t="n">
-        <v>7086065</v>
+        <v>7086155</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3691,7 +3696,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3701,7 +3706,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>20:13</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3728,32 +3733,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>133582131</v>
+        <v>133582258</v>
       </c>
       <c r="B30" t="n">
-        <v>79517</v>
+        <v>91971</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3763,10 +3768,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>485094</v>
+        <v>485063</v>
       </c>
       <c r="R30" t="n">
-        <v>7086180</v>
+        <v>7086065</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3798,7 +3803,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3808,7 +3813,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>20:13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3835,32 +3840,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>133582259</v>
+        <v>133582131</v>
       </c>
       <c r="B31" t="n">
-        <v>83207</v>
+        <v>79517</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>1249</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3870,10 +3875,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>485025</v>
+        <v>485094</v>
       </c>
       <c r="R31" t="n">
-        <v>7086046</v>
+        <v>7086180</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3905,7 +3910,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3915,7 +3920,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:14</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3942,10 +3947,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133582054</v>
+        <v>133582259</v>
       </c>
       <c r="B32" t="n">
-        <v>80473</v>
+        <v>83207</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3953,21 +3958,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3977,10 +3982,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>484643</v>
+        <v>485025</v>
       </c>
       <c r="R32" t="n">
-        <v>7085961</v>
+        <v>7086046</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4012,7 +4017,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4022,12 +4027,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4054,32 +4054,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>133582279</v>
+        <v>133582054</v>
       </c>
       <c r="B33" t="n">
-        <v>79517</v>
+        <v>80473</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4089,10 +4089,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>484908</v>
+        <v>484643</v>
       </c>
       <c r="R33" t="n">
-        <v>7086035</v>
+        <v>7085961</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4124,7 +4124,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4134,7 +4134,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4161,32 +4166,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>133582243</v>
+        <v>133582279</v>
       </c>
       <c r="B34" t="n">
-        <v>80473</v>
+        <v>79517</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4196,10 +4201,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>485112</v>
+        <v>484908</v>
       </c>
       <c r="R34" t="n">
-        <v>7086149</v>
+        <v>7086035</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4231,7 +4236,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4241,7 +4246,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4268,10 +4273,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>133582187</v>
+        <v>133582243</v>
       </c>
       <c r="B35" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4279,21 +4284,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4303,10 +4308,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>484646</v>
+        <v>485112</v>
       </c>
       <c r="R35" t="n">
-        <v>7085969</v>
+        <v>7086149</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4338,7 +4343,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4348,12 +4353,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:46</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Rikligt &gt;1000 bålar</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4492,32 +4492,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>133582102</v>
+        <v>133582137</v>
       </c>
       <c r="B37" t="n">
-        <v>91971</v>
+        <v>79517</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>1249</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4527,10 +4527,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>485032</v>
+        <v>485049</v>
       </c>
       <c r="R37" t="n">
-        <v>7085899</v>
+        <v>7086191</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>21:06</t>
+          <t>16:19</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4599,32 +4599,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133582278</v>
+        <v>133582091</v>
       </c>
       <c r="B38" t="n">
-        <v>79517</v>
+        <v>80473</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1249</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4634,10 +4634,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>484899</v>
+        <v>484893</v>
       </c>
       <c r="R38" t="n">
-        <v>7086032</v>
+        <v>7086018</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4679,7 +4679,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>20:33</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4706,10 +4706,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133582114</v>
+        <v>133582102</v>
       </c>
       <c r="B39" t="n">
-        <v>80474</v>
+        <v>91971</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4717,21 +4717,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>1204</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4741,10 +4741,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>485164</v>
+        <v>485032</v>
       </c>
       <c r="R39" t="n">
-        <v>7086216</v>
+        <v>7085899</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4786,12 +4786,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>21:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4818,32 +4813,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>133582059</v>
+        <v>133582278</v>
       </c>
       <c r="B40" t="n">
-        <v>80473</v>
+        <v>79517</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>1249</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4853,10 +4848,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>484703</v>
+        <v>484899</v>
       </c>
       <c r="R40" t="n">
-        <v>7085994</v>
+        <v>7086032</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4888,7 +4883,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4898,7 +4893,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:52</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4925,32 +4920,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133582137</v>
+        <v>133582155</v>
       </c>
       <c r="B41" t="n">
-        <v>79517</v>
+        <v>79358</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1249</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4960,10 +4955,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>485049</v>
+        <v>484885</v>
       </c>
       <c r="R41" t="n">
-        <v>7086191</v>
+        <v>7086164</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4995,7 +4990,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5005,7 +5000,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:19</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5032,7 +5027,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>133582091</v>
+        <v>133582072</v>
       </c>
       <c r="B42" t="n">
         <v>80473</v>
@@ -5067,10 +5062,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>484893</v>
+        <v>484979</v>
       </c>
       <c r="R42" t="n">
-        <v>7086018</v>
+        <v>7086133</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5102,7 +5097,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5112,7 +5107,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>20:33</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5139,10 +5134,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>133582155</v>
+        <v>133582268</v>
       </c>
       <c r="B43" t="n">
-        <v>79358</v>
+        <v>80473</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5150,21 +5145,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5174,10 +5169,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>484885</v>
+        <v>484974</v>
       </c>
       <c r="R43" t="n">
-        <v>7086164</v>
+        <v>7086064</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5209,7 +5204,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5219,7 +5214,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5246,10 +5241,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>133582072</v>
+        <v>133582114</v>
       </c>
       <c r="B44" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5257,21 +5252,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5281,10 +5276,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>484979</v>
+        <v>485164</v>
       </c>
       <c r="R44" t="n">
-        <v>7086133</v>
+        <v>7086216</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5316,7 +5311,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5326,7 +5321,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5353,7 +5353,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>133582268</v>
+        <v>133582198</v>
       </c>
       <c r="B45" t="n">
         <v>80473</v>
@@ -5388,10 +5388,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>484974</v>
+        <v>484719</v>
       </c>
       <c r="R45" t="n">
-        <v>7086064</v>
+        <v>7085978</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>17:53</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5460,7 +5460,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>133582198</v>
+        <v>133582059</v>
       </c>
       <c r="B46" t="n">
         <v>80473</v>
@@ -5495,10 +5495,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>484719</v>
+        <v>484703</v>
       </c>
       <c r="R46" t="n">
-        <v>7085978</v>
+        <v>7085994</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5530,7 +5530,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:53</t>
+          <t>17:52</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5567,32 +5567,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>133582070</v>
+        <v>133582046</v>
       </c>
       <c r="B47" t="n">
-        <v>91971</v>
+        <v>80423</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1204</v>
+        <v>229497</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>484969</v>
+        <v>484605</v>
       </c>
       <c r="R47" t="n">
-        <v>7086150</v>
+        <v>7086015</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5637,7 +5637,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5647,7 +5647,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:31</t>
+          <t>17:33</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5674,32 +5674,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>133582046</v>
+        <v>133582065</v>
       </c>
       <c r="B48" t="n">
-        <v>80423</v>
+        <v>91971</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>229497</v>
+        <v>1204</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5709,10 +5709,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>484605</v>
+        <v>484873</v>
       </c>
       <c r="R48" t="n">
-        <v>7086015</v>
+        <v>7086047</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5744,7 +5744,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>17:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5781,10 +5781,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>133582065</v>
+        <v>133582223</v>
       </c>
       <c r="B49" t="n">
-        <v>91971</v>
+        <v>83207</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5792,21 +5792,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1204</v>
+        <v>1312</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5816,10 +5816,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>484873</v>
+        <v>484876</v>
       </c>
       <c r="R49" t="n">
-        <v>7086047</v>
+        <v>7086138</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5851,7 +5851,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5888,10 +5888,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>133582223</v>
+        <v>133582036</v>
       </c>
       <c r="B50" t="n">
-        <v>83207</v>
+        <v>57975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5899,34 +5899,50 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>484876</v>
+        <v>484867</v>
       </c>
       <c r="R50" t="n">
-        <v>7086138</v>
+        <v>7086182</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5958,7 +5974,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5968,7 +5984,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:23</t>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Bohål, flertalet i tajgagrantickerötad granhögstubbe.  Hane ser ut att färdigställa bohål vid besöket.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5995,10 +6016,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>133582036</v>
+        <v>133582106</v>
       </c>
       <c r="B51" t="n">
-        <v>57975</v>
+        <v>91971</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6006,50 +6027,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>bobygge</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Öster-långtjärnen, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>484867</v>
+        <v>485052</v>
       </c>
       <c r="R51" t="n">
-        <v>7086182</v>
+        <v>7085993</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6081,7 +6086,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6091,12 +6096,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Bohål, flertalet i tajgagrantickerötad granhögstubbe.  Hane ser ut att färdigställa bohål vid besöket.</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6123,10 +6123,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>133582106</v>
+        <v>133582156</v>
       </c>
       <c r="B52" t="n">
-        <v>91971</v>
+        <v>79358</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6134,21 +6134,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6158,10 +6158,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>485052</v>
+        <v>484918</v>
       </c>
       <c r="R52" t="n">
-        <v>7085993</v>
+        <v>7086183</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6193,7 +6193,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6203,7 +6203,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>21:15</t>
+          <t>16:42</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6230,10 +6230,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>133582273</v>
+        <v>133582248</v>
       </c>
       <c r="B53" t="n">
-        <v>80473</v>
+        <v>83335</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6241,21 +6241,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>308</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6265,10 +6265,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>484937</v>
+        <v>485157</v>
       </c>
       <c r="R53" t="n">
-        <v>7086072</v>
+        <v>7086076</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>20:25</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6337,32 +6337,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>133582156</v>
+        <v>133582121</v>
       </c>
       <c r="B54" t="n">
-        <v>79358</v>
+        <v>91920</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6372,10 +6372,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>484918</v>
+        <v>485166</v>
       </c>
       <c r="R54" t="n">
-        <v>7086183</v>
+        <v>7086186</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6407,7 +6407,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6417,7 +6417,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:42</t>
+          <t>15:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6444,10 +6444,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>133582248</v>
+        <v>133582261</v>
       </c>
       <c r="B55" t="n">
-        <v>83335</v>
+        <v>80473</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6455,21 +6455,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>308</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6479,10 +6479,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>485157</v>
+        <v>485011</v>
       </c>
       <c r="R55" t="n">
-        <v>7086076</v>
+        <v>7086069</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6514,7 +6514,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:56</t>
+          <t>20:16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6551,10 +6551,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>133582121</v>
+        <v>133582115</v>
       </c>
       <c r="B56" t="n">
-        <v>91920</v>
+        <v>80423</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6562,21 +6562,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5447</v>
+        <v>229497</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6589,7 +6589,7 @@
         <v>485166</v>
       </c>
       <c r="R56" t="n">
-        <v>7086186</v>
+        <v>7086199</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6621,7 +6621,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6631,7 +6631,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:48</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6658,10 +6658,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>133582261</v>
+        <v>133582251</v>
       </c>
       <c r="B57" t="n">
-        <v>80473</v>
+        <v>83207</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6669,21 +6669,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6693,10 +6693,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>485011</v>
+        <v>485137</v>
       </c>
       <c r="R57" t="n">
-        <v>7086069</v>
+        <v>7086066</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6728,7 +6728,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>20:16</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6765,7 +6765,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>133582115</v>
+        <v>133582110</v>
       </c>
       <c r="B58" t="n">
         <v>80423</v>
@@ -6800,10 +6800,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>485166</v>
+        <v>485191</v>
       </c>
       <c r="R58" t="n">
-        <v>7086199</v>
+        <v>7086213</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6835,7 +6835,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6845,7 +6845,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6872,10 +6872,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>133582251</v>
+        <v>133582098</v>
       </c>
       <c r="B59" t="n">
-        <v>83207</v>
+        <v>79358</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6883,21 +6883,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6907,10 +6907,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>485137</v>
+        <v>484881</v>
       </c>
       <c r="R59" t="n">
-        <v>7086066</v>
+        <v>7085801</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6942,7 +6942,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:53</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -6952,7 +6952,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>20:53</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6979,32 +6984,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>133582110</v>
+        <v>133582083</v>
       </c>
       <c r="B60" t="n">
-        <v>80423</v>
+        <v>79517</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229497</v>
+        <v>1249</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7014,10 +7019,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>485191</v>
+        <v>484926</v>
       </c>
       <c r="R60" t="n">
-        <v>7086213</v>
+        <v>7086090</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7049,7 +7054,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7059,7 +7064,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:28</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7086,10 +7091,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>133582098</v>
+        <v>133582021</v>
       </c>
       <c r="B61" t="n">
-        <v>79358</v>
+        <v>91971</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7097,21 +7102,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7121,10 +7126,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>484881</v>
+        <v>485082</v>
       </c>
       <c r="R61" t="n">
-        <v>7085801</v>
+        <v>7086186</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7156,7 +7161,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>20:53</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7166,12 +7171,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>20:53</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7198,32 +7198,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>133582083</v>
+        <v>133582070</v>
       </c>
       <c r="B62" t="n">
-        <v>79517</v>
+        <v>91971</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1249</v>
+        <v>1204</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7233,10 +7233,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>484926</v>
+        <v>484969</v>
       </c>
       <c r="R62" t="n">
-        <v>7086090</v>
+        <v>7086150</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7278,7 +7278,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>20:21</t>
+          <t>18:31</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7305,10 +7305,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>133582021</v>
+        <v>133582273</v>
       </c>
       <c r="B63" t="n">
-        <v>91971</v>
+        <v>80473</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7316,21 +7316,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7340,10 +7340,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>485082</v>
+        <v>484937</v>
       </c>
       <c r="R63" t="n">
-        <v>7086186</v>
+        <v>7086072</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7375,7 +7375,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7385,7 +7385,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 17285-2026 artfynd.xlsx
+++ b/artfynd/A 17285-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY233"/>
+  <dimension ref="A1:AZ233"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582231</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582248</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582082</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582044</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582211</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582022</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1422,6 +1457,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582080</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1529,6 +1569,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582130</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1636,6 +1681,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582018</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1743,6 +1793,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582043</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1850,6 +1905,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582058</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1957,6 +2017,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582066</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2064,6 +2129,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582069</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2171,6 +2241,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582075</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2278,6 +2353,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582087</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2385,6 +2465,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582109</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2492,6 +2577,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582210</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2599,6 +2689,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582310</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2706,6 +2801,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2813,6 +2913,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582021</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2920,6 +3025,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582056</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3027,6 +3137,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582065</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3134,6 +3249,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582070</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3241,6 +3361,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582076</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3348,6 +3473,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582084</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3455,6 +3585,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582085</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3562,6 +3697,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582102</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3669,6 +3809,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582106</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3776,6 +3921,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582108</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3883,6 +4033,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582139</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3990,6 +4145,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582140</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4097,6 +4257,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582163</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4204,6 +4369,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582165</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4311,6 +4481,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582168</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4418,6 +4593,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582209</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4525,6 +4705,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582220</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4632,6 +4817,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582234</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4739,6 +4929,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582258</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4846,6 +5041,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582311</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4953,6 +5153,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582067</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5060,6 +5265,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582083</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5167,6 +5377,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582116</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5274,6 +5489,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582131</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5381,6 +5601,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582136</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5488,6 +5713,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582137</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5595,6 +5825,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582162</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5702,6 +5937,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582190</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5809,6 +6049,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582239</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5916,6 +6161,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582242</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6023,6 +6273,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582250</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6130,6 +6385,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582254</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6237,6 +6497,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582260</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6344,6 +6609,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582263</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6451,6 +6721,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582278</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6558,6 +6833,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582279</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6665,6 +6945,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582283</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6772,6 +7057,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582309</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6879,6 +7169,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582223</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6986,6 +7281,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582249</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7093,6 +7393,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582251</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7200,6 +7505,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582259</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7307,6 +7617,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582272</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7414,6 +7729,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582315</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7521,6 +7841,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582291</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7633,6 +7958,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582114</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7740,6 +8070,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582132</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7847,6 +8182,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582173</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7954,6 +8294,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582178</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8061,6 +8406,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582228</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8168,6 +8518,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582252</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8275,6 +8630,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582020</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8382,6 +8742,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582041</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8489,6 +8854,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582078</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8596,6 +8966,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582094</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8703,6 +9078,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582105</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8810,6 +9190,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582149</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8917,6 +9302,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582164</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9024,6 +9414,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582280</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9131,6 +9526,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582288</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9238,6 +9638,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582121</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9345,6 +9750,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582212</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9452,6 +9862,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582053</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9564,6 +9979,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582055</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9671,6 +10091,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582081</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9783,6 +10208,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582092</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9895,6 +10325,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582093</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10007,6 +10442,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582095</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10119,6 +10559,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582096</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10231,6 +10676,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582098</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10338,6 +10788,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582119</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10445,6 +10900,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582155</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10552,6 +11012,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582156</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10664,6 +11129,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582166</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10776,6 +11246,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582187</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10883,6 +11358,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582221</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10995,6 +11475,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582290</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11107,6 +11592,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582298</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11219,6 +11709,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582299</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11331,6 +11826,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582305</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11443,6 +11943,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582307</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11555,6 +12060,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582314</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11662,6 +12172,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582025</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11769,6 +12284,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582026</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11876,6 +12396,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582034</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11983,6 +12508,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582047</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12103,6 +12633,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582048</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12223,6 +12758,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582050</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12330,6 +12870,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582051</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12437,6 +12982,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582052</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12549,6 +13099,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582054</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12661,6 +13216,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582057</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12768,6 +13328,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582059</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12875,6 +13440,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582071</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12982,6 +13552,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582072</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13094,6 +13669,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582073</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13201,6 +13781,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582074</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13308,6 +13893,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582086</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13415,6 +14005,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582091</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13527,6 +14122,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582099</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13634,6 +14234,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582103</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13741,6 +14346,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582111</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13848,6 +14458,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582112</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13955,6 +14570,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582117</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14062,6 +14682,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582122</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14169,6 +14794,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582126</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14276,6 +14906,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582134</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14383,6 +15018,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582141</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14490,6 +15130,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582144</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14597,6 +15242,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582145</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14704,6 +15354,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582148</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14811,6 +15466,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582150</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14918,6 +15578,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582152</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15025,6 +15690,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582157</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15132,6 +15802,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582160</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15239,6 +15914,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582161</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15346,6 +16026,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582172</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15453,6 +16138,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582175</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15560,6 +16250,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582176</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15667,6 +16362,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582180</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15774,6 +16474,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582182</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15881,6 +16586,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582184</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15988,6 +16698,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582185</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16095,6 +16810,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582188</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16202,6 +16922,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582192</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16309,6 +17034,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582193</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16416,6 +17146,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582194</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16523,6 +17258,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582195</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16630,6 +17370,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582196</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16737,6 +17482,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582197</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16844,6 +17594,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582198</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16951,6 +17706,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582199</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17058,6 +17818,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582200</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17165,6 +17930,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582201</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17272,6 +18042,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582203</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17379,6 +18154,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582206</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17486,6 +18266,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582207</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17593,6 +18378,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582208</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17700,6 +18490,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582213</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17807,6 +18602,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582215</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17914,6 +18714,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582217</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18021,6 +18826,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582224</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18128,6 +18938,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582225</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18235,6 +19050,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582227</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18342,6 +19162,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582229</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18449,6 +19274,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582232</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18556,6 +19386,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582233</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18663,6 +19498,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582235</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18770,6 +19610,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582237</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18877,6 +19722,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582240</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18984,6 +19834,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582243</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19091,6 +19946,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582246</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19198,6 +20058,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582255</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19305,6 +20170,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582256</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19412,6 +20282,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582257</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19519,6 +20394,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582261</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19626,6 +20506,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582264</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19733,6 +20618,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582265</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19840,6 +20730,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582266</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19947,6 +20842,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582268</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20054,6 +20954,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582271</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20161,6 +21066,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582273</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20268,6 +21178,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582274</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20375,6 +21290,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582275</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20482,6 +21402,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582276</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20589,6 +21514,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582282</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20696,6 +21626,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582292</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20803,6 +21738,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582295</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20910,6 +21850,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582296</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21017,6 +21962,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582301</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21124,6 +22074,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582100</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21231,6 +22186,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582174</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21338,6 +22298,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582303</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21445,6 +22410,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582133</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21552,6 +22522,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582204</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21659,6 +22634,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582300</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21766,6 +22746,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582183</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21878,6 +22863,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582035</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22006,6 +22996,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582036</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22118,6 +23113,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582038</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22230,6 +23230,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582039</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22342,6 +23347,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582042</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22462,6 +23472,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582045</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22574,6 +23589,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582060</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22686,6 +23706,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582061</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -22798,6 +23823,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582062</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22910,6 +23940,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582063</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -23022,6 +24057,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582064</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -23142,6 +24182,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582089</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -23254,6 +24299,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582097</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -23382,6 +24432,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582129</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -23514,6 +24569,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582153</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -23634,6 +24694,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582218</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -23746,6 +24811,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582286</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -23858,6 +24928,11 @@
         </is>
       </c>
       <c r="AY215" t="inlineStr"/>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582297</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23965,6 +25040,11 @@
         </is>
       </c>
       <c r="AY216" t="inlineStr"/>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582245</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -24072,6 +25152,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582027</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -24179,6 +25264,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582046</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -24286,6 +25376,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582049</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -24393,6 +25488,11 @@
         </is>
       </c>
       <c r="AY220" t="inlineStr"/>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582101</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -24500,6 +25600,11 @@
         </is>
       </c>
       <c r="AY221" t="inlineStr"/>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582110</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -24607,6 +25712,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582115</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -24714,6 +25824,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582124</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -24821,6 +25936,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582135</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24928,6 +26048,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582146</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -25035,6 +26160,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582170</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -25142,6 +26272,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582177</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -25249,6 +26384,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582179</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -25356,6 +26496,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582186</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -25463,6 +26608,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582205</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -25570,6 +26720,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582230</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -25677,6 +26832,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582302</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -25789,8 +26949,247 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133582202</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>